--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -473,7 +473,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -496,7 +496,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +517,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -540,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -645,7 +645,7 @@
         <v>5</v>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -473,7 +473,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         <v>5</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6780"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="1068">
   <si>
     <t>Topic</t>
   </si>
@@ -3231,9 +3231,6 @@
   </si>
   <si>
     <t>Which animal can survive extreme heat?</t>
-  </si>
-  <si>
-    <t>Which animal can sleep upside down?</t>
   </si>
 </sst>
 </file>
@@ -4220,7 +4217,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E841"/>
+  <dimension ref="A1:E840"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="41.8571428571429" customWidth="1"/>
@@ -18509,23 +18506,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="841" spans="1:5">
-      <c r="A841" t="s">
-        <v>639</v>
-      </c>
-      <c r="B841" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C841" t="s">
-        <v>634</v>
-      </c>
-      <c r="D841">
-        <v>7</v>
-      </c>
-      <c r="E841" t="b">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6780"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3263,7 +3263,7 @@
     <t>Right</t>
   </si>
   <si>
-    <t>None</t>
+    <t/>
   </si>
   <si>
     <t>If you overtake the last person in a race, what position are you in?</t>
@@ -5439,12 +5439,7 @@
   <dimension ref="A1:I641"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="61.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="26.1428571428571" customWidth="1"/>
-    <col min="4" max="4" width="22.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="20.8571428571429" customWidth="1"/>
-    <col min="6" max="6" width="20.2857142857143" customWidth="1"/>
-    <col min="7" max="7" width="16.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="22.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -7242,7 +7237,7 @@
         <v>5</v>
       </c>
       <c r="I62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -7271,7 +7266,7 @@
         <v>5</v>
       </c>
       <c r="I63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -7300,7 +7295,7 @@
         <v>5</v>
       </c>
       <c r="I64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -7329,7 +7324,7 @@
         <v>5</v>
       </c>
       <c r="I65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -7358,7 +7353,7 @@
         <v>5</v>
       </c>
       <c r="I66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -7387,7 +7382,7 @@
         <v>5</v>
       </c>
       <c r="I67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -7416,7 +7411,7 @@
         <v>5</v>
       </c>
       <c r="I68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -7445,7 +7440,7 @@
         <v>5</v>
       </c>
       <c r="I69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -7474,7 +7469,7 @@
         <v>5</v>
       </c>
       <c r="I70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -7503,7 +7498,7 @@
         <v>5</v>
       </c>
       <c r="I71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -7532,7 +7527,7 @@
         <v>5</v>
       </c>
       <c r="I72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -7561,7 +7556,7 @@
         <v>5</v>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -7590,7 +7585,7 @@
         <v>5</v>
       </c>
       <c r="I74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -7619,7 +7614,7 @@
         <v>5</v>
       </c>
       <c r="I75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -7648,7 +7643,7 @@
         <v>5</v>
       </c>
       <c r="I76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -7677,7 +7672,7 @@
         <v>5</v>
       </c>
       <c r="I77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -7706,7 +7701,7 @@
         <v>5</v>
       </c>
       <c r="I78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -7735,7 +7730,7 @@
         <v>5</v>
       </c>
       <c r="I79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -7764,7 +7759,7 @@
         <v>5</v>
       </c>
       <c r="I80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -7793,7 +7788,7 @@
         <v>5</v>
       </c>
       <c r="I81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -7822,7 +7817,7 @@
         <v>5</v>
       </c>
       <c r="I82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -7851,7 +7846,7 @@
         <v>5</v>
       </c>
       <c r="I83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -7880,7 +7875,7 @@
         <v>5</v>
       </c>
       <c r="I84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -7909,7 +7904,7 @@
         <v>5</v>
       </c>
       <c r="I85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -7938,7 +7933,7 @@
         <v>5</v>
       </c>
       <c r="I86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -7967,7 +7962,7 @@
         <v>5</v>
       </c>
       <c r="I87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -7996,7 +7991,7 @@
         <v>5</v>
       </c>
       <c r="I88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -8025,7 +8020,7 @@
         <v>5</v>
       </c>
       <c r="I89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -8054,7 +8049,7 @@
         <v>5</v>
       </c>
       <c r="I90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -8083,7 +8078,7 @@
         <v>5</v>
       </c>
       <c r="I91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -8112,7 +8107,7 @@
         <v>5</v>
       </c>
       <c r="I92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -8141,7 +8136,7 @@
         <v>5</v>
       </c>
       <c r="I93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -8170,7 +8165,7 @@
         <v>5</v>
       </c>
       <c r="I94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -8199,7 +8194,7 @@
         <v>5</v>
       </c>
       <c r="I95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -8228,7 +8223,7 @@
         <v>5</v>
       </c>
       <c r="I96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -8257,7 +8252,7 @@
         <v>5</v>
       </c>
       <c r="I97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -8286,7 +8281,7 @@
         <v>5</v>
       </c>
       <c r="I98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -8315,7 +8310,7 @@
         <v>5</v>
       </c>
       <c r="I99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -8344,7 +8339,7 @@
         <v>5</v>
       </c>
       <c r="I100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -8373,7 +8368,7 @@
         <v>5</v>
       </c>
       <c r="I101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -8402,7 +8397,7 @@
         <v>5</v>
       </c>
       <c r="I102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -8431,7 +8426,7 @@
         <v>5</v>
       </c>
       <c r="I103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -8460,7 +8455,7 @@
         <v>5</v>
       </c>
       <c r="I104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -8489,7 +8484,7 @@
         <v>5</v>
       </c>
       <c r="I105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -8518,7 +8513,7 @@
         <v>5</v>
       </c>
       <c r="I106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -8547,7 +8542,7 @@
         <v>5</v>
       </c>
       <c r="I107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -8576,7 +8571,7 @@
         <v>5</v>
       </c>
       <c r="I108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -8605,7 +8600,7 @@
         <v>5</v>
       </c>
       <c r="I109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -8634,7 +8629,7 @@
         <v>5</v>
       </c>
       <c r="I110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -8663,7 +8658,7 @@
         <v>5</v>
       </c>
       <c r="I111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -8692,7 +8687,7 @@
         <v>5</v>
       </c>
       <c r="I112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -8721,7 +8716,7 @@
         <v>5</v>
       </c>
       <c r="I113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -8750,7 +8745,7 @@
         <v>5</v>
       </c>
       <c r="I114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -8779,7 +8774,7 @@
         <v>5</v>
       </c>
       <c r="I115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -8808,7 +8803,7 @@
         <v>5</v>
       </c>
       <c r="I116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -8837,7 +8832,7 @@
         <v>5</v>
       </c>
       <c r="I117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -8866,7 +8861,7 @@
         <v>5</v>
       </c>
       <c r="I118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -8895,7 +8890,7 @@
         <v>5</v>
       </c>
       <c r="I119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -8924,7 +8919,7 @@
         <v>5</v>
       </c>
       <c r="I120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -8953,7 +8948,7 @@
         <v>5</v>
       </c>
       <c r="I121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -8982,7 +8977,7 @@
         <v>5</v>
       </c>
       <c r="I122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -9011,7 +9006,7 @@
         <v>5</v>
       </c>
       <c r="I123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -9040,7 +9035,7 @@
         <v>5</v>
       </c>
       <c r="I124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -9069,7 +9064,7 @@
         <v>5</v>
       </c>
       <c r="I125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -9098,7 +9093,7 @@
         <v>5</v>
       </c>
       <c r="I126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -9127,7 +9122,7 @@
         <v>5</v>
       </c>
       <c r="I127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -9156,7 +9151,7 @@
         <v>5</v>
       </c>
       <c r="I128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -9185,7 +9180,7 @@
         <v>5</v>
       </c>
       <c r="I129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -9214,7 +9209,7 @@
         <v>5</v>
       </c>
       <c r="I130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -9243,7 +9238,7 @@
         <v>5</v>
       </c>
       <c r="I131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -9272,7 +9267,7 @@
         <v>5</v>
       </c>
       <c r="I132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -9301,7 +9296,7 @@
         <v>5</v>
       </c>
       <c r="I133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -9330,7 +9325,7 @@
         <v>5</v>
       </c>
       <c r="I134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -9359,7 +9354,7 @@
         <v>5</v>
       </c>
       <c r="I135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -9388,7 +9383,7 @@
         <v>5</v>
       </c>
       <c r="I136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -9417,7 +9412,7 @@
         <v>5</v>
       </c>
       <c r="I137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -9446,7 +9441,7 @@
         <v>5</v>
       </c>
       <c r="I138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -9475,7 +9470,7 @@
         <v>5</v>
       </c>
       <c r="I139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -9504,7 +9499,7 @@
         <v>5</v>
       </c>
       <c r="I140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -9533,7 +9528,7 @@
         <v>5</v>
       </c>
       <c r="I141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -9562,7 +9557,7 @@
         <v>5</v>
       </c>
       <c r="I142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -9591,7 +9586,7 @@
         <v>5</v>
       </c>
       <c r="I143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -9620,7 +9615,7 @@
         <v>5</v>
       </c>
       <c r="I144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -9649,7 +9644,7 @@
         <v>5</v>
       </c>
       <c r="I145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -9678,7 +9673,7 @@
         <v>5</v>
       </c>
       <c r="I146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -9707,7 +9702,7 @@
         <v>5</v>
       </c>
       <c r="I147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -9736,7 +9731,7 @@
         <v>5</v>
       </c>
       <c r="I148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -9765,7 +9760,7 @@
         <v>5</v>
       </c>
       <c r="I149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -9794,7 +9789,7 @@
         <v>5</v>
       </c>
       <c r="I150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -9823,7 +9818,7 @@
         <v>5</v>
       </c>
       <c r="I151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -9852,7 +9847,7 @@
         <v>5</v>
       </c>
       <c r="I152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -9881,7 +9876,7 @@
         <v>5</v>
       </c>
       <c r="I153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -9910,7 +9905,7 @@
         <v>5</v>
       </c>
       <c r="I154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -9939,7 +9934,7 @@
         <v>5</v>
       </c>
       <c r="I155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -9968,7 +9963,7 @@
         <v>5</v>
       </c>
       <c r="I156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -9997,7 +9992,7 @@
         <v>5</v>
       </c>
       <c r="I157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -10026,7 +10021,7 @@
         <v>5</v>
       </c>
       <c r="I158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -10055,7 +10050,7 @@
         <v>5</v>
       </c>
       <c r="I159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -10084,7 +10079,7 @@
         <v>5</v>
       </c>
       <c r="I160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -10113,7 +10108,7 @@
         <v>5</v>
       </c>
       <c r="I161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -10142,7 +10137,7 @@
         <v>5</v>
       </c>
       <c r="I162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -10171,7 +10166,7 @@
         <v>5</v>
       </c>
       <c r="I163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -10200,7 +10195,7 @@
         <v>5</v>
       </c>
       <c r="I164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -10229,7 +10224,7 @@
         <v>5</v>
       </c>
       <c r="I165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -10258,7 +10253,7 @@
         <v>5</v>
       </c>
       <c r="I166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -10287,7 +10282,7 @@
         <v>5</v>
       </c>
       <c r="I167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -10316,7 +10311,7 @@
         <v>5</v>
       </c>
       <c r="I168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -10345,7 +10340,7 @@
         <v>5</v>
       </c>
       <c r="I169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -10374,7 +10369,7 @@
         <v>5</v>
       </c>
       <c r="I170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -10403,7 +10398,7 @@
         <v>5</v>
       </c>
       <c r="I171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -10432,7 +10427,7 @@
         <v>5</v>
       </c>
       <c r="I172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -10461,7 +10456,7 @@
         <v>5</v>
       </c>
       <c r="I173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -10490,7 +10485,7 @@
         <v>5</v>
       </c>
       <c r="I174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -10519,7 +10514,7 @@
         <v>5</v>
       </c>
       <c r="I175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -10548,7 +10543,7 @@
         <v>5</v>
       </c>
       <c r="I176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -10577,7 +10572,7 @@
         <v>5</v>
       </c>
       <c r="I177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -10606,7 +10601,7 @@
         <v>5</v>
       </c>
       <c r="I178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -10635,7 +10630,7 @@
         <v>5</v>
       </c>
       <c r="I179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -10664,7 +10659,7 @@
         <v>5</v>
       </c>
       <c r="I180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -10693,7 +10688,7 @@
         <v>5</v>
       </c>
       <c r="I181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -10722,7 +10717,7 @@
         <v>5</v>
       </c>
       <c r="I182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -10751,7 +10746,7 @@
         <v>5</v>
       </c>
       <c r="I183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -10780,7 +10775,7 @@
         <v>5</v>
       </c>
       <c r="I184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -10809,7 +10804,7 @@
         <v>5</v>
       </c>
       <c r="I185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -10838,7 +10833,7 @@
         <v>5</v>
       </c>
       <c r="I186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -10867,7 +10862,7 @@
         <v>5</v>
       </c>
       <c r="I187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -10896,7 +10891,7 @@
         <v>5</v>
       </c>
       <c r="I188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -10925,7 +10920,7 @@
         <v>5</v>
       </c>
       <c r="I189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -10954,7 +10949,7 @@
         <v>5</v>
       </c>
       <c r="I190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -10983,7 +10978,7 @@
         <v>5</v>
       </c>
       <c r="I191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -11012,7 +11007,7 @@
         <v>5</v>
       </c>
       <c r="I192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -11041,7 +11036,7 @@
         <v>5</v>
       </c>
       <c r="I193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -11070,7 +11065,7 @@
         <v>5</v>
       </c>
       <c r="I194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -11099,7 +11094,7 @@
         <v>5</v>
       </c>
       <c r="I195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -11128,7 +11123,7 @@
         <v>5</v>
       </c>
       <c r="I196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -11157,7 +11152,7 @@
         <v>5</v>
       </c>
       <c r="I197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -11186,7 +11181,7 @@
         <v>5</v>
       </c>
       <c r="I198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -11215,7 +11210,7 @@
         <v>5</v>
       </c>
       <c r="I199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -11244,7 +11239,7 @@
         <v>5</v>
       </c>
       <c r="I200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -11273,7 +11268,7 @@
         <v>5</v>
       </c>
       <c r="I201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -11302,7 +11297,7 @@
         <v>5</v>
       </c>
       <c r="I202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -11331,7 +11326,7 @@
         <v>5</v>
       </c>
       <c r="I203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -11360,7 +11355,7 @@
         <v>5</v>
       </c>
       <c r="I204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -11389,7 +11384,7 @@
         <v>5</v>
       </c>
       <c r="I205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -11418,7 +11413,7 @@
         <v>5</v>
       </c>
       <c r="I206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -11447,7 +11442,7 @@
         <v>5</v>
       </c>
       <c r="I207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -11476,7 +11471,7 @@
         <v>5</v>
       </c>
       <c r="I208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -11505,7 +11500,7 @@
         <v>5</v>
       </c>
       <c r="I209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -11534,7 +11529,7 @@
         <v>5</v>
       </c>
       <c r="I210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -11563,7 +11558,7 @@
         <v>5</v>
       </c>
       <c r="I211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -11592,7 +11587,7 @@
         <v>5</v>
       </c>
       <c r="I212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:9">
@@ -11621,7 +11616,7 @@
         <v>5</v>
       </c>
       <c r="I213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -11650,7 +11645,7 @@
         <v>5</v>
       </c>
       <c r="I214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -11679,7 +11674,7 @@
         <v>5</v>
       </c>
       <c r="I215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -11708,7 +11703,7 @@
         <v>5</v>
       </c>
       <c r="I216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:9">
@@ -11737,7 +11732,7 @@
         <v>5</v>
       </c>
       <c r="I217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -11766,7 +11761,7 @@
         <v>5</v>
       </c>
       <c r="I218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -11795,7 +11790,7 @@
         <v>5</v>
       </c>
       <c r="I219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -11824,7 +11819,7 @@
         <v>5</v>
       </c>
       <c r="I220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -11853,7 +11848,7 @@
         <v>5</v>
       </c>
       <c r="I221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -11882,7 +11877,7 @@
         <v>5</v>
       </c>
       <c r="I222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -11911,7 +11906,7 @@
         <v>5</v>
       </c>
       <c r="I223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -11940,7 +11935,7 @@
         <v>5</v>
       </c>
       <c r="I224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -11969,7 +11964,7 @@
         <v>5</v>
       </c>
       <c r="I225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -11998,7 +11993,7 @@
         <v>5</v>
       </c>
       <c r="I226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -12027,7 +12022,7 @@
         <v>5</v>
       </c>
       <c r="I227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -12056,7 +12051,7 @@
         <v>5</v>
       </c>
       <c r="I228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -12085,7 +12080,7 @@
         <v>5</v>
       </c>
       <c r="I229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -12114,7 +12109,7 @@
         <v>5</v>
       </c>
       <c r="I230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -12143,7 +12138,7 @@
         <v>5</v>
       </c>
       <c r="I231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:9">
@@ -12172,7 +12167,7 @@
         <v>5</v>
       </c>
       <c r="I232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:9">
@@ -12201,7 +12196,7 @@
         <v>5</v>
       </c>
       <c r="I233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -12230,7 +12225,7 @@
         <v>5</v>
       </c>
       <c r="I234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -12259,7 +12254,7 @@
         <v>5</v>
       </c>
       <c r="I235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -12288,7 +12283,7 @@
         <v>5</v>
       </c>
       <c r="I236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -12317,7 +12312,7 @@
         <v>5</v>
       </c>
       <c r="I237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:9">
@@ -12346,7 +12341,7 @@
         <v>5</v>
       </c>
       <c r="I238" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -12375,7 +12370,7 @@
         <v>5</v>
       </c>
       <c r="I239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -12404,7 +12399,7 @@
         <v>5</v>
       </c>
       <c r="I240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -12433,7 +12428,7 @@
         <v>5</v>
       </c>
       <c r="I241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -12462,7 +12457,7 @@
         <v>5</v>
       </c>
       <c r="I242" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -12491,7 +12486,7 @@
         <v>5</v>
       </c>
       <c r="I243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -12520,7 +12515,7 @@
         <v>5</v>
       </c>
       <c r="I244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -12549,7 +12544,7 @@
         <v>5</v>
       </c>
       <c r="I245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -12578,7 +12573,7 @@
         <v>5</v>
       </c>
       <c r="I246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -12607,7 +12602,7 @@
         <v>5</v>
       </c>
       <c r="I247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -12636,7 +12631,7 @@
         <v>5</v>
       </c>
       <c r="I248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -12665,7 +12660,7 @@
         <v>5</v>
       </c>
       <c r="I249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:9">
@@ -12694,7 +12689,7 @@
         <v>5</v>
       </c>
       <c r="I250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -12723,7 +12718,7 @@
         <v>5</v>
       </c>
       <c r="I251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -12752,7 +12747,7 @@
         <v>5</v>
       </c>
       <c r="I252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -12781,7 +12776,7 @@
         <v>5</v>
       </c>
       <c r="I253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -12810,7 +12805,7 @@
         <v>5</v>
       </c>
       <c r="I254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -12839,7 +12834,7 @@
         <v>5</v>
       </c>
       <c r="I255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -12868,7 +12863,7 @@
         <v>5</v>
       </c>
       <c r="I256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -12897,7 +12892,7 @@
         <v>5</v>
       </c>
       <c r="I257" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -12926,7 +12921,7 @@
         <v>5</v>
       </c>
       <c r="I258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -12955,7 +12950,7 @@
         <v>5</v>
       </c>
       <c r="I259" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -12984,7 +12979,7 @@
         <v>5</v>
       </c>
       <c r="I260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -13013,7 +13008,7 @@
         <v>5</v>
       </c>
       <c r="I261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -13042,7 +13037,7 @@
         <v>5</v>
       </c>
       <c r="I262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:9">
@@ -13071,7 +13066,7 @@
         <v>5</v>
       </c>
       <c r="I263" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264" spans="1:9">
@@ -13100,7 +13095,7 @@
         <v>5</v>
       </c>
       <c r="I264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265" spans="1:9">
@@ -13129,7 +13124,7 @@
         <v>5</v>
       </c>
       <c r="I265" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -13158,7 +13153,7 @@
         <v>5</v>
       </c>
       <c r="I266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267" spans="1:9">
@@ -13187,7 +13182,7 @@
         <v>5</v>
       </c>
       <c r="I267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268" spans="1:9">
@@ -13216,7 +13211,7 @@
         <v>5</v>
       </c>
       <c r="I268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269" spans="1:9">
@@ -13245,7 +13240,7 @@
         <v>5</v>
       </c>
       <c r="I269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -13274,7 +13269,7 @@
         <v>5</v>
       </c>
       <c r="I270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -13303,7 +13298,7 @@
         <v>5</v>
       </c>
       <c r="I271" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:9">
@@ -13332,7 +13327,7 @@
         <v>5</v>
       </c>
       <c r="I272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273" spans="1:9">
@@ -13361,7 +13356,7 @@
         <v>5</v>
       </c>
       <c r="I273" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274" spans="1:9">
@@ -13390,7 +13385,7 @@
         <v>5</v>
       </c>
       <c r="I274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275" spans="1:9">
@@ -13419,7 +13414,7 @@
         <v>5</v>
       </c>
       <c r="I275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:9">
@@ -13448,7 +13443,7 @@
         <v>5</v>
       </c>
       <c r="I276" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277" spans="1:9">
@@ -13477,7 +13472,7 @@
         <v>5</v>
       </c>
       <c r="I277" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278" spans="1:9">
@@ -13506,7 +13501,7 @@
         <v>5</v>
       </c>
       <c r="I278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:9">
@@ -13535,7 +13530,7 @@
         <v>5</v>
       </c>
       <c r="I279" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280" spans="1:9">
@@ -13564,7 +13559,7 @@
         <v>5</v>
       </c>
       <c r="I280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281" spans="1:9">
@@ -13593,7 +13588,7 @@
         <v>5</v>
       </c>
       <c r="I281" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282" spans="1:9">

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500"/>
+    <workbookView windowWidth="20490" windowHeight="6780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4099" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="1095">
   <si>
     <t>Topic</t>
   </si>
@@ -4298,7 +4298,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J601"/>
+  <dimension ref="A1:J602"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
@@ -21750,6 +21750,35 @@
         <v>0</v>
       </c>
     </row>
+    <row r="602" spans="1:9">
+      <c r="A602" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B602" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C602" t="s">
+        <v>797</v>
+      </c>
+      <c r="D602" t="s">
+        <v>796</v>
+      </c>
+      <c r="E602" t="s">
+        <v>797</v>
+      </c>
+      <c r="F602" t="s">
+        <v>795</v>
+      </c>
+      <c r="G602" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H602">
+        <v>5</v>
+      </c>
+      <c r="I602" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6780"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="1095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="1329">
   <si>
     <t>Topic</t>
   </si>
@@ -3312,6 +3312,708 @@
   </si>
   <si>
     <t>Which player is Jalen Hurts?</t>
+  </si>
+  <si>
+    <t>Bible</t>
+  </si>
+  <si>
+    <t>Who built the ark?</t>
+  </si>
+  <si>
+    <t>Noah</t>
+  </si>
+  <si>
+    <t>Moses</t>
+  </si>
+  <si>
+    <t>Abraham</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Who was the first man created by God?</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t>Who was the first woman?</t>
+  </si>
+  <si>
+    <t>Eve</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>Ruth</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Who defeated Goliath?</t>
+  </si>
+  <si>
+    <t>Samson</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Who led Israelites out of Egypt?</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>Who was swallowed by a big fish?</t>
+  </si>
+  <si>
+    <t>Jonah</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Who was born in Bethlehem?</t>
+  </si>
+  <si>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>Who betrayed Jesus?</t>
+  </si>
+  <si>
+    <t>Judas</t>
+  </si>
+  <si>
+    <t>How many disciples did Jesus have?</t>
+  </si>
+  <si>
+    <t>What was the first book of Bible?</t>
+  </si>
+  <si>
+    <t>Genesis</t>
+  </si>
+  <si>
+    <t>Exodus</t>
+  </si>
+  <si>
+    <t>Psalms</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>Who killed Abel?</t>
+  </si>
+  <si>
+    <t>Cain</t>
+  </si>
+  <si>
+    <t>Saul</t>
+  </si>
+  <si>
+    <t>Who received Ten Commandments?</t>
+  </si>
+  <si>
+    <t>What sea did Moses part?</t>
+  </si>
+  <si>
+    <t>Red Sea</t>
+  </si>
+  <si>
+    <t>Dead Sea</t>
+  </si>
+  <si>
+    <t>Galilee</t>
+  </si>
+  <si>
+    <t>Mediterranean</t>
+  </si>
+  <si>
+    <t>Who was strongest man in Bible?</t>
+  </si>
+  <si>
+    <t>Who was thrown into lion’s den?</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Who interpreted dreams in Egypt?</t>
+  </si>
+  <si>
+    <t>Elijah</t>
+  </si>
+  <si>
+    <t>Who denied Jesus three times?</t>
+  </si>
+  <si>
+    <t>Who was mother of Jesus?</t>
+  </si>
+  <si>
+    <t>Who baptized Jesus?</t>
+  </si>
+  <si>
+    <t>John the Baptist</t>
+  </si>
+  <si>
+    <t>Where was Jesus born?</t>
+  </si>
+  <si>
+    <t>Bethlehem</t>
+  </si>
+  <si>
+    <t>Nazareth</t>
+  </si>
+  <si>
+    <t>Jerusalem</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>Who was first king of Israel?</t>
+  </si>
+  <si>
+    <t>Solomon</t>
+  </si>
+  <si>
+    <t>Who built the temple in Jerusalem?</t>
+  </si>
+  <si>
+    <t>What is shortest verse in Bible?</t>
+  </si>
+  <si>
+    <t>Jesus wept</t>
+  </si>
+  <si>
+    <t>Pray always</t>
+  </si>
+  <si>
+    <t>Hallelujah</t>
+  </si>
+  <si>
+    <t>Amen</t>
+  </si>
+  <si>
+    <t>Who walked on water with Jesus?</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Who was known for wisdom?</t>
+  </si>
+  <si>
+    <t>Who was father of Isaac?</t>
+  </si>
+  <si>
+    <t>Who was wife of Adam?</t>
+  </si>
+  <si>
+    <t>Rachel</t>
+  </si>
+  <si>
+    <t>What fruit did Adam and Eve eat?</t>
+  </si>
+  <si>
+    <t>Forbidden fruit</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Grapes</t>
+  </si>
+  <si>
+    <t>Fig</t>
+  </si>
+  <si>
+    <t>Who was giant defeated by David?</t>
+  </si>
+  <si>
+    <t>Goliath</t>
+  </si>
+  <si>
+    <t>Who survived flood in ark?</t>
+  </si>
+  <si>
+    <t>Who was Jesus’ earthly father?</t>
+  </si>
+  <si>
+    <t>Who was brother of Moses?</t>
+  </si>
+  <si>
+    <t>Aaron</t>
+  </si>
+  <si>
+    <t>Who was famous tax collector disciple?</t>
+  </si>
+  <si>
+    <t>Who doubted Jesus’ resurrection?</t>
+  </si>
+  <si>
+    <t>What city fell after trumpets blew?</t>
+  </si>
+  <si>
+    <t>Jericho</t>
+  </si>
+  <si>
+    <t>Babylon</t>
+  </si>
+  <si>
+    <t>Who stayed faithful in lion’s den?</t>
+  </si>
+  <si>
+    <t>Who was first murderer in Bible?</t>
+  </si>
+  <si>
+    <t>What garden did Adam and Eve live in?</t>
+  </si>
+  <si>
+    <t>Eden</t>
+  </si>
+  <si>
+    <t>Gethsemane</t>
+  </si>
+  <si>
+    <t>Who wrote many Psalms?</t>
+  </si>
+  <si>
+    <t>Who was thrown into fiery furnace?</t>
+  </si>
+  <si>
+    <t>Shadrach Meshach Abednego</t>
+  </si>
+  <si>
+    <t>Who climbed tree to see Jesus?</t>
+  </si>
+  <si>
+    <t>Zacchaeus</t>
+  </si>
+  <si>
+    <t>What animal spoke to Balaam?</t>
+  </si>
+  <si>
+    <t>Donkey</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>Lion</t>
+  </si>
+  <si>
+    <t>Who was first Christian martyr?</t>
+  </si>
+  <si>
+    <t>Stephen</t>
+  </si>
+  <si>
+    <t>What river was Jesus baptized in?</t>
+  </si>
+  <si>
+    <t>Nile</t>
+  </si>
+  <si>
+    <t>Euphrates</t>
+  </si>
+  <si>
+    <t>Who betrayed Jesus with a kiss?</t>
+  </si>
+  <si>
+    <t>Who was wisest king in Bible?</t>
+  </si>
+  <si>
+    <t>Who saw ladder reaching heaven?</t>
+  </si>
+  <si>
+    <t>Jacob</t>
+  </si>
+  <si>
+    <t>Who was sold by brothers into Egypt?</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>Reuben</t>
+  </si>
+  <si>
+    <t>Isaac</t>
+  </si>
+  <si>
+    <t>Who was oldest man in Bible?</t>
+  </si>
+  <si>
+    <t>Methuselah</t>
+  </si>
+  <si>
+    <t>What was Jesus’ profession before ministry?</t>
+  </si>
+  <si>
+    <t>Carpenter</t>
+  </si>
+  <si>
+    <t>Fisherman</t>
+  </si>
+  <si>
+    <t>Teacher</t>
+  </si>
+  <si>
+    <t>Shepherd</t>
+  </si>
+  <si>
+    <t>What city was Jesus born in?</t>
+  </si>
+  <si>
+    <t>Rome</t>
+  </si>
+  <si>
+    <t>King</t>
+  </si>
+  <si>
+    <t>What sea did Jesus walk on?</t>
+  </si>
+  <si>
+    <t>Who visited Jesus after His birth?</t>
+  </si>
+  <si>
+    <t>Shepherds</t>
+  </si>
+  <si>
+    <t>Soldiers</t>
+  </si>
+  <si>
+    <t>Priests</t>
+  </si>
+  <si>
+    <t>What gift did wise men bring?</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>Who was Roman governor during Jesus’ trial?</t>
+  </si>
+  <si>
+    <t>Pilate</t>
+  </si>
+  <si>
+    <t>Herod</t>
+  </si>
+  <si>
+    <t>Caesar</t>
+  </si>
+  <si>
+    <t>Nero</t>
+  </si>
+  <si>
+    <t>What town did Jesus grow up in?</t>
+  </si>
+  <si>
+    <t>What miracle did Jesus perform at wedding?</t>
+  </si>
+  <si>
+    <t>Turned water into wine</t>
+  </si>
+  <si>
+    <t>Healed blind</t>
+  </si>
+  <si>
+    <t>Walked on water</t>
+  </si>
+  <si>
+    <t>Fed crowd</t>
+  </si>
+  <si>
+    <t>Who was Jesus’ cousin?</t>
+  </si>
+  <si>
+    <t>What day did Jesus rise again?</t>
+  </si>
+  <si>
+    <t>Third day</t>
+  </si>
+  <si>
+    <t>Second day</t>
+  </si>
+  <si>
+    <t>Fifth day</t>
+  </si>
+  <si>
+    <t>Seventh day</t>
+  </si>
+  <si>
+    <t>Who rolled away the stone from tomb?</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>Who found empty tomb first?</t>
+  </si>
+  <si>
+    <t>Mary Magdalene</t>
+  </si>
+  <si>
+    <t>Martha</t>
+  </si>
+  <si>
+    <t>What animal did Jesus ride into Jerusalem?</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>What prayer did Jesus teach?</t>
+  </si>
+  <si>
+    <t>Lord’s Prayer</t>
+  </si>
+  <si>
+    <t>Psalm 23</t>
+  </si>
+  <si>
+    <t>Hail Mary</t>
+  </si>
+  <si>
+    <t>Blessing Prayer</t>
+  </si>
+  <si>
+    <t>What is Jesus called in Christianity?</t>
+  </si>
+  <si>
+    <t>Son of God</t>
+  </si>
+  <si>
+    <t>Prophet</t>
+  </si>
+  <si>
+    <t>King only</t>
+  </si>
+  <si>
+    <t>Who was tax collector disciple?</t>
+  </si>
+  <si>
+    <t>What miracle involved five loaves and two fish?</t>
+  </si>
+  <si>
+    <t>Fed 5000</t>
+  </si>
+  <si>
+    <t>Raised Lazarus</t>
+  </si>
+  <si>
+    <t>Who did Jesus raise from dead?</t>
+  </si>
+  <si>
+    <t>Lazarus</t>
+  </si>
+  <si>
+    <t>What garden did Jesus pray in before arrest?</t>
+  </si>
+  <si>
+    <t>Who kissed Jesus to identify Him?</t>
+  </si>
+  <si>
+    <t>What crown was placed on Jesus?</t>
+  </si>
+  <si>
+    <t>Thorns</t>
+  </si>
+  <si>
+    <t>Flowers</t>
+  </si>
+  <si>
+    <t>What was written on Jesus’ cross?</t>
+  </si>
+  <si>
+    <t>King of the Jews</t>
+  </si>
+  <si>
+    <t>Messiah</t>
+  </si>
+  <si>
+    <t>Savior</t>
+  </si>
+  <si>
+    <t>Who carried Jesus’ cross?</t>
+  </si>
+  <si>
+    <t>Simon of Cyrene</t>
+  </si>
+  <si>
+    <t>How many days did Jesus fast in wilderness?</t>
+  </si>
+  <si>
+    <t>Who tempted Jesus in wilderness?</t>
+  </si>
+  <si>
+    <t>Satan</t>
+  </si>
+  <si>
+    <t>What was Jesus’ first miracle?</t>
+  </si>
+  <si>
+    <t>Turning water into wine</t>
+  </si>
+  <si>
+    <t>Healing blind</t>
+  </si>
+  <si>
+    <t>Walking on water</t>
+  </si>
+  <si>
+    <t>Feeding crowd</t>
+  </si>
+  <si>
+    <t>What language did Jesus likely speak?</t>
+  </si>
+  <si>
+    <t>Aramaic</t>
+  </si>
+  <si>
+    <t>Hebrew</t>
+  </si>
+  <si>
+    <t>Greek</t>
+  </si>
+  <si>
+    <t>Latin</t>
+  </si>
+  <si>
+    <t>What disciple walked on water briefly?</t>
+  </si>
+  <si>
+    <t>Who washed Jesus’ feet with tears?</t>
+  </si>
+  <si>
+    <t>What mountain gave famous sermon?</t>
+  </si>
+  <si>
+    <t>Mount of Beatitudes</t>
+  </si>
+  <si>
+    <t>Sinai</t>
+  </si>
+  <si>
+    <t>Carmel</t>
+  </si>
+  <si>
+    <t>What did Jesus calm during storm?</t>
+  </si>
+  <si>
+    <t>Sea</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Earthquake</t>
+  </si>
+  <si>
+    <t>Windmill</t>
+  </si>
+  <si>
+    <t>What food did Jesus multiply?</t>
+  </si>
+  <si>
+    <t>Bread and fish</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Rice</t>
+  </si>
+  <si>
+    <t>Honey</t>
+  </si>
+  <si>
+    <t>What disciple betrayed Jesus?</t>
+  </si>
+  <si>
+    <t>What disciple was fisherman?</t>
+  </si>
+  <si>
+    <t>Luke</t>
+  </si>
+  <si>
+    <t>Who said “Let the little children come to me”?</t>
+  </si>
+  <si>
+    <t>What did Jesus use at Last Supper?</t>
+  </si>
+  <si>
+    <t>Bread and wine</t>
+  </si>
+  <si>
+    <t>Fish</t>
+  </si>
+  <si>
+    <t>Who prepared way for Jesus?</t>
+  </si>
+  <si>
+    <t>How old was Jesus when ministry began?</t>
+  </si>
+  <si>
+    <t>What did Jesus say greatest commandment was?</t>
+  </si>
+  <si>
+    <t>Love God</t>
+  </si>
+  <si>
+    <t>Love money</t>
+  </si>
+  <si>
+    <t>Build temple</t>
+  </si>
+  <si>
+    <t>Fast daily</t>
+  </si>
+  <si>
+    <t>Who was released instead of Jesus?</t>
+  </si>
+  <si>
+    <t>Barabbas</t>
+  </si>
+  <si>
+    <t>What happened after Jesus rose again?</t>
+  </si>
+  <si>
+    <t>Ascended to heaven</t>
+  </si>
+  <si>
+    <t>Stayed on Earth</t>
+  </si>
+  <si>
+    <t>Became king</t>
+  </si>
+  <si>
+    <t>Went to Rome</t>
   </si>
 </sst>
 </file>
@@ -4298,7 +5000,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J602"/>
+  <dimension ref="A1:J702"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
@@ -21779,6 +22481,2906 @@
         <v>0</v>
       </c>
     </row>
+    <row r="603" spans="1:9">
+      <c r="A603" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B603" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C603" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D603" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E603" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F603" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G603" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H603">
+        <v>5</v>
+      </c>
+      <c r="I603" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604" spans="1:9">
+      <c r="A604" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C604" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D604" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E604" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F604" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G604" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H604">
+        <v>5</v>
+      </c>
+      <c r="I604" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9">
+      <c r="A605" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C605" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D605" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E605" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F605" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G605" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H605">
+        <v>5</v>
+      </c>
+      <c r="I605" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:9">
+      <c r="A606" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B606" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C606" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D606" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E606" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F606" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G606" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H606">
+        <v>5</v>
+      </c>
+      <c r="I606" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:9">
+      <c r="A607" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B607" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C607" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D607" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E607" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F607" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G607" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H607">
+        <v>5</v>
+      </c>
+      <c r="I607" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608" spans="1:9">
+      <c r="A608" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B608" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C608" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D608" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E608" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F608" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G608" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H608">
+        <v>5</v>
+      </c>
+      <c r="I608" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609" spans="1:9">
+      <c r="A609" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B609" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C609" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D609" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E609" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F609" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G609" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H609">
+        <v>5</v>
+      </c>
+      <c r="I609" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610" spans="1:9">
+      <c r="A610" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B610" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C610" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D610" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E610" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F610" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G610" t="s">
+        <v>232</v>
+      </c>
+      <c r="H610">
+        <v>5</v>
+      </c>
+      <c r="I610" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611" spans="1:9">
+      <c r="A611" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B611" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C611">
+        <v>12</v>
+      </c>
+      <c r="D611">
+        <v>10</v>
+      </c>
+      <c r="E611">
+        <v>12</v>
+      </c>
+      <c r="F611">
+        <v>7</v>
+      </c>
+      <c r="G611">
+        <v>15</v>
+      </c>
+      <c r="H611">
+        <v>5</v>
+      </c>
+      <c r="I611" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612" spans="1:9">
+      <c r="A612" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B612" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C612" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D612" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E612" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F612" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G612" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H612">
+        <v>5</v>
+      </c>
+      <c r="I612" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613" spans="1:9">
+      <c r="A613" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B613" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C613" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D613" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E613" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F613" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G613" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H613">
+        <v>5</v>
+      </c>
+      <c r="I613" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614" spans="1:9">
+      <c r="A614" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B614" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C614" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D614" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E614" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F614" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G614" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H614">
+        <v>5</v>
+      </c>
+      <c r="I614" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615" spans="1:9">
+      <c r="A615" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B615" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C615" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D615" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E615" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F615" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G615" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H615">
+        <v>5</v>
+      </c>
+      <c r="I615" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616" spans="1:9">
+      <c r="A616" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B616" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C616" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D616" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E616" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F616" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G616" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H616">
+        <v>5</v>
+      </c>
+      <c r="I616" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617" spans="1:9">
+      <c r="A617" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B617" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C617" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D617" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E617" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F617" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G617" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H617">
+        <v>5</v>
+      </c>
+      <c r="I617" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:9">
+      <c r="A618" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B618" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C618" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D618" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E618" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F618" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G618" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H618">
+        <v>5</v>
+      </c>
+      <c r="I618" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619" spans="1:9">
+      <c r="A619" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B619" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C619" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D619" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E619" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F619" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G619" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H619">
+        <v>5</v>
+      </c>
+      <c r="I619" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:9">
+      <c r="A620" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B620" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C620" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D620" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E620" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F620" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G620" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H620">
+        <v>5</v>
+      </c>
+      <c r="I620" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621" spans="1:9">
+      <c r="A621" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B621" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C621" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D621" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E621" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F621" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G621" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H621">
+        <v>5</v>
+      </c>
+      <c r="I621" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622" spans="1:9">
+      <c r="A622" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B622" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C622" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D622" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E622" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F622" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G622" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H622">
+        <v>5</v>
+      </c>
+      <c r="I622" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623" spans="1:9">
+      <c r="A623" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B623" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C623" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D623" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E623" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F623" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G623" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H623">
+        <v>5</v>
+      </c>
+      <c r="I623" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624" spans="1:9">
+      <c r="A624" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B624" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C624" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D624" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E624" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F624" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G624" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H624">
+        <v>5</v>
+      </c>
+      <c r="I624" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625" spans="1:9">
+      <c r="A625" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B625" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C625" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D625" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E625" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F625" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G625" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H625">
+        <v>5</v>
+      </c>
+      <c r="I625" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626" spans="1:9">
+      <c r="A626" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B626" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C626" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D626" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E626" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F626" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G626" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H626">
+        <v>5</v>
+      </c>
+      <c r="I626" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627" spans="1:9">
+      <c r="A627" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B627" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C627" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D627" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E627" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F627" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G627" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H627">
+        <v>5</v>
+      </c>
+      <c r="I627" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628" spans="1:9">
+      <c r="A628" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B628" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C628" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D628" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E628" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F628" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G628" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H628">
+        <v>5</v>
+      </c>
+      <c r="I628" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629" spans="1:9">
+      <c r="A629" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C629" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D629" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E629" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F629" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G629" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H629">
+        <v>5</v>
+      </c>
+      <c r="I629" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630" spans="1:9">
+      <c r="A630" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B630" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C630" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D630" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E630" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F630" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G630" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H630">
+        <v>5</v>
+      </c>
+      <c r="I630" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631" spans="1:9">
+      <c r="A631" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B631" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C631" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D631" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E631" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F631" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G631" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H631">
+        <v>5</v>
+      </c>
+      <c r="I631" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632" spans="1:9">
+      <c r="A632" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B632" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C632" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D632" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E632" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F632" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G632" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H632">
+        <v>5</v>
+      </c>
+      <c r="I632" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633" spans="1:9">
+      <c r="A633" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C633" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D633" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E633" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F633" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G633" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H633">
+        <v>5</v>
+      </c>
+      <c r="I633" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634" spans="1:9">
+      <c r="A634" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B634" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C634" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D634" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E634" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F634" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G634" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H634">
+        <v>5</v>
+      </c>
+      <c r="I634" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635" spans="1:9">
+      <c r="A635" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B635" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C635" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D635" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E635" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F635" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G635" t="s">
+        <v>232</v>
+      </c>
+      <c r="H635">
+        <v>5</v>
+      </c>
+      <c r="I635" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636" spans="1:9">
+      <c r="A636" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B636" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C636" t="s">
+        <v>232</v>
+      </c>
+      <c r="D636" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E636" t="s">
+        <v>232</v>
+      </c>
+      <c r="F636" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G636" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H636">
+        <v>5</v>
+      </c>
+      <c r="I636" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637" spans="1:9">
+      <c r="A637" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C637" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D637" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E637" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F637" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G637" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H637">
+        <v>5</v>
+      </c>
+      <c r="I637" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:9">
+      <c r="A638" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B638" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C638" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D638" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E638" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F638" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G638" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H638">
+        <v>5</v>
+      </c>
+      <c r="I638" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639" spans="1:9">
+      <c r="A639" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B639" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C639" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D639" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E639" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F639" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G639" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H639">
+        <v>5</v>
+      </c>
+      <c r="I639" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640" spans="1:9">
+      <c r="A640" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B640" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C640" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D640" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E640" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F640" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G640" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H640">
+        <v>5</v>
+      </c>
+      <c r="I640" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641" spans="1:9">
+      <c r="A641" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B641" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C641" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D641" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E641" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F641" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G641" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H641">
+        <v>5</v>
+      </c>
+      <c r="I641" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642" spans="1:9">
+      <c r="A642" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B642" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C642" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D642" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E642" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F642" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G642" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H642">
+        <v>5</v>
+      </c>
+      <c r="I642" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643" spans="1:9">
+      <c r="A643" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B643" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C643" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D643" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E643" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F643" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G643" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H643">
+        <v>5</v>
+      </c>
+      <c r="I643" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644" spans="1:9">
+      <c r="A644" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B644" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C644" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D644" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E644" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F644" t="s">
+        <v>1194</v>
+      </c>
+      <c r="G644" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H644">
+        <v>5</v>
+      </c>
+      <c r="I644" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645" spans="1:9">
+      <c r="A645" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B645" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C645" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D645" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E645" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F645" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G645" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H645">
+        <v>5</v>
+      </c>
+      <c r="I645" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646" spans="1:9">
+      <c r="A646" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B646" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C646" t="s">
+        <v>930</v>
+      </c>
+      <c r="D646" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E646" t="s">
+        <v>930</v>
+      </c>
+      <c r="F646" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G646" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H646">
+        <v>5</v>
+      </c>
+      <c r="I646" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647" spans="1:9">
+      <c r="A647" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C647" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D647" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E647" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F647" t="s">
+        <v>232</v>
+      </c>
+      <c r="G647" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H647">
+        <v>5</v>
+      </c>
+      <c r="I647" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="648" spans="1:9">
+      <c r="A648" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B648" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C648" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D648" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E648" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F648" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G648" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H648">
+        <v>5</v>
+      </c>
+      <c r="I648" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="649" spans="1:9">
+      <c r="A649" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B649" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C649" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D649" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E649" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F649" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G649" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H649">
+        <v>5</v>
+      </c>
+      <c r="I649" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="650" spans="1:9">
+      <c r="A650" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B650" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C650" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D650" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E650" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F650" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G650" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H650">
+        <v>5</v>
+      </c>
+      <c r="I650" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="1:9">
+      <c r="A651" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B651" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C651" t="s">
+        <v>1210</v>
+      </c>
+      <c r="D651" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E651" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F651" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G651" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H651">
+        <v>5</v>
+      </c>
+      <c r="I651" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="652" spans="1:9">
+      <c r="A652" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B652" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C652" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D652" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E652" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F652" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G652" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H652">
+        <v>5</v>
+      </c>
+      <c r="I652" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="653" spans="1:9">
+      <c r="A653" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B653" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C653" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D653" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E653" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F653" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G653" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H653">
+        <v>5</v>
+      </c>
+      <c r="I653" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="1:9">
+      <c r="A654" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B654" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C654" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D654" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E654" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F654" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G654" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H654">
+        <v>5</v>
+      </c>
+      <c r="I654" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="655" spans="1:9">
+      <c r="A655" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B655" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C655" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D655" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E655" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F655" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G655" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H655">
+        <v>5</v>
+      </c>
+      <c r="I655" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="656" spans="1:9">
+      <c r="A656" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B656" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C656" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D656" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E656" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F656" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G656" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H656">
+        <v>5</v>
+      </c>
+      <c r="I656" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="1:9">
+      <c r="A657" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B657" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C657">
+        <v>12</v>
+      </c>
+      <c r="D657">
+        <v>10</v>
+      </c>
+      <c r="E657">
+        <v>12</v>
+      </c>
+      <c r="F657">
+        <v>7</v>
+      </c>
+      <c r="G657">
+        <v>15</v>
+      </c>
+      <c r="H657">
+        <v>5</v>
+      </c>
+      <c r="I657" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="658" spans="1:9">
+      <c r="A658" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B658" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C658" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D658" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E658" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F658" t="s">
+        <v>232</v>
+      </c>
+      <c r="G658" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H658">
+        <v>5</v>
+      </c>
+      <c r="I658" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="659" spans="1:9">
+      <c r="A659" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B659" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C659" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D659" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E659" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F659" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G659" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H659">
+        <v>5</v>
+      </c>
+      <c r="I659" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="660" spans="1:9">
+      <c r="A660" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B660" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C660" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D660" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E660" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F660" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G660" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H660">
+        <v>5</v>
+      </c>
+      <c r="I660" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:9">
+      <c r="A661" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B661" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C661" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D661" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E661" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F661" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G661" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H661">
+        <v>5</v>
+      </c>
+      <c r="I661" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="662" spans="1:9">
+      <c r="A662" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B662" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C662" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D662" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E662" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F662" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G662" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H662">
+        <v>5</v>
+      </c>
+      <c r="I662" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="663" spans="1:9">
+      <c r="A663" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B663" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C663" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D663" t="s">
+        <v>910</v>
+      </c>
+      <c r="E663" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F663" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G663" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H663">
+        <v>5</v>
+      </c>
+      <c r="I663" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="664" spans="1:9">
+      <c r="A664" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B664" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C664" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D664" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E664" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F664" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G664" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H664">
+        <v>5</v>
+      </c>
+      <c r="I664" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="665" spans="1:9">
+      <c r="A665" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B665" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C665" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D665" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E665" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F665" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G665" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H665">
+        <v>5</v>
+      </c>
+      <c r="I665" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="666" spans="1:9">
+      <c r="A666" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B666" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C666" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D666" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E666" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F666" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G666" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H666">
+        <v>5</v>
+      </c>
+      <c r="I666" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="667" spans="1:9">
+      <c r="A667" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B667" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C667" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D667" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E667" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F667" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G667" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H667">
+        <v>5</v>
+      </c>
+      <c r="I667" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="668" spans="1:9">
+      <c r="A668" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B668" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C668" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D668" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E668" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F668" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G668" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H668">
+        <v>5</v>
+      </c>
+      <c r="I668" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="669" spans="1:9">
+      <c r="A669" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B669" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C669" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D669" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E669" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F669" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G669" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H669">
+        <v>5</v>
+      </c>
+      <c r="I669" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="670" spans="1:9">
+      <c r="A670" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B670" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C670" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D670" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E670" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F670" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G670" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H670">
+        <v>5</v>
+      </c>
+      <c r="I670" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="671" spans="1:9">
+      <c r="A671" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B671" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C671" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D671" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E671" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F671" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G671" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H671">
+        <v>5</v>
+      </c>
+      <c r="I671" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="672" spans="1:9">
+      <c r="A672" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C672" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D672" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E672" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F672" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G672" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H672">
+        <v>5</v>
+      </c>
+      <c r="I672" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="673" spans="1:9">
+      <c r="A673" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B673" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C673" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D673" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E673" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F673" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G673" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H673">
+        <v>5</v>
+      </c>
+      <c r="I673" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="674" spans="1:9">
+      <c r="A674" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B674" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C674" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D674" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E674" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F674" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G674" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H674">
+        <v>5</v>
+      </c>
+      <c r="I674" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="1:9">
+      <c r="A675" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B675" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C675" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D675" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E675" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F675" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G675" t="s">
+        <v>232</v>
+      </c>
+      <c r="H675">
+        <v>5</v>
+      </c>
+      <c r="I675" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="1:9">
+      <c r="A676" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B676" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C676" t="s">
+        <v>232</v>
+      </c>
+      <c r="D676" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E676" t="s">
+        <v>232</v>
+      </c>
+      <c r="F676" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G676" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H676">
+        <v>5</v>
+      </c>
+      <c r="I676" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677" spans="1:9">
+      <c r="A677" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B677" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C677" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D677" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E677" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F677" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G677" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H677">
+        <v>5</v>
+      </c>
+      <c r="I677" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="678" spans="1:9">
+      <c r="A678" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B678" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C678" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D678" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E678" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F678" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G678" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H678">
+        <v>5</v>
+      </c>
+      <c r="I678" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679" spans="1:9">
+      <c r="A679" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B679" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C679" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D679" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E679" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F679" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G679" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H679">
+        <v>5</v>
+      </c>
+      <c r="I679" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680" spans="1:9">
+      <c r="A680" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B680" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C680" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D680" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E680" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F680" t="s">
+        <v>232</v>
+      </c>
+      <c r="G680" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H680">
+        <v>5</v>
+      </c>
+      <c r="I680" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681" spans="1:9">
+      <c r="A681" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B681" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C681" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D681" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E681" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F681" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G681" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H681">
+        <v>5</v>
+      </c>
+      <c r="I681" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="682" spans="1:9">
+      <c r="A682" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B682" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C682" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D682" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E682" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F682" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G682" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H682">
+        <v>5</v>
+      </c>
+      <c r="I682" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="683" spans="1:9">
+      <c r="A683" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B683" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C683" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D683" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E683" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F683" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G683" t="s">
+        <v>232</v>
+      </c>
+      <c r="H683">
+        <v>5</v>
+      </c>
+      <c r="I683" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="684" spans="1:9">
+      <c r="A684" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B684" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C684">
+        <v>40</v>
+      </c>
+      <c r="D684">
+        <v>7</v>
+      </c>
+      <c r="E684">
+        <v>40</v>
+      </c>
+      <c r="F684">
+        <v>12</v>
+      </c>
+      <c r="G684">
+        <v>30</v>
+      </c>
+      <c r="H684">
+        <v>5</v>
+      </c>
+      <c r="I684" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="1:9">
+      <c r="A685" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B685" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C685" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D685" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E685" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F685" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G685" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H685">
+        <v>5</v>
+      </c>
+      <c r="I685" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="1:9">
+      <c r="A686" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B686" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C686" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D686" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E686" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F686" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G686" t="s">
+        <v>1286</v>
+      </c>
+      <c r="H686">
+        <v>5</v>
+      </c>
+      <c r="I686" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="1:9">
+      <c r="A687" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B687" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C687" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D687" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E687" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F687" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G687" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H687">
+        <v>5</v>
+      </c>
+      <c r="I687" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="688" spans="1:9">
+      <c r="A688" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B688" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C688" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D688" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E688" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F688" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G688" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H688">
+        <v>5</v>
+      </c>
+      <c r="I688" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689" spans="1:9">
+      <c r="A689" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B689" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C689" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D689" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E689" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F689" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G689" t="s">
+        <v>232</v>
+      </c>
+      <c r="H689">
+        <v>5</v>
+      </c>
+      <c r="I689" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="690" spans="1:9">
+      <c r="A690" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B690" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C690" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D690" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E690" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F690" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G690" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H690">
+        <v>5</v>
+      </c>
+      <c r="I690" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="1:9">
+      <c r="A691" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B691" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C691" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D691" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E691" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F691" t="s">
+        <v>940</v>
+      </c>
+      <c r="G691" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H691">
+        <v>5</v>
+      </c>
+      <c r="I691" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692" spans="1:9">
+      <c r="A692" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B692" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C692" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D692" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E692" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F692" t="s">
+        <v>1301</v>
+      </c>
+      <c r="G692" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H692">
+        <v>5</v>
+      </c>
+      <c r="I692" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693" spans="1:9">
+      <c r="A693" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B693" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C693" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D693" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E693" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F693" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G693" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H693">
+        <v>5</v>
+      </c>
+      <c r="I693" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="1:9">
+      <c r="A694" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B694" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C694" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D694" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E694" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F694" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G694" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H694">
+        <v>5</v>
+      </c>
+      <c r="I694" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="1:9">
+      <c r="A695" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B695" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C695" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D695" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E695" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F695" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G695" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H695">
+        <v>5</v>
+      </c>
+      <c r="I695" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696" spans="1:9">
+      <c r="A696" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B696" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C696" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D696" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E696" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F696" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G696" t="s">
+        <v>1098</v>
+      </c>
+      <c r="H696">
+        <v>5</v>
+      </c>
+      <c r="I696" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="697" spans="1:9">
+      <c r="A697" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B697" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C697" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D697" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E697" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F697" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G697" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H697">
+        <v>5</v>
+      </c>
+      <c r="I697" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:9">
+      <c r="A698" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B698" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C698" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D698" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E698" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F698" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G698" t="s">
+        <v>232</v>
+      </c>
+      <c r="H698">
+        <v>5</v>
+      </c>
+      <c r="I698" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="1:9">
+      <c r="A699" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B699" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C699">
+        <v>30</v>
+      </c>
+      <c r="D699">
+        <v>25</v>
+      </c>
+      <c r="E699">
+        <v>30</v>
+      </c>
+      <c r="F699">
+        <v>33</v>
+      </c>
+      <c r="G699">
+        <v>40</v>
+      </c>
+      <c r="H699">
+        <v>5</v>
+      </c>
+      <c r="I699" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700" spans="1:9">
+      <c r="A700" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B700" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C700" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D700" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E700" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F700" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G700" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H700">
+        <v>5</v>
+      </c>
+      <c r="I700" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="1:9">
+      <c r="A701" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B701" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C701" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D701" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E701" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F701" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G701" t="s">
+        <v>232</v>
+      </c>
+      <c r="H701">
+        <v>5</v>
+      </c>
+      <c r="I701" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="1:9">
+      <c r="A702" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B702" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C702" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D702" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E702" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F702" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G702" t="s">
+        <v>1328</v>
+      </c>
+      <c r="H702">
+        <v>5</v>
+      </c>
+      <c r="I702" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500"/>
+    <workbookView windowWidth="20490" windowHeight="6780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4786" uniqueCount="1329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4793" uniqueCount="1329">
   <si>
     <t>Topic</t>
   </si>
@@ -5000,7 +5000,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J702"/>
+  <dimension ref="A1:J703"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.2857142857143" customWidth="1"/>
@@ -25381,6 +25381,35 @@
         <v>0</v>
       </c>
     </row>
+    <row r="703" spans="1:9">
+      <c r="A703" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B703" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C703" t="s">
+        <v>795</v>
+      </c>
+      <c r="D703" t="s">
+        <v>797</v>
+      </c>
+      <c r="E703" t="s">
+        <v>795</v>
+      </c>
+      <c r="F703" t="s">
+        <v>796</v>
+      </c>
+      <c r="G703" t="s">
+        <v>798</v>
+      </c>
+      <c r="H703">
+        <v>5</v>
+      </c>
+      <c r="I703" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="339">
   <si>
     <t>Topic</t>
   </si>
@@ -56,777 +56,489 @@
     <t>Used</t>
   </si>
   <si>
-    <t>Bible</t>
-  </si>
-  <si>
-    <t>Who built the first altar to God after the flood?</t>
-  </si>
-  <si>
-    <t>Noah</t>
-  </si>
-  <si>
-    <t>Abraham</t>
+    <t>Jesus</t>
+  </si>
+  <si>
+    <t>What age was Jesus when He stayed behind in the temple?</t>
+  </si>
+  <si>
+    <t>Who recognized baby Jesus in the temple?</t>
+  </si>
+  <si>
+    <t>Simeon</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>Zechariah</t>
+  </si>
+  <si>
+    <t>Who prepared the way for Jesus?</t>
+  </si>
+  <si>
+    <t>John the Baptist</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>What was Jesus wrapped in after birth?</t>
+  </si>
+  <si>
+    <t>Swaddling cloths</t>
+  </si>
+  <si>
+    <t>Blanket</t>
+  </si>
+  <si>
+    <t>Silk</t>
+  </si>
+  <si>
+    <t>Leaves</t>
+  </si>
+  <si>
+    <t>Where did Jesus turn water into wine?</t>
+  </si>
+  <si>
+    <t>Cana</t>
+  </si>
+  <si>
+    <t>Bethlehem</t>
+  </si>
+  <si>
+    <t>Nazareth</t>
+  </si>
+  <si>
+    <t>Jerusalem</t>
+  </si>
+  <si>
+    <t>Who was the Roman ruler when Jesus was born?</t>
+  </si>
+  <si>
+    <t>Herod</t>
+  </si>
+  <si>
+    <t>Caesar</t>
+  </si>
+  <si>
+    <t>Pilate</t>
+  </si>
+  <si>
+    <t>Nero</t>
+  </si>
+  <si>
+    <t>What trade did Jesus likely learn from Joseph?</t>
+  </si>
+  <si>
+    <t>Carpentry</t>
+  </si>
+  <si>
+    <t>Fishing</t>
+  </si>
+  <si>
+    <t>Farming</t>
+  </si>
+  <si>
+    <t>Blacksmithing</t>
+  </si>
+  <si>
+    <t>How many baskets were left after feeding 5000?</t>
+  </si>
+  <si>
+    <t>Who climbed onto roof to lower sick man to Jesus?</t>
+  </si>
+  <si>
+    <t>Friends of paralytic</t>
+  </si>
+  <si>
+    <t>Disciples</t>
+  </si>
+  <si>
+    <t>Priests</t>
+  </si>
+  <si>
+    <t>Soldiers</t>
+  </si>
+  <si>
+    <t>What illness did Jesus heal by touching eyes?</t>
+  </si>
+  <si>
+    <t>Blindness</t>
+  </si>
+  <si>
+    <t>Fever</t>
+  </si>
+  <si>
+    <t>Leprosy</t>
+  </si>
+  <si>
+    <t>Paralysis</t>
+  </si>
+  <si>
+    <t>Who washed Jesus’ feet with expensive perfume?</t>
+  </si>
+  <si>
+    <t>Mary of Bethany</t>
+  </si>
+  <si>
+    <t>Martha</t>
+  </si>
+  <si>
+    <t>Ruth</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>What disciple was a tax collector?</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Who tried walking on water toward Jesus?</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>What did Jesus calm with His words?</t>
+  </si>
+  <si>
+    <t>Storm</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Earthquake</t>
+  </si>
+  <si>
+    <t>Flood</t>
+  </si>
+  <si>
+    <t>What bird descended during Jesus’ baptism?</t>
+  </si>
+  <si>
+    <t>Dove</t>
+  </si>
+  <si>
+    <t>Eagle</t>
+  </si>
+  <si>
+    <t>Sparrow</t>
+  </si>
+  <si>
+    <t>Raven</t>
+  </si>
+  <si>
+    <t>Who wanted Jesus crucified?</t>
+  </si>
+  <si>
+    <t>Crowd</t>
+  </si>
+  <si>
+    <t>Lazarus</t>
+  </si>
+  <si>
+    <t>What crown was forced onto Jesus’ head?</t>
+  </si>
+  <si>
+    <t>Crown of thorns</t>
+  </si>
+  <si>
+    <t>Gold crown</t>
+  </si>
+  <si>
+    <t>Silver crown</t>
+  </si>
+  <si>
+    <t>Flower crown</t>
+  </si>
+  <si>
+    <t>What was placed above Jesus on the cross?</t>
+  </si>
+  <si>
+    <t>King of the Jews</t>
+  </si>
+  <si>
+    <t>Savior</t>
+  </si>
+  <si>
+    <t>Messiah</t>
+  </si>
+  <si>
+    <t>Prophet</t>
+  </si>
+  <si>
+    <t>Who helped carry Jesus’ cross?</t>
+  </si>
+  <si>
+    <t>Simon of Cyrene</t>
+  </si>
+  <si>
+    <t>What happened in temple when Jesus died?</t>
+  </si>
+  <si>
+    <t>Curtain tore</t>
+  </si>
+  <si>
+    <t>Earth stopped</t>
+  </si>
+  <si>
+    <t>Fire appeared</t>
+  </si>
+  <si>
+    <t>Statues broke</t>
+  </si>
+  <si>
+    <t>Who buried Jesus in tomb?</t>
+  </si>
+  <si>
+    <t>Joseph of Arimathea</t>
+  </si>
+  <si>
+    <t>Nicodemus</t>
+  </si>
+  <si>
+    <t>Who came to Jesus at night to ask questions?</t>
+  </si>
+  <si>
+    <t>Who was raised from dead after four days?</t>
+  </si>
+  <si>
+    <t>Jairus</t>
+  </si>
+  <si>
+    <t>Stephen</t>
+  </si>
+  <si>
+    <t>What miracle happened at Sea of Galilee?</t>
+  </si>
+  <si>
+    <t>Jesus walked on water</t>
+  </si>
+  <si>
+    <t>Fish multiplied</t>
+  </si>
+  <si>
+    <t>Mountain moved</t>
+  </si>
+  <si>
+    <t>Boat vanished</t>
+  </si>
+  <si>
+    <t>Who doubted until touching Jesus’ wounds?</t>
+  </si>
+  <si>
+    <t>What did Jesus multiply for the crowd?</t>
+  </si>
+  <si>
+    <t>Bread and fish</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Honey</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>What prayer begins with “Our Father”?</t>
+  </si>
+  <si>
+    <t>Lord’s Prayer</t>
+  </si>
+  <si>
+    <t>Psalm 23</t>
+  </si>
+  <si>
+    <t>Holy Prayer</t>
+  </si>
+  <si>
+    <t>Morning Prayer</t>
+  </si>
+  <si>
+    <t>Who betrayed Jesus for silver coins?</t>
+  </si>
+  <si>
+    <t>Judas</t>
+  </si>
+  <si>
+    <t>How many silver coins betrayed Jesus?</t>
+  </si>
+  <si>
+    <t>Who cut off servant’s ear during arrest?</t>
+  </si>
+  <si>
+    <t>What miracle healed ten men at once?</t>
+  </si>
+  <si>
+    <t>Healing lepers</t>
+  </si>
+  <si>
+    <t>Raising dead</t>
+  </si>
+  <si>
+    <t>Walking on water</t>
+  </si>
+  <si>
+    <t>Blind healing</t>
+  </si>
+  <si>
+    <t>What did Jesus ride into Jerusalem?</t>
+  </si>
+  <si>
+    <t>Donkey</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>Chariot</t>
+  </si>
+  <si>
+    <t>Who denied knowing Jesus three times?</t>
+  </si>
+  <si>
+    <t>What garden did Jesus pray in before arrest?</t>
+  </si>
+  <si>
+    <t>Gethsemane</t>
+  </si>
+  <si>
+    <t>Eden</t>
+  </si>
+  <si>
+    <t>Who tempted Jesus in wilderness?</t>
+  </si>
+  <si>
+    <t>Satan</t>
+  </si>
+  <si>
+    <t>How many days did Jesus fast in wilderness?</t>
+  </si>
+  <si>
+    <t>What did Jesus say to calm the storm?</t>
+  </si>
+  <si>
+    <t>Peace be still</t>
+  </si>
+  <si>
+    <t>Be quiet</t>
+  </si>
+  <si>
+    <t>Stop now</t>
+  </si>
+  <si>
+    <t>Stay calm</t>
+  </si>
+  <si>
+    <t>Who touched Jesus’ robe and was healed?</t>
+  </si>
+  <si>
+    <t>Bleeding woman</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>Who climbed tree to see Jesus?</t>
+  </si>
+  <si>
+    <t>Zacchaeus</t>
+  </si>
+  <si>
+    <t>What did Jesus use to feed 5000?</t>
+  </si>
+  <si>
+    <t>5 loaves and 2 fish</t>
+  </si>
+  <si>
+    <t>7 loaves</t>
+  </si>
+  <si>
+    <t>3 fish</t>
+  </si>
+  <si>
+    <t>10 loaves</t>
+  </si>
+  <si>
+    <t>What disciple doubted Jesus’ resurrection?</t>
+  </si>
+  <si>
+    <t>What happened three days after crucifixion?</t>
+  </si>
+  <si>
+    <t>Resurrection</t>
+  </si>
+  <si>
+    <t>What city did Jesus grow up in?</t>
+  </si>
+  <si>
+    <t>Who announced Jesus’ birth to shepherds?</t>
+  </si>
+  <si>
+    <t>Angels</t>
+  </si>
+  <si>
+    <t>Prophets</t>
+  </si>
+  <si>
+    <t>Kings</t>
+  </si>
+  <si>
+    <t>What heavenly object guided wise men?</t>
+  </si>
+  <si>
+    <t>Star</t>
+  </si>
+  <si>
+    <t>Moon</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Comet</t>
+  </si>
+  <si>
+    <t>Who wanted to kill baby Jesus?</t>
+  </si>
+  <si>
+    <t>What disciple was brother of Peter?</t>
+  </si>
+  <si>
+    <t>Philip</t>
+  </si>
+  <si>
+    <t>What disciple was called beloved disciple?</t>
+  </si>
+  <si>
+    <t>Who said “Prepare the way of the Lord”?</t>
   </si>
   <si>
     <t>Moses</t>
   </si>
   <si>
-    <t>Isaac</t>
-  </si>
-  <si>
-    <t>Who was known as the father of many nations?</t>
-  </si>
-  <si>
-    <t>Jacob</t>
-  </si>
-  <si>
-    <t>Joseph</t>
-  </si>
-  <si>
-    <t>Who wrestled with an angel?</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Samson</t>
-  </si>
-  <si>
-    <t>Who interpreted King Nebuchadnezzar’s dreams?</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Elijah</t>
-  </si>
-  <si>
-    <t>Isaiah</t>
-  </si>
-  <si>
-    <t>Who became queen of Persia and saved the Jews?</t>
-  </si>
-  <si>
-    <t>Esther</t>
-  </si>
-  <si>
-    <t>Ruth</t>
-  </si>
-  <si>
-    <t>Mary</t>
-  </si>
-  <si>
-    <t>Deborah</t>
-  </si>
-  <si>
-    <t>Who was the mother of Samuel?</t>
-  </si>
-  <si>
-    <t>Hannah</t>
-  </si>
-  <si>
-    <t>Rachel</t>
-  </si>
-  <si>
-    <t>Leah</t>
-  </si>
-  <si>
-    <t>Sarah</t>
-  </si>
-  <si>
-    <t>Which disciple replaced Judas?</t>
-  </si>
-  <si>
-    <t>Matthias</t>
-  </si>
-  <si>
-    <t>Barnabas</t>
-  </si>
-  <si>
-    <t>Stephen</t>
-  </si>
-  <si>
-    <t>Luke</t>
-  </si>
-  <si>
-    <t>Who was blinded on the road to Damascus?</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>Peter</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>Who baptized the Ethiopian eunuch?</t>
-  </si>
-  <si>
-    <t>Philip</t>
-  </si>
-  <si>
-    <t>Who was thrown from a ship during a storm?</t>
-  </si>
-  <si>
-    <t>Jonah</t>
-  </si>
-  <si>
-    <t>Who interpreted Pharaoh’s dreams?</t>
-  </si>
-  <si>
-    <t>Aaron</t>
-  </si>
-  <si>
-    <t>Who led Israelites into Promised Land after Moses?</t>
-  </si>
-  <si>
-    <t>Joshua</t>
-  </si>
-  <si>
-    <t>Caleb</t>
-  </si>
-  <si>
-    <t>Samuel</t>
-  </si>
-  <si>
-    <t>Who destroyed walls of Jericho?</t>
-  </si>
-  <si>
-    <t>Gideon</t>
-  </si>
-  <si>
-    <t>Who was strongest judge of Israel?</t>
-  </si>
-  <si>
-    <t>Saul</t>
-  </si>
-  <si>
-    <t>Solomon</t>
-  </si>
-  <si>
-    <t>Who anointed David as king?</t>
-  </si>
-  <si>
-    <t>Nathan</t>
-  </si>
-  <si>
-    <t>Who survived being thrown into sea by sailors?</t>
-  </si>
-  <si>
-    <t>Who wrote most Proverbs?</t>
-  </si>
-  <si>
-    <t>Who prayed and fire came from heaven?</t>
-  </si>
-  <si>
-    <t>Elisha</t>
-  </si>
-  <si>
-    <t>Who succeeded Elijah as prophet?</t>
-  </si>
-  <si>
-    <t>Jeremiah</t>
-  </si>
-  <si>
-    <t>Ezekiel</t>
-  </si>
-  <si>
-    <t>Who killed a lion with bare hands?</t>
-  </si>
-  <si>
-    <t>Who found baby Moses in river?</t>
-  </si>
-  <si>
-    <t>Pharaoh’s daughter</t>
-  </si>
-  <si>
-    <t>Miriam</t>
-  </si>
-  <si>
-    <t>Who was swallowed by earth after rebellion?</t>
-  </si>
-  <si>
-    <t>Korah</t>
-  </si>
-  <si>
-    <t>Absalom</t>
-  </si>
-  <si>
-    <t>Ahab</t>
-  </si>
-  <si>
-    <t>Who asked for wisdom from God?</t>
-  </si>
-  <si>
-    <t>Who rebuilt Jerusalem’s walls?</t>
-  </si>
-  <si>
-    <t>Nehemiah</t>
-  </si>
-  <si>
-    <t>Ezra</t>
-  </si>
-  <si>
-    <t>Who was famous for patience during suffering?</t>
-  </si>
-  <si>
-    <t>Job</t>
-  </si>
-  <si>
-    <t>Who was sold for twenty pieces of silver?</t>
-  </si>
-  <si>
-    <t>Benjamin</t>
-  </si>
-  <si>
-    <t>Who climbed Mount Sinai with Moses?</t>
-  </si>
-  <si>
-    <t>Who cut off giant Goliath’s head?</t>
-  </si>
-  <si>
-    <t>Jonathan</t>
-  </si>
-  <si>
-    <t>Who was king before David?</t>
-  </si>
-  <si>
-    <t>Who saw dry bones come alive in vision?</t>
-  </si>
-  <si>
-    <t>Who built a huge boat before flood?</t>
-  </si>
-  <si>
-    <t>Who interpreted handwriting on wall?</t>
-  </si>
-  <si>
-    <t>Who became blind after seeing heavenly light?</t>
-  </si>
-  <si>
-    <t>Who was known as weeping prophet?</t>
-  </si>
-  <si>
-    <t>Who stayed with Naomi after famine?</t>
-  </si>
-  <si>
-    <t>Martha</t>
-  </si>
-  <si>
-    <t>Who was father of John the Baptist?</t>
-  </si>
-  <si>
-    <t>Zechariah</t>
-  </si>
-  <si>
-    <t>Who dreamed about ladder to heaven?</t>
-  </si>
-  <si>
-    <t>Who killed thousands with jawbone of donkey?</t>
-  </si>
-  <si>
-    <t>Who was first high priest of Israel?</t>
-  </si>
-  <si>
-    <t>Who survived fiery furnace unharmed?</t>
-  </si>
-  <si>
-    <t>Shadrach Meshach Abednego</t>
-  </si>
-  <si>
-    <t>Who was raised from dead by Jesus after four days?</t>
-  </si>
-  <si>
-    <t>Lazarus</t>
-  </si>
-  <si>
-    <t>Jairus</t>
-  </si>
-  <si>
-    <t>Who doubted until seeing Jesus’ wounds?</t>
-  </si>
-  <si>
-    <t>Matthew</t>
-  </si>
-  <si>
-    <t>Who climbed sycamore tree to see Jesus?</t>
-  </si>
-  <si>
-    <t>Zacchaeus</t>
-  </si>
-  <si>
-    <t>Who wrote Book of Revelation?</t>
-  </si>
-  <si>
-    <t>Who was famous doctor and gospel writer?</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
-    <t>Who survived inside fish for three days?</t>
-  </si>
-  <si>
-    <t>Who led worship with harp for King Saul?</t>
-  </si>
-  <si>
-    <t>Asaph</t>
-  </si>
-  <si>
-    <t>Who was mother of John the Baptist?</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>Who was Roman centurion praising Jesus at crucifixion?</t>
-  </si>
-  <si>
-    <t>Longinus</t>
-  </si>
-  <si>
-    <t>Cornelius</t>
-  </si>
-  <si>
-    <t>Pilate</t>
-  </si>
-  <si>
-    <t>Herod</t>
-  </si>
-  <si>
-    <t>Who was disciple known as “the beloved disciple”?</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>Jesus</t>
-  </si>
-  <si>
-    <t>What age was Jesus when He stayed behind in the temple?</t>
-  </si>
-  <si>
-    <t>Who recognized baby Jesus in the temple?</t>
-  </si>
-  <si>
-    <t>Simeon</t>
-  </si>
-  <si>
-    <t>Who prepared the way for Jesus?</t>
-  </si>
-  <si>
-    <t>John the Baptist</t>
-  </si>
-  <si>
-    <t>What was Jesus wrapped in after birth?</t>
-  </si>
-  <si>
-    <t>Swaddling cloths</t>
-  </si>
-  <si>
-    <t>Blanket</t>
-  </si>
-  <si>
-    <t>Silk</t>
-  </si>
-  <si>
-    <t>Leaves</t>
-  </si>
-  <si>
-    <t>Where did Jesus turn water into wine?</t>
-  </si>
-  <si>
-    <t>Cana</t>
-  </si>
-  <si>
-    <t>Bethlehem</t>
-  </si>
-  <si>
-    <t>Nazareth</t>
-  </si>
-  <si>
-    <t>Jerusalem</t>
-  </si>
-  <si>
-    <t>Who was the Roman ruler when Jesus was born?</t>
-  </si>
-  <si>
-    <t>Caesar</t>
-  </si>
-  <si>
-    <t>Nero</t>
-  </si>
-  <si>
-    <t>What trade did Jesus likely learn from Joseph?</t>
-  </si>
-  <si>
-    <t>Carpentry</t>
-  </si>
-  <si>
-    <t>Fishing</t>
-  </si>
-  <si>
-    <t>Farming</t>
-  </si>
-  <si>
-    <t>Blacksmithing</t>
-  </si>
-  <si>
-    <t>How many baskets were left after feeding 5000?</t>
-  </si>
-  <si>
-    <t>Who climbed onto roof to lower sick man to Jesus?</t>
-  </si>
-  <si>
-    <t>Friends of paralytic</t>
-  </si>
-  <si>
-    <t>Disciples</t>
-  </si>
-  <si>
-    <t>Priests</t>
-  </si>
-  <si>
-    <t>Soldiers</t>
-  </si>
-  <si>
-    <t>What illness did Jesus heal by touching eyes?</t>
-  </si>
-  <si>
-    <t>Blindness</t>
-  </si>
-  <si>
-    <t>Fever</t>
-  </si>
-  <si>
-    <t>Leprosy</t>
-  </si>
-  <si>
-    <t>Paralysis</t>
-  </si>
-  <si>
-    <t>Who washed Jesus’ feet with expensive perfume?</t>
-  </si>
-  <si>
-    <t>Mary of Bethany</t>
-  </si>
-  <si>
-    <t>What disciple was a tax collector?</t>
-  </si>
-  <si>
-    <t>Who tried walking on water toward Jesus?</t>
-  </si>
-  <si>
-    <t>Andrew</t>
-  </si>
-  <si>
-    <t>What did Jesus calm with His words?</t>
-  </si>
-  <si>
-    <t>Storm</t>
-  </si>
-  <si>
-    <t>Fire</t>
-  </si>
-  <si>
-    <t>Earthquake</t>
-  </si>
-  <si>
-    <t>Flood</t>
-  </si>
-  <si>
-    <t>What bird descended during Jesus’ baptism?</t>
-  </si>
-  <si>
-    <t>Dove</t>
-  </si>
-  <si>
-    <t>Eagle</t>
-  </si>
-  <si>
-    <t>Sparrow</t>
-  </si>
-  <si>
-    <t>Raven</t>
-  </si>
-  <si>
-    <t>Who wanted Jesus crucified?</t>
-  </si>
-  <si>
-    <t>Crowd</t>
-  </si>
-  <si>
-    <t>What crown was forced onto Jesus’ head?</t>
-  </si>
-  <si>
-    <t>Crown of thorns</t>
-  </si>
-  <si>
-    <t>Gold crown</t>
-  </si>
-  <si>
-    <t>Silver crown</t>
-  </si>
-  <si>
-    <t>Flower crown</t>
-  </si>
-  <si>
-    <t>What was placed above Jesus on the cross?</t>
-  </si>
-  <si>
-    <t>King of the Jews</t>
-  </si>
-  <si>
-    <t>Savior</t>
-  </si>
-  <si>
-    <t>Messiah</t>
-  </si>
-  <si>
-    <t>Prophet</t>
-  </si>
-  <si>
-    <t>Who helped carry Jesus’ cross?</t>
-  </si>
-  <si>
-    <t>Simon of Cyrene</t>
-  </si>
-  <si>
-    <t>What happened in temple when Jesus died?</t>
-  </si>
-  <si>
-    <t>Curtain tore</t>
-  </si>
-  <si>
-    <t>Earth stopped</t>
-  </si>
-  <si>
-    <t>Fire appeared</t>
-  </si>
-  <si>
-    <t>Statues broke</t>
-  </si>
-  <si>
-    <t>Who buried Jesus in tomb?</t>
-  </si>
-  <si>
-    <t>Joseph of Arimathea</t>
-  </si>
-  <si>
-    <t>Nicodemus</t>
-  </si>
-  <si>
-    <t>Who came to Jesus at night to ask questions?</t>
-  </si>
-  <si>
-    <t>Who was raised from dead after four days?</t>
-  </si>
-  <si>
-    <t>What miracle happened at Sea of Galilee?</t>
-  </si>
-  <si>
-    <t>Jesus walked on water</t>
-  </si>
-  <si>
-    <t>Fish multiplied</t>
-  </si>
-  <si>
-    <t>Mountain moved</t>
-  </si>
-  <si>
-    <t>Boat vanished</t>
-  </si>
-  <si>
-    <t>Who doubted until touching Jesus’ wounds?</t>
-  </si>
-  <si>
-    <t>What did Jesus multiply for the crowd?</t>
-  </si>
-  <si>
-    <t>Bread and fish</t>
-  </si>
-  <si>
-    <t>Fruit</t>
-  </si>
-  <si>
-    <t>Honey</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>What prayer begins with “Our Father”?</t>
-  </si>
-  <si>
-    <t>Lord’s Prayer</t>
-  </si>
-  <si>
-    <t>Psalm 23</t>
-  </si>
-  <si>
-    <t>Holy Prayer</t>
-  </si>
-  <si>
-    <t>Morning Prayer</t>
-  </si>
-  <si>
-    <t>Who betrayed Jesus for silver coins?</t>
-  </si>
-  <si>
-    <t>Judas</t>
-  </si>
-  <si>
-    <t>How many silver coins betrayed Jesus?</t>
-  </si>
-  <si>
-    <t>Who cut off servant’s ear during arrest?</t>
-  </si>
-  <si>
-    <t>What miracle healed ten men at once?</t>
-  </si>
-  <si>
-    <t>Healing lepers</t>
-  </si>
-  <si>
-    <t>Raising dead</t>
-  </si>
-  <si>
-    <t>Walking on water</t>
-  </si>
-  <si>
-    <t>Blind healing</t>
-  </si>
-  <si>
-    <t>What did Jesus ride into Jerusalem?</t>
-  </si>
-  <si>
-    <t>Donkey</t>
-  </si>
-  <si>
-    <t>Horse</t>
-  </si>
-  <si>
-    <t>Camel</t>
-  </si>
-  <si>
-    <t>Chariot</t>
-  </si>
-  <si>
-    <t>Who denied knowing Jesus three times?</t>
-  </si>
-  <si>
-    <t>What garden did Jesus pray in before arrest?</t>
-  </si>
-  <si>
-    <t>Gethsemane</t>
-  </si>
-  <si>
-    <t>Eden</t>
-  </si>
-  <si>
-    <t>Who tempted Jesus in wilderness?</t>
-  </si>
-  <si>
-    <t>Satan</t>
-  </si>
-  <si>
-    <t>How many days did Jesus fast in wilderness?</t>
-  </si>
-  <si>
-    <t>What did Jesus say to calm the storm?</t>
-  </si>
-  <si>
-    <t>Peace be still</t>
-  </si>
-  <si>
-    <t>Be quiet</t>
-  </si>
-  <si>
-    <t>Stop now</t>
-  </si>
-  <si>
-    <t>Stay calm</t>
-  </si>
-  <si>
-    <t>Who touched Jesus’ robe and was healed?</t>
-  </si>
-  <si>
-    <t>Bleeding woman</t>
-  </si>
-  <si>
-    <t>Who climbed tree to see Jesus?</t>
-  </si>
-  <si>
-    <t>What did Jesus use to feed 5000?</t>
-  </si>
-  <si>
-    <t>5 loaves and 2 fish</t>
-  </si>
-  <si>
-    <t>7 loaves</t>
-  </si>
-  <si>
-    <t>3 fish</t>
-  </si>
-  <si>
-    <t>10 loaves</t>
-  </si>
-  <si>
-    <t>What disciple doubted Jesus’ resurrection?</t>
-  </si>
-  <si>
-    <t>What happened three days after crucifixion?</t>
-  </si>
-  <si>
-    <t>Resurrection</t>
-  </si>
-  <si>
-    <t>What city did Jesus grow up in?</t>
-  </si>
-  <si>
-    <t>Who announced Jesus’ birth to shepherds?</t>
-  </si>
-  <si>
-    <t>Angels</t>
-  </si>
-  <si>
-    <t>Prophets</t>
-  </si>
-  <si>
-    <t>Kings</t>
-  </si>
-  <si>
-    <t>What heavenly object guided wise men?</t>
-  </si>
-  <si>
-    <t>Star</t>
-  </si>
-  <si>
-    <t>Moon</t>
-  </si>
-  <si>
-    <t>Cloud</t>
-  </si>
-  <si>
-    <t>Comet</t>
-  </si>
-  <si>
-    <t>Who wanted to kill baby Jesus?</t>
-  </si>
-  <si>
-    <t>What disciple was brother of Peter?</t>
-  </si>
-  <si>
-    <t>What disciple was called beloved disciple?</t>
-  </si>
-  <si>
-    <t>Who said “Prepare the way of the Lord”?</t>
-  </si>
-  <si>
     <t>What happened after Jesus ascended?</t>
   </si>
   <si>
@@ -840,6 +552,498 @@
   </si>
   <si>
     <t>Fire rained</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>What planet is closest to the Sun?</t>
+  </si>
+  <si>
+    <t>Mercury</t>
+  </si>
+  <si>
+    <t>Venus</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>Jupiter</t>
+  </si>
+  <si>
+    <t>What gas do plants absorb from atmosphere?</t>
+  </si>
+  <si>
+    <t>Carbon dioxide</t>
+  </si>
+  <si>
+    <t>Oxygen</t>
+  </si>
+  <si>
+    <t>Nitrogen</t>
+  </si>
+  <si>
+    <t>Helium</t>
+  </si>
+  <si>
+    <t>What is the hardest natural substance?</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>Quartz</t>
+  </si>
+  <si>
+    <t>What force pulls objects toward Earth?</t>
+  </si>
+  <si>
+    <t>Gravity</t>
+  </si>
+  <si>
+    <t>Magnetism</t>
+  </si>
+  <si>
+    <t>Friction</t>
+  </si>
+  <si>
+    <t>Pressure</t>
+  </si>
+  <si>
+    <t>Which organ helps humans breathe?</t>
+  </si>
+  <si>
+    <t>Lungs</t>
+  </si>
+  <si>
+    <t>Heart</t>
+  </si>
+  <si>
+    <t>Liver</t>
+  </si>
+  <si>
+    <t>Kidney</t>
+  </si>
+  <si>
+    <t>What is chemical formula of water?</t>
+  </si>
+  <si>
+    <t>H2O</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>O2</t>
+  </si>
+  <si>
+    <t>NaCl</t>
+  </si>
+  <si>
+    <t>What gas do humans need to survive?</t>
+  </si>
+  <si>
+    <t>Hydrogen</t>
+  </si>
+  <si>
+    <t>Which planet is known for rings?</t>
+  </si>
+  <si>
+    <t>Saturn</t>
+  </si>
+  <si>
+    <t>What part of plant absorbs water?</t>
+  </si>
+  <si>
+    <t>Roots</t>
+  </si>
+  <si>
+    <t>Stem</t>
+  </si>
+  <si>
+    <t>Flower</t>
+  </si>
+  <si>
+    <t>What is center of atom called?</t>
+  </si>
+  <si>
+    <t>Nucleus</t>
+  </si>
+  <si>
+    <t>Electron</t>
+  </si>
+  <si>
+    <t>Proton</t>
+  </si>
+  <si>
+    <t>Neutron</t>
+  </si>
+  <si>
+    <t>What is boiling point of water in Celsius?</t>
+  </si>
+  <si>
+    <t>100°C</t>
+  </si>
+  <si>
+    <t>90°C</t>
+  </si>
+  <si>
+    <t>120°C</t>
+  </si>
+  <si>
+    <t>80°C</t>
+  </si>
+  <si>
+    <t>Which vitamin comes from sunlight?</t>
+  </si>
+  <si>
+    <t>Vitamin D</t>
+  </si>
+  <si>
+    <t>Vitamin A</t>
+  </si>
+  <si>
+    <t>Vitamin C</t>
+  </si>
+  <si>
+    <t>Vitamin K</t>
+  </si>
+  <si>
+    <t>What galaxy do we live in?</t>
+  </si>
+  <si>
+    <t>Milky Way</t>
+  </si>
+  <si>
+    <t>Andromeda</t>
+  </si>
+  <si>
+    <t>Solar Galaxy</t>
+  </si>
+  <si>
+    <t>Whirlpool</t>
+  </si>
+  <si>
+    <t>Which blood cells fight infections?</t>
+  </si>
+  <si>
+    <t>White blood cells</t>
+  </si>
+  <si>
+    <t>Red blood cells</t>
+  </si>
+  <si>
+    <t>Platelets</t>
+  </si>
+  <si>
+    <t>Plasma</t>
+  </si>
+  <si>
+    <t>What is fastest land animal?</t>
+  </si>
+  <si>
+    <t>Cheetah</t>
+  </si>
+  <si>
+    <t>Lion</t>
+  </si>
+  <si>
+    <t>Tiger</t>
+  </si>
+  <si>
+    <t>What is largest organ in human body?</t>
+  </si>
+  <si>
+    <t>Skin</t>
+  </si>
+  <si>
+    <t>What part of eye controls light entry?</t>
+  </si>
+  <si>
+    <t>Pupil</t>
+  </si>
+  <si>
+    <t>Retina</t>
+  </si>
+  <si>
+    <t>Cornea</t>
+  </si>
+  <si>
+    <t>Lens</t>
+  </si>
+  <si>
+    <t>Which planet is called Blue Planet?</t>
+  </si>
+  <si>
+    <t>Earth</t>
+  </si>
+  <si>
+    <t>Neptune</t>
+  </si>
+  <si>
+    <t>What gas do plants release?</t>
+  </si>
+  <si>
+    <t>What is nearest star to Earth?</t>
+  </si>
+  <si>
+    <t>Sun</t>
+  </si>
+  <si>
+    <t>Sirius</t>
+  </si>
+  <si>
+    <t>Which metal is liquid at room temperature?</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>What is study of living things called?</t>
+  </si>
+  <si>
+    <t>Biology</t>
+  </si>
+  <si>
+    <t>Chemistry</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>Geology</t>
+  </si>
+  <si>
+    <t>What is process plants use to make food?</t>
+  </si>
+  <si>
+    <t>Photosynthesis</t>
+  </si>
+  <si>
+    <t>Respiration</t>
+  </si>
+  <si>
+    <t>Digestion</t>
+  </si>
+  <si>
+    <t>Fermentation</t>
+  </si>
+  <si>
+    <t>What is largest planet in solar system?</t>
+  </si>
+  <si>
+    <t>What type of energy comes from Sun?</t>
+  </si>
+  <si>
+    <t>Solar energy</t>
+  </si>
+  <si>
+    <t>Wind energy</t>
+  </si>
+  <si>
+    <t>Nuclear energy</t>
+  </si>
+  <si>
+    <t>Hydro energy</t>
+  </si>
+  <si>
+    <t>What instrument measures temperature?</t>
+  </si>
+  <si>
+    <t>Thermometer</t>
+  </si>
+  <si>
+    <t>Barometer</t>
+  </si>
+  <si>
+    <t>Compass</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>Which planet is known as Red Planet?</t>
+  </si>
+  <si>
+    <t>What part of body pumps blood?</t>
+  </si>
+  <si>
+    <t>Brain</t>
+  </si>
+  <si>
+    <t>What is freezing point of water?</t>
+  </si>
+  <si>
+    <t>0°C</t>
+  </si>
+  <si>
+    <t>10°C</t>
+  </si>
+  <si>
+    <t>-10°C</t>
+  </si>
+  <si>
+    <t>5°C</t>
+  </si>
+  <si>
+    <t>Which scientist discovered gravity?</t>
+  </si>
+  <si>
+    <t>Isaac Newton</t>
+  </si>
+  <si>
+    <t>Einstein</t>
+  </si>
+  <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>Galileo</t>
+  </si>
+  <si>
+    <t>What is largest mammal on Earth?</t>
+  </si>
+  <si>
+    <t>Blue whale</t>
+  </si>
+  <si>
+    <t>Elephant</t>
+  </si>
+  <si>
+    <t>Giraffe</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>What gas is most abundant in atmosphere?</t>
+  </si>
+  <si>
+    <t>What is process of water turning into vapor?</t>
+  </si>
+  <si>
+    <t>Evaporation</t>
+  </si>
+  <si>
+    <t>Condensation</t>
+  </si>
+  <si>
+    <t>Freezing</t>
+  </si>
+  <si>
+    <t>Melting</t>
+  </si>
+  <si>
+    <t>Which organ filters blood?</t>
+  </si>
+  <si>
+    <t>What is smallest unit of matter?</t>
+  </si>
+  <si>
+    <t>Atom</t>
+  </si>
+  <si>
+    <t>Molecule</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Particle</t>
+  </si>
+  <si>
+    <t>What planet has strongest gravity?</t>
+  </si>
+  <si>
+    <t>What is study of stars and planets called?</t>
+  </si>
+  <si>
+    <t>Astronomy</t>
+  </si>
+  <si>
+    <t>Geography</t>
+  </si>
+  <si>
+    <t>Which blood cells carry oxygen?</t>
+  </si>
+  <si>
+    <t>What organ controls body functions?</t>
+  </si>
+  <si>
+    <t>Which gas causes greenhouse effect most?</t>
+  </si>
+  <si>
+    <t>What is process of solid changing to liquid?</t>
+  </si>
+  <si>
+    <t>What natural satellite orbits Earth?</t>
+  </si>
+  <si>
+    <t>Which scientist developed theory of relativity?</t>
+  </si>
+  <si>
+    <t>Newton</t>
+  </si>
+  <si>
+    <t>Edison</t>
+  </si>
+  <si>
+    <t>What is unit of electrical power?</t>
+  </si>
+  <si>
+    <t>Watt</t>
+  </si>
+  <si>
+    <t>Volt</t>
+  </si>
+  <si>
+    <t>Ampere</t>
+  </si>
+  <si>
+    <t>Which planet is hottest in solar system?</t>
+  </si>
+  <si>
+    <t>What organ helps digest food?</t>
+  </si>
+  <si>
+    <t>Stomach</t>
+  </si>
+  <si>
+    <t>What is study of Earth rocks called?</t>
+  </si>
+  <si>
+    <t>What gas is used by divers for breathing tanks?</t>
+  </si>
+  <si>
+    <t>What force keeps planets orbiting Sun?</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>What is device used to see tiny organisms?</t>
+  </si>
+  <si>
+    <t>Microscope</t>
+  </si>
+  <si>
+    <t>Telescope</t>
+  </si>
+  <si>
+    <t>Periscope</t>
+  </si>
+  <si>
+    <t>Binoculars</t>
   </si>
 </sst>
 </file>
@@ -1873,20 +2077,20 @@
       <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>18</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -1900,22 +2104,22 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -1929,22 +2133,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>19</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1958,16 +2162,16 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
         <v>23</v>
@@ -2076,20 +2280,20 @@
       <c r="B9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" t="s">
-        <v>44</v>
+      <c r="C9">
+        <v>12</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -2103,22 +2307,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
         <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
       </c>
       <c r="H10">
         <v>5</v>
@@ -2132,22 +2336,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
         <v>47</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>48</v>
       </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -2161,22 +2365,22 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -2190,22 +2394,22 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G13" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -2219,22 +2423,22 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
         <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>52</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -2248,22 +2452,22 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -2277,22 +2481,22 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -2306,22 +2510,22 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="H17">
         <v>5</v>
@@ -2335,22 +2539,22 @@
         <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -2364,22 +2568,22 @@
         <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -2393,22 +2597,22 @@
         <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -2422,22 +2626,22 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="H21">
         <v>5</v>
@@ -2451,22 +2655,22 @@
         <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="G22" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="H22">
         <v>5</v>
@@ -2480,22 +2684,22 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="H23">
         <v>5</v>
@@ -2509,22 +2713,22 @@
         <v>9</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H24">
         <v>5</v>
@@ -2538,22 +2742,22 @@
         <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -2567,22 +2771,22 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G26" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -2596,22 +2800,22 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="G27" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -2625,22 +2829,22 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -2654,22 +2858,22 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" t="s">
         <v>19</v>
       </c>
-      <c r="D29" t="s">
+      <c r="G29" t="s">
         <v>58</v>
-      </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" t="s">
-        <v>87</v>
       </c>
       <c r="H29">
         <v>5</v>
@@ -2683,22 +2887,22 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" t="s">
-        <v>59</v>
-      </c>
-      <c r="E30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" t="s">
-        <v>87</v>
-      </c>
-      <c r="G30" t="s">
-        <v>75</v>
+        <v>117</v>
+      </c>
+      <c r="C30">
+        <v>30</v>
+      </c>
+      <c r="D30">
+        <v>20</v>
+      </c>
+      <c r="E30">
+        <v>30</v>
+      </c>
+      <c r="F30">
+        <v>40</v>
+      </c>
+      <c r="G30">
+        <v>50</v>
       </c>
       <c r="H30">
         <v>5</v>
@@ -2712,22 +2916,22 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G31" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H31">
         <v>5</v>
@@ -2741,22 +2945,22 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="G32" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="H32">
         <v>5</v>
@@ -2770,22 +2974,22 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="G33" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="H33">
         <v>5</v>
@@ -2799,22 +3003,22 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F34" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G34" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -2828,22 +3032,22 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="F35" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="G35" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -2857,22 +3061,22 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -2886,22 +3090,22 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" t="s">
-        <v>97</v>
-      </c>
-      <c r="D37" t="s">
-        <v>17</v>
-      </c>
-      <c r="E37" t="s">
-        <v>97</v>
-      </c>
-      <c r="F37" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" t="s">
-        <v>41</v>
+        <v>135</v>
+      </c>
+      <c r="C37">
+        <v>40</v>
+      </c>
+      <c r="D37">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>40</v>
+      </c>
+      <c r="F37">
+        <v>7</v>
+      </c>
+      <c r="G37">
+        <v>30</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -2915,22 +3119,22 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>140</v>
       </c>
       <c r="H38">
         <v>5</v>
@@ -2944,22 +3148,22 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H39">
         <v>5</v>
@@ -2973,22 +3177,22 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C40" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G40" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H40">
         <v>5</v>
@@ -3002,22 +3206,22 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="E41" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="F41" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="G41" t="s">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -3031,22 +3235,22 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="D42" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G42" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="H42">
         <v>5</v>
@@ -3060,22 +3264,22 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>153</v>
       </c>
       <c r="D43" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G43" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="H43">
         <v>5</v>
@@ -3089,22 +3293,22 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E44" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="F44" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G44" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H44">
         <v>5</v>
@@ -3118,22 +3322,22 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>157</v>
       </c>
       <c r="E45" t="s">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="F45" t="s">
-        <v>41</v>
+        <v>158</v>
       </c>
       <c r="G45" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H45">
         <v>5</v>
@@ -3147,22 +3351,22 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="C46" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="D46" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="E46" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="F46" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="G46" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="H46">
         <v>5</v>
@@ -3176,22 +3380,22 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E47" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H47">
         <v>5</v>
@@ -3205,22 +3409,22 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="C48" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" t="s">
         <v>19</v>
       </c>
-      <c r="D48" t="s">
-        <v>59</v>
-      </c>
-      <c r="E48" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
       <c r="G48" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -3234,22 +3438,22 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="D49" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="H49">
         <v>5</v>
@@ -3263,22 +3467,22 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="C50" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="G50" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="H50">
         <v>5</v>
@@ -3292,22 +3496,22 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="C51" t="s">
-        <v>43</v>
+        <v>171</v>
       </c>
       <c r="D51" t="s">
-        <v>42</v>
+        <v>172</v>
       </c>
       <c r="E51" t="s">
-        <v>43</v>
+        <v>171</v>
       </c>
       <c r="F51" t="s">
-        <v>44</v>
+        <v>173</v>
       </c>
       <c r="G51" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="H51">
         <v>5</v>
@@ -3318,25 +3522,25 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
-      </c>
-      <c r="C52">
-        <v>12</v>
-      </c>
-      <c r="D52">
-        <v>10</v>
-      </c>
-      <c r="E52">
-        <v>12</v>
-      </c>
-      <c r="F52">
-        <v>15</v>
-      </c>
-      <c r="G52">
-        <v>18</v>
+        <v>176</v>
+      </c>
+      <c r="C52" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" t="s">
+        <v>178</v>
+      </c>
+      <c r="E52" t="s">
+        <v>177</v>
+      </c>
+      <c r="F52" t="s">
+        <v>179</v>
+      </c>
+      <c r="G52" t="s">
+        <v>180</v>
       </c>
       <c r="H52">
         <v>5</v>
@@ -3347,25 +3551,25 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="E53" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="F53" t="s">
-        <v>17</v>
+        <v>184</v>
       </c>
       <c r="G53" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="H53">
         <v>5</v>
@@ -3376,25 +3580,25 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="C54" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="D54" t="s">
-        <v>41</v>
+        <v>188</v>
       </c>
       <c r="E54" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="F54" t="s">
-        <v>42</v>
+        <v>189</v>
       </c>
       <c r="G54" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="H54">
         <v>5</v>
@@ -3405,25 +3609,25 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="C55" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="D55" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="E55" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="F55" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="G55" t="s">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="H55">
         <v>5</v>
@@ -3434,25 +3638,25 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="C56" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="D56" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="E56" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="F56" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="G56" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="H56">
         <v>5</v>
@@ -3463,25 +3667,25 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B57" t="s">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="C57" t="s">
-        <v>122</v>
+        <v>202</v>
       </c>
       <c r="D57" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="E57" t="s">
-        <v>122</v>
+        <v>202</v>
       </c>
       <c r="F57" t="s">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="G57" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="H57">
         <v>5</v>
@@ -3492,25 +3696,25 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="C58" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="D58" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="E58" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="F58" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="G58" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="H58">
         <v>5</v>
@@ -3521,25 +3725,25 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
-      </c>
-      <c r="C59">
-        <v>12</v>
-      </c>
-      <c r="D59">
-        <v>7</v>
-      </c>
-      <c r="E59">
-        <v>12</v>
-      </c>
-      <c r="F59">
-        <v>5</v>
-      </c>
-      <c r="G59">
-        <v>10</v>
+        <v>208</v>
+      </c>
+      <c r="C59" t="s">
+        <v>209</v>
+      </c>
+      <c r="D59" t="s">
+        <v>180</v>
+      </c>
+      <c r="E59" t="s">
+        <v>209</v>
+      </c>
+      <c r="F59" t="s">
+        <v>179</v>
+      </c>
+      <c r="G59" t="s">
+        <v>178</v>
       </c>
       <c r="H59">
         <v>5</v>
@@ -3550,25 +3754,25 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B60" t="s">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="C60" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="F60" t="s">
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="G60" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
       <c r="H60">
         <v>5</v>
@@ -3579,25 +3783,25 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B61" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="C61" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="D61" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="E61" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="F61" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
       <c r="G61" t="s">
-        <v>159</v>
+        <v>218</v>
       </c>
       <c r="H61">
         <v>5</v>
@@ -3608,25 +3812,25 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="C62" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="D62" t="s">
-        <v>95</v>
+        <v>221</v>
       </c>
       <c r="E62" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c r="F62" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="G62" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="H62">
         <v>5</v>
@@ -3637,25 +3841,25 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B63" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
+        <v>225</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
+        <v>226</v>
       </c>
       <c r="E63" t="s">
-        <v>107</v>
+        <v>225</v>
       </c>
       <c r="F63" t="s">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="G63" t="s">
-        <v>124</v>
+        <v>228</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -3666,25 +3870,25 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="C64" t="s">
-        <v>42</v>
+        <v>230</v>
       </c>
       <c r="D64" t="s">
-        <v>43</v>
+        <v>231</v>
       </c>
       <c r="E64" t="s">
-        <v>42</v>
+        <v>230</v>
       </c>
       <c r="F64" t="s">
-        <v>44</v>
+        <v>232</v>
       </c>
       <c r="G64" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -3695,25 +3899,25 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B65" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="C65" t="s">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="D65" t="s">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="E65" t="s">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="F65" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="G65" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -3724,25 +3928,25 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B66" t="s">
-        <v>170</v>
+        <v>239</v>
       </c>
       <c r="C66" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="E66" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
       <c r="F66" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="G66" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="H66">
         <v>5</v>
@@ -3753,25 +3957,25 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B67" t="s">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="C67" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="D67" t="s">
-        <v>42</v>
+        <v>198</v>
       </c>
       <c r="E67" t="s">
-        <v>176</v>
+        <v>244</v>
       </c>
       <c r="F67" t="s">
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="G67" t="s">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="H67">
         <v>5</v>
@@ -3782,25 +3986,25 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B68" t="s">
-        <v>177</v>
+        <v>245</v>
       </c>
       <c r="C68" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="D68" t="s">
-        <v>179</v>
+        <v>247</v>
       </c>
       <c r="E68" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="F68" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="G68" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="H68">
         <v>5</v>
@@ -3811,25 +4015,25 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B69" t="s">
-        <v>182</v>
+        <v>250</v>
       </c>
       <c r="C69" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="D69" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E69" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="F69" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="G69" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="H69">
         <v>5</v>
@@ -3840,25 +4044,25 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B70" t="s">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="C70" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D70" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="E70" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F70" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="G70" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -3869,25 +4073,25 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B71" t="s">
-        <v>189</v>
+        <v>254</v>
       </c>
       <c r="C71" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="D71" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="E71" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="F71" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="G71" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="H71">
         <v>5</v>
@@ -3898,25 +4102,25 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B72" t="s">
-        <v>194</v>
+        <v>257</v>
       </c>
       <c r="C72" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="D72" t="s">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="E72" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F72" t="s">
-        <v>43</v>
+        <v>258</v>
       </c>
       <c r="G72" t="s">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="H72">
         <v>5</v>
@@ -3927,25 +4131,25 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B73" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C73" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="E73" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="F73" t="s">
-        <v>41</v>
+        <v>263</v>
       </c>
       <c r="G73" t="s">
-        <v>44</v>
+        <v>264</v>
       </c>
       <c r="H73">
         <v>5</v>
@@ -3956,25 +4160,25 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B74" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="C74" t="s">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="D74" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="E74" t="s">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="F74" t="s">
-        <v>38</v>
+        <v>268</v>
       </c>
       <c r="G74" t="s">
-        <v>41</v>
+        <v>269</v>
       </c>
       <c r="H74">
         <v>5</v>
@@ -3985,25 +4189,25 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B75" t="s">
-        <v>199</v>
+        <v>270</v>
       </c>
       <c r="C75" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D75" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="E75" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="F75" t="s">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="G75" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="H75">
         <v>5</v>
@@ -4014,25 +4218,25 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B76" t="s">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>272</v>
       </c>
       <c r="D76" t="s">
-        <v>42</v>
+        <v>273</v>
       </c>
       <c r="E76" t="s">
-        <v>44</v>
+        <v>272</v>
       </c>
       <c r="F76" t="s">
-        <v>43</v>
+        <v>274</v>
       </c>
       <c r="G76" t="s">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="H76">
         <v>5</v>
@@ -4043,25 +4247,25 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B77" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="C77" t="s">
-        <v>206</v>
+        <v>277</v>
       </c>
       <c r="D77" t="s">
-        <v>207</v>
+        <v>278</v>
       </c>
       <c r="E77" t="s">
-        <v>206</v>
+        <v>277</v>
       </c>
       <c r="F77" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="G77" t="s">
-        <v>209</v>
+        <v>280</v>
       </c>
       <c r="H77">
         <v>5</v>
@@ -4072,25 +4276,25 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B78" t="s">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="C78" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="D78" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="E78" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="F78" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="G78" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H78">
         <v>5</v>
@@ -4101,25 +4305,25 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B79" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="C79" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D79" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="E79" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="F79" t="s">
-        <v>44</v>
+        <v>283</v>
       </c>
       <c r="G79" t="s">
-        <v>43</v>
+        <v>200</v>
       </c>
       <c r="H79">
         <v>5</v>
@@ -4130,25 +4334,25 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>217</v>
-      </c>
-      <c r="C80">
-        <v>30</v>
-      </c>
-      <c r="D80">
-        <v>20</v>
-      </c>
-      <c r="E80">
-        <v>30</v>
-      </c>
-      <c r="F80">
-        <v>40</v>
-      </c>
-      <c r="G80">
-        <v>50</v>
+        <v>284</v>
+      </c>
+      <c r="C80" t="s">
+        <v>285</v>
+      </c>
+      <c r="D80" t="s">
+        <v>286</v>
+      </c>
+      <c r="E80" t="s">
+        <v>285</v>
+      </c>
+      <c r="F80" t="s">
+        <v>287</v>
+      </c>
+      <c r="G80" t="s">
+        <v>288</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -4159,25 +4363,25 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B81" t="s">
-        <v>218</v>
+        <v>289</v>
       </c>
       <c r="C81" t="s">
-        <v>42</v>
+        <v>290</v>
       </c>
       <c r="D81" t="s">
-        <v>43</v>
+        <v>291</v>
       </c>
       <c r="E81" t="s">
-        <v>42</v>
+        <v>290</v>
       </c>
       <c r="F81" t="s">
-        <v>44</v>
+        <v>292</v>
       </c>
       <c r="G81" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
       <c r="H81">
         <v>5</v>
@@ -4188,25 +4392,25 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B82" t="s">
-        <v>219</v>
+        <v>294</v>
       </c>
       <c r="C82" t="s">
-        <v>220</v>
+        <v>295</v>
       </c>
       <c r="D82" t="s">
-        <v>221</v>
+        <v>296</v>
       </c>
       <c r="E82" t="s">
-        <v>220</v>
+        <v>295</v>
       </c>
       <c r="F82" t="s">
-        <v>222</v>
+        <v>297</v>
       </c>
       <c r="G82" t="s">
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -4217,25 +4421,25 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>224</v>
+        <v>299</v>
       </c>
       <c r="C83" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="D83" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="E83" t="s">
-        <v>225</v>
+        <v>184</v>
       </c>
       <c r="F83" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="G83" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="H83">
         <v>5</v>
@@ -4246,25 +4450,25 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B84" t="s">
-        <v>229</v>
+        <v>300</v>
       </c>
       <c r="C84" t="s">
-        <v>42</v>
+        <v>301</v>
       </c>
       <c r="D84" t="s">
-        <v>43</v>
+        <v>302</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>301</v>
       </c>
       <c r="F84" t="s">
-        <v>44</v>
+        <v>303</v>
       </c>
       <c r="G84" t="s">
-        <v>41</v>
+        <v>304</v>
       </c>
       <c r="H84">
         <v>5</v>
@@ -4275,25 +4479,25 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B85" t="s">
-        <v>230</v>
+        <v>305</v>
       </c>
       <c r="C85" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="D85" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="E85" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="F85" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="G85" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="H85">
         <v>5</v>
@@ -4304,25 +4508,25 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B86" t="s">
-        <v>233</v>
+        <v>306</v>
       </c>
       <c r="C86" t="s">
-        <v>234</v>
+        <v>307</v>
       </c>
       <c r="D86" t="s">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="E86" t="s">
-        <v>234</v>
+        <v>307</v>
       </c>
       <c r="F86" t="s">
-        <v>42</v>
+        <v>309</v>
       </c>
       <c r="G86" t="s">
-        <v>122</v>
+        <v>310</v>
       </c>
       <c r="H86">
         <v>5</v>
@@ -4333,25 +4537,25 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B87" t="s">
-        <v>235</v>
-      </c>
-      <c r="C87">
-        <v>40</v>
-      </c>
-      <c r="D87">
-        <v>12</v>
-      </c>
-      <c r="E87">
-        <v>40</v>
-      </c>
-      <c r="F87">
-        <v>7</v>
-      </c>
-      <c r="G87">
-        <v>30</v>
+        <v>311</v>
+      </c>
+      <c r="C87" t="s">
+        <v>180</v>
+      </c>
+      <c r="D87" t="s">
+        <v>251</v>
+      </c>
+      <c r="E87" t="s">
+        <v>180</v>
+      </c>
+      <c r="F87" t="s">
+        <v>209</v>
+      </c>
+      <c r="G87" t="s">
+        <v>179</v>
       </c>
       <c r="H87">
         <v>5</v>
@@ -4362,25 +4566,25 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B88" t="s">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="C88" t="s">
-        <v>237</v>
+        <v>313</v>
       </c>
       <c r="D88" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="E88" t="s">
-        <v>237</v>
+        <v>313</v>
       </c>
       <c r="F88" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="G88" t="s">
-        <v>240</v>
+        <v>314</v>
       </c>
       <c r="H88">
         <v>5</v>
@@ -4391,25 +4595,25 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B89" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="C89" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>235</v>
       </c>
       <c r="E89" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F89" t="s">
-        <v>95</v>
+        <v>237</v>
       </c>
       <c r="G89" t="s">
-        <v>27</v>
+        <v>238</v>
       </c>
       <c r="H89">
         <v>5</v>
@@ -4420,25 +4624,25 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B90" t="s">
-        <v>243</v>
+        <v>316</v>
       </c>
       <c r="C90" t="s">
-        <v>109</v>
+        <v>283</v>
       </c>
       <c r="D90" t="s">
-        <v>42</v>
+        <v>198</v>
       </c>
       <c r="E90" t="s">
-        <v>109</v>
+        <v>283</v>
       </c>
       <c r="F90" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="G90" t="s">
-        <v>41</v>
+        <v>199</v>
       </c>
       <c r="H90">
         <v>5</v>
@@ -4449,25 +4653,25 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B91" t="s">
-        <v>244</v>
+        <v>317</v>
       </c>
       <c r="C91" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>246</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="F91" t="s">
-        <v>247</v>
+        <v>184</v>
       </c>
       <c r="G91" t="s">
-        <v>248</v>
+        <v>185</v>
       </c>
       <c r="H91">
         <v>5</v>
@@ -4478,25 +4682,25 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B92" t="s">
-        <v>249</v>
+        <v>318</v>
       </c>
       <c r="C92" t="s">
-        <v>44</v>
+        <v>304</v>
       </c>
       <c r="D92" t="s">
-        <v>42</v>
+        <v>303</v>
       </c>
       <c r="E92" t="s">
-        <v>44</v>
+        <v>304</v>
       </c>
       <c r="F92" t="s">
-        <v>43</v>
+        <v>301</v>
       </c>
       <c r="G92" t="s">
-        <v>107</v>
+        <v>302</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -4507,25 +4711,25 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B93" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
       <c r="C93" t="s">
-        <v>251</v>
+        <v>161</v>
       </c>
       <c r="D93" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="E93" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F93" t="s">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="G93" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H93">
         <v>5</v>
@@ -4536,25 +4740,25 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>252</v>
+        <v>320</v>
       </c>
       <c r="C94" t="s">
-        <v>139</v>
+        <v>291</v>
       </c>
       <c r="D94" t="s">
-        <v>138</v>
+        <v>321</v>
       </c>
       <c r="E94" t="s">
-        <v>139</v>
+        <v>291</v>
       </c>
       <c r="F94" t="s">
-        <v>140</v>
+        <v>292</v>
       </c>
       <c r="G94" t="s">
-        <v>137</v>
+        <v>322</v>
       </c>
       <c r="H94">
         <v>5</v>
@@ -4565,25 +4769,25 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>253</v>
+        <v>323</v>
       </c>
       <c r="C95" t="s">
-        <v>254</v>
+        <v>324</v>
       </c>
       <c r="D95" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="E95" t="s">
-        <v>254</v>
+        <v>324</v>
       </c>
       <c r="F95" t="s">
-        <v>256</v>
+        <v>326</v>
       </c>
       <c r="G95" t="s">
-        <v>153</v>
+        <v>321</v>
       </c>
       <c r="H95">
         <v>5</v>
@@ -4594,25 +4798,25 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>257</v>
+        <v>327</v>
       </c>
       <c r="C96" t="s">
-        <v>258</v>
+        <v>178</v>
       </c>
       <c r="D96" t="s">
-        <v>259</v>
+        <v>177</v>
       </c>
       <c r="E96" t="s">
-        <v>258</v>
+        <v>178</v>
       </c>
       <c r="F96" t="s">
-        <v>260</v>
+        <v>179</v>
       </c>
       <c r="G96" t="s">
-        <v>261</v>
+        <v>180</v>
       </c>
       <c r="H96">
         <v>5</v>
@@ -4623,25 +4827,25 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B97" t="s">
-        <v>262</v>
+        <v>328</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>329</v>
       </c>
       <c r="D97" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="E97" t="s">
-        <v>122</v>
+        <v>329</v>
       </c>
       <c r="F97" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="G97" t="s">
-        <v>142</v>
+        <v>283</v>
       </c>
       <c r="H97">
         <v>5</v>
@@ -4652,25 +4856,25 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B98" t="s">
-        <v>263</v>
+        <v>330</v>
       </c>
       <c r="C98" t="s">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>43</v>
+        <v>261</v>
       </c>
       <c r="E98" t="s">
-        <v>164</v>
+        <v>264</v>
       </c>
       <c r="F98" t="s">
-        <v>44</v>
+        <v>313</v>
       </c>
       <c r="G98" t="s">
-        <v>46</v>
+        <v>262</v>
       </c>
       <c r="H98">
         <v>5</v>
@@ -4681,25 +4885,25 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B99" t="s">
-        <v>264</v>
+        <v>331</v>
       </c>
       <c r="C99" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="D99" t="s">
-        <v>42</v>
+        <v>185</v>
       </c>
       <c r="E99" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="F99" t="s">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="G99" t="s">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="H99">
         <v>5</v>
@@ -4710,25 +4914,25 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B100" t="s">
-        <v>265</v>
+        <v>332</v>
       </c>
       <c r="C100" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="D100" t="s">
-        <v>42</v>
+        <v>193</v>
       </c>
       <c r="E100" t="s">
-        <v>130</v>
+        <v>192</v>
       </c>
       <c r="F100" t="s">
-        <v>41</v>
+        <v>333</v>
       </c>
       <c r="G100" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="H100">
         <v>5</v>
@@ -4739,25 +4943,25 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="B101" t="s">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="C101" t="s">
-        <v>267</v>
+        <v>335</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="E101" t="s">
-        <v>267</v>
+        <v>335</v>
       </c>
       <c r="F101" t="s">
-        <v>269</v>
+        <v>337</v>
       </c>
       <c r="G101" t="s">
-        <v>270</v>
+        <v>338</v>
       </c>
       <c r="H101">
         <v>5</v>

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500"/>
+    <workbookView windowWidth="20490" windowHeight="6780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="438">
   <si>
     <t>Topic</t>
   </si>
@@ -1044,6 +1044,303 @@
   </si>
   <si>
     <t>Binoculars</t>
+  </si>
+  <si>
+    <t>Bible</t>
+  </si>
+  <si>
+    <t>What is the longest book in the Bible?</t>
+  </si>
+  <si>
+    <t>Psalms</t>
+  </si>
+  <si>
+    <t>Genesis</t>
+  </si>
+  <si>
+    <t>Isaiah</t>
+  </si>
+  <si>
+    <t>Exodus</t>
+  </si>
+  <si>
+    <t>What is the shortest book in the Bible?</t>
+  </si>
+  <si>
+    <t>3 John</t>
+  </si>
+  <si>
+    <t>Jude</t>
+  </si>
+  <si>
+    <t>Obadiah</t>
+  </si>
+  <si>
+    <t>Philemon</t>
+  </si>
+  <si>
+    <t>How many books are in the Bible?</t>
+  </si>
+  <si>
+    <t>How many books are in the New Testament?</t>
+  </si>
+  <si>
+    <t>How many books are in the Old Testament?</t>
+  </si>
+  <si>
+    <t>Who wrote the first five books of Bible?</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Solomon</t>
+  </si>
+  <si>
+    <t>What is the final book of Bible?</t>
+  </si>
+  <si>
+    <t>Revelation</t>
+  </si>
+  <si>
+    <t>Who built the giant ark?</t>
+  </si>
+  <si>
+    <t>Noah</t>
+  </si>
+  <si>
+    <t>Abraham</t>
+  </si>
+  <si>
+    <t>Who was thrown into lion’s den?</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Samson</t>
+  </si>
+  <si>
+    <t>Who defeated giant Goliath?</t>
+  </si>
+  <si>
+    <t>Saul</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Who parted the Red Sea?</t>
+  </si>
+  <si>
+    <t>Aaron</t>
+  </si>
+  <si>
+    <t>Elijah</t>
+  </si>
+  <si>
+    <t>Who was swallowed by a great fish?</t>
+  </si>
+  <si>
+    <t>Jonah</t>
+  </si>
+  <si>
+    <t>How many disciples did Jesus have?</t>
+  </si>
+  <si>
+    <t>Who denied Jesus three times?</t>
+  </si>
+  <si>
+    <t>What city was Jesus born in?</t>
+  </si>
+  <si>
+    <t>Rome</t>
+  </si>
+  <si>
+    <t>Who baptized Jesus?</t>
+  </si>
+  <si>
+    <t>What river was Jesus baptized in?</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>Nile</t>
+  </si>
+  <si>
+    <t>Euphrates</t>
+  </si>
+  <si>
+    <t>Red Sea</t>
+  </si>
+  <si>
+    <t>Who was mother of Jesus?</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Eve</t>
+  </si>
+  <si>
+    <t>Who was earthly father of Jesus?</t>
+  </si>
+  <si>
+    <t>Who was strongest man in Bible?</t>
+  </si>
+  <si>
+    <t>Who interpreted Pharaoh’s dreams?</t>
+  </si>
+  <si>
+    <t>Who built the temple in Jerusalem?</t>
+  </si>
+  <si>
+    <t>Who was wisest king in Bible?</t>
+  </si>
+  <si>
+    <t>What is shortest verse in Bible?</t>
+  </si>
+  <si>
+    <t>Jesus wept</t>
+  </si>
+  <si>
+    <t>Pray always</t>
+  </si>
+  <si>
+    <t>Amen</t>
+  </si>
+  <si>
+    <t>Hallelujah</t>
+  </si>
+  <si>
+    <t>Who saw a burning bush?</t>
+  </si>
+  <si>
+    <t>Who was first man created by God?</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Cain</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t>Who was first woman created by God?</t>
+  </si>
+  <si>
+    <t>What garden did Adam and Eve live in?</t>
+  </si>
+  <si>
+    <t>Babylon</t>
+  </si>
+  <si>
+    <t>Who killed Abel?</t>
+  </si>
+  <si>
+    <t>Who was father of many nations?</t>
+  </si>
+  <si>
+    <t>Isaac</t>
+  </si>
+  <si>
+    <t>Jacob</t>
+  </si>
+  <si>
+    <t>Who walked on water with Jesus?</t>
+  </si>
+  <si>
+    <t>What was Jesus’ first miracle?</t>
+  </si>
+  <si>
+    <t>Turning water into wine</t>
+  </si>
+  <si>
+    <t>Healing blind</t>
+  </si>
+  <si>
+    <t>Feeding crowd</t>
+  </si>
+  <si>
+    <t>Who was first king of Israel?</t>
+  </si>
+  <si>
+    <t>Jonathan</t>
+  </si>
+  <si>
+    <t>Who anointed David as king?</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>Nathan</t>
+  </si>
+  <si>
+    <t>Who wrote many Psalms?</t>
+  </si>
+  <si>
+    <t>Who survived fiery furnace unharmed?</t>
+  </si>
+  <si>
+    <t>Shadrach Meshach Abednego</t>
+  </si>
+  <si>
+    <t>Who rebuilt walls of Jerusalem?</t>
+  </si>
+  <si>
+    <t>Nehemiah</t>
+  </si>
+  <si>
+    <t>Ezra</t>
+  </si>
+  <si>
+    <t>Who was famous for patience during suffering?</t>
+  </si>
+  <si>
+    <t>Job</t>
+  </si>
+  <si>
+    <t>Who became queen and saved Jews?</t>
+  </si>
+  <si>
+    <t>Esther</t>
+  </si>
+  <si>
+    <t>Deborah</t>
+  </si>
+  <si>
+    <t>What disciple doubted resurrection until seeing Jesus?</t>
+  </si>
+  <si>
+    <t>What disciple was tax collector?</t>
+  </si>
+  <si>
+    <t>Who wrote Book of Revelation?</t>
+  </si>
+  <si>
+    <t>Luke</t>
+  </si>
+  <si>
+    <t>What mountain did Moses receive commandments on?</t>
+  </si>
+  <si>
+    <t>Mount Sinai</t>
+  </si>
+  <si>
+    <t>Zion</t>
+  </si>
+  <si>
+    <t>Carmel</t>
+  </si>
+  <si>
+    <t>Olivet</t>
+  </si>
+  <si>
+    <t>What happened three days after Jesus died?</t>
   </si>
 </sst>
 </file>
@@ -4970,6 +5267,1456 @@
         <v>0</v>
       </c>
     </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>339</v>
+      </c>
+      <c r="B102" t="s">
+        <v>340</v>
+      </c>
+      <c r="C102" t="s">
+        <v>341</v>
+      </c>
+      <c r="D102" t="s">
+        <v>342</v>
+      </c>
+      <c r="E102" t="s">
+        <v>341</v>
+      </c>
+      <c r="F102" t="s">
+        <v>343</v>
+      </c>
+      <c r="G102" t="s">
+        <v>344</v>
+      </c>
+      <c r="H102">
+        <v>5</v>
+      </c>
+      <c r="I102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>339</v>
+      </c>
+      <c r="B103" t="s">
+        <v>345</v>
+      </c>
+      <c r="C103" t="s">
+        <v>346</v>
+      </c>
+      <c r="D103" t="s">
+        <v>347</v>
+      </c>
+      <c r="E103" t="s">
+        <v>346</v>
+      </c>
+      <c r="F103" t="s">
+        <v>348</v>
+      </c>
+      <c r="G103" t="s">
+        <v>349</v>
+      </c>
+      <c r="H103">
+        <v>5</v>
+      </c>
+      <c r="I103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>339</v>
+      </c>
+      <c r="B104" t="s">
+        <v>350</v>
+      </c>
+      <c r="C104">
+        <v>66</v>
+      </c>
+      <c r="D104">
+        <v>39</v>
+      </c>
+      <c r="E104">
+        <v>66</v>
+      </c>
+      <c r="F104">
+        <v>72</v>
+      </c>
+      <c r="G104">
+        <v>100</v>
+      </c>
+      <c r="H104">
+        <v>5</v>
+      </c>
+      <c r="I104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>339</v>
+      </c>
+      <c r="B105" t="s">
+        <v>351</v>
+      </c>
+      <c r="C105">
+        <v>27</v>
+      </c>
+      <c r="D105">
+        <v>20</v>
+      </c>
+      <c r="E105">
+        <v>27</v>
+      </c>
+      <c r="F105">
+        <v>39</v>
+      </c>
+      <c r="G105">
+        <v>12</v>
+      </c>
+      <c r="H105">
+        <v>5</v>
+      </c>
+      <c r="I105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
+        <v>339</v>
+      </c>
+      <c r="B106" t="s">
+        <v>352</v>
+      </c>
+      <c r="C106">
+        <v>39</v>
+      </c>
+      <c r="D106">
+        <v>27</v>
+      </c>
+      <c r="E106">
+        <v>39</v>
+      </c>
+      <c r="F106">
+        <v>50</v>
+      </c>
+      <c r="G106">
+        <v>66</v>
+      </c>
+      <c r="H106">
+        <v>5</v>
+      </c>
+      <c r="I106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>339</v>
+      </c>
+      <c r="B107" t="s">
+        <v>353</v>
+      </c>
+      <c r="C107" t="s">
+        <v>169</v>
+      </c>
+      <c r="D107" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" t="s">
+        <v>169</v>
+      </c>
+      <c r="F107" t="s">
+        <v>354</v>
+      </c>
+      <c r="G107" t="s">
+        <v>355</v>
+      </c>
+      <c r="H107">
+        <v>5</v>
+      </c>
+      <c r="I107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>339</v>
+      </c>
+      <c r="B108" t="s">
+        <v>356</v>
+      </c>
+      <c r="C108" t="s">
+        <v>357</v>
+      </c>
+      <c r="D108" t="s">
+        <v>342</v>
+      </c>
+      <c r="E108" t="s">
+        <v>357</v>
+      </c>
+      <c r="F108" t="s">
+        <v>347</v>
+      </c>
+      <c r="G108" t="s">
+        <v>341</v>
+      </c>
+      <c r="H108">
+        <v>5</v>
+      </c>
+      <c r="I108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>339</v>
+      </c>
+      <c r="B109" t="s">
+        <v>358</v>
+      </c>
+      <c r="C109" t="s">
+        <v>359</v>
+      </c>
+      <c r="D109" t="s">
+        <v>169</v>
+      </c>
+      <c r="E109" t="s">
+        <v>359</v>
+      </c>
+      <c r="F109" t="s">
+        <v>360</v>
+      </c>
+      <c r="G109" t="s">
+        <v>354</v>
+      </c>
+      <c r="H109">
+        <v>5</v>
+      </c>
+      <c r="I109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>339</v>
+      </c>
+      <c r="B110" t="s">
+        <v>361</v>
+      </c>
+      <c r="C110" t="s">
+        <v>362</v>
+      </c>
+      <c r="D110" t="s">
+        <v>14</v>
+      </c>
+      <c r="E110" t="s">
+        <v>362</v>
+      </c>
+      <c r="F110" t="s">
+        <v>363</v>
+      </c>
+      <c r="G110" t="s">
+        <v>13</v>
+      </c>
+      <c r="H110">
+        <v>5</v>
+      </c>
+      <c r="I110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>339</v>
+      </c>
+      <c r="B111" t="s">
+        <v>364</v>
+      </c>
+      <c r="C111" t="s">
+        <v>354</v>
+      </c>
+      <c r="D111" t="s">
+        <v>365</v>
+      </c>
+      <c r="E111" t="s">
+        <v>354</v>
+      </c>
+      <c r="F111" t="s">
+        <v>363</v>
+      </c>
+      <c r="G111" t="s">
+        <v>366</v>
+      </c>
+      <c r="H111">
+        <v>5</v>
+      </c>
+      <c r="I111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" t="s">
+        <v>339</v>
+      </c>
+      <c r="B112" t="s">
+        <v>367</v>
+      </c>
+      <c r="C112" t="s">
+        <v>169</v>
+      </c>
+      <c r="D112" t="s">
+        <v>368</v>
+      </c>
+      <c r="E112" t="s">
+        <v>169</v>
+      </c>
+      <c r="F112" t="s">
+        <v>369</v>
+      </c>
+      <c r="G112" t="s">
+        <v>18</v>
+      </c>
+      <c r="H112">
+        <v>5</v>
+      </c>
+      <c r="I112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" t="s">
+        <v>339</v>
+      </c>
+      <c r="B113" t="s">
+        <v>370</v>
+      </c>
+      <c r="C113" t="s">
+        <v>371</v>
+      </c>
+      <c r="D113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>371</v>
+      </c>
+      <c r="F113" t="s">
+        <v>58</v>
+      </c>
+      <c r="G113" t="s">
+        <v>18</v>
+      </c>
+      <c r="H113">
+        <v>5</v>
+      </c>
+      <c r="I113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>339</v>
+      </c>
+      <c r="B114" t="s">
+        <v>115</v>
+      </c>
+      <c r="C114" t="s">
+        <v>116</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>116</v>
+      </c>
+      <c r="F114" t="s">
+        <v>19</v>
+      </c>
+      <c r="G114" t="s">
+        <v>58</v>
+      </c>
+      <c r="H114">
+        <v>5</v>
+      </c>
+      <c r="I114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" t="s">
+        <v>339</v>
+      </c>
+      <c r="B115" t="s">
+        <v>372</v>
+      </c>
+      <c r="C115">
+        <v>12</v>
+      </c>
+      <c r="D115">
+        <v>10</v>
+      </c>
+      <c r="E115">
+        <v>12</v>
+      </c>
+      <c r="F115">
+        <v>7</v>
+      </c>
+      <c r="G115">
+        <v>15</v>
+      </c>
+      <c r="H115">
+        <v>5</v>
+      </c>
+      <c r="I115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" t="s">
+        <v>339</v>
+      </c>
+      <c r="B116" t="s">
+        <v>373</v>
+      </c>
+      <c r="C116" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" t="s">
+        <v>58</v>
+      </c>
+      <c r="E116" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" t="s">
+        <v>116</v>
+      </c>
+      <c r="G116" t="s">
+        <v>18</v>
+      </c>
+      <c r="H116">
+        <v>5</v>
+      </c>
+      <c r="I116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" t="s">
+        <v>339</v>
+      </c>
+      <c r="B117" t="s">
+        <v>374</v>
+      </c>
+      <c r="C117" t="s">
+        <v>27</v>
+      </c>
+      <c r="D117" t="s">
+        <v>28</v>
+      </c>
+      <c r="E117" t="s">
+        <v>27</v>
+      </c>
+      <c r="F117" t="s">
+        <v>29</v>
+      </c>
+      <c r="G117" t="s">
+        <v>375</v>
+      </c>
+      <c r="H117">
+        <v>5</v>
+      </c>
+      <c r="I117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" t="s">
+        <v>339</v>
+      </c>
+      <c r="B118" t="s">
+        <v>376</v>
+      </c>
+      <c r="C118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" t="s">
+        <v>17</v>
+      </c>
+      <c r="F118" t="s">
+        <v>18</v>
+      </c>
+      <c r="G118" t="s">
+        <v>169</v>
+      </c>
+      <c r="H118">
+        <v>5</v>
+      </c>
+      <c r="I118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" t="s">
+        <v>339</v>
+      </c>
+      <c r="B119" t="s">
+        <v>377</v>
+      </c>
+      <c r="C119" t="s">
+        <v>378</v>
+      </c>
+      <c r="D119" t="s">
+        <v>379</v>
+      </c>
+      <c r="E119" t="s">
+        <v>378</v>
+      </c>
+      <c r="F119" t="s">
+        <v>380</v>
+      </c>
+      <c r="G119" t="s">
+        <v>381</v>
+      </c>
+      <c r="H119">
+        <v>5</v>
+      </c>
+      <c r="I119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" t="s">
+        <v>339</v>
+      </c>
+      <c r="B120" t="s">
+        <v>382</v>
+      </c>
+      <c r="C120" t="s">
+        <v>143</v>
+      </c>
+      <c r="D120" t="s">
+        <v>54</v>
+      </c>
+      <c r="E120" t="s">
+        <v>143</v>
+      </c>
+      <c r="F120" t="s">
+        <v>383</v>
+      </c>
+      <c r="G120" t="s">
+        <v>384</v>
+      </c>
+      <c r="H120">
+        <v>5</v>
+      </c>
+      <c r="I120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" t="s">
+        <v>339</v>
+      </c>
+      <c r="B121" t="s">
+        <v>385</v>
+      </c>
+      <c r="C121" t="s">
+        <v>14</v>
+      </c>
+      <c r="D121" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" t="s">
+        <v>14</v>
+      </c>
+      <c r="F121" t="s">
+        <v>58</v>
+      </c>
+      <c r="G121" t="s">
+        <v>18</v>
+      </c>
+      <c r="H121">
+        <v>5</v>
+      </c>
+      <c r="I121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" t="s">
+        <v>339</v>
+      </c>
+      <c r="B122" t="s">
+        <v>386</v>
+      </c>
+      <c r="C122" t="s">
+        <v>363</v>
+      </c>
+      <c r="D122" t="s">
+        <v>354</v>
+      </c>
+      <c r="E122" t="s">
+        <v>363</v>
+      </c>
+      <c r="F122" t="s">
+        <v>365</v>
+      </c>
+      <c r="G122" t="s">
+        <v>366</v>
+      </c>
+      <c r="H122">
+        <v>5</v>
+      </c>
+      <c r="I122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" t="s">
+        <v>339</v>
+      </c>
+      <c r="B123" t="s">
+        <v>387</v>
+      </c>
+      <c r="C123" t="s">
+        <v>14</v>
+      </c>
+      <c r="D123" t="s">
+        <v>362</v>
+      </c>
+      <c r="E123" t="s">
+        <v>14</v>
+      </c>
+      <c r="F123" t="s">
+        <v>169</v>
+      </c>
+      <c r="G123" t="s">
+        <v>368</v>
+      </c>
+      <c r="H123">
+        <v>5</v>
+      </c>
+      <c r="I123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" t="s">
+        <v>339</v>
+      </c>
+      <c r="B124" t="s">
+        <v>388</v>
+      </c>
+      <c r="C124" t="s">
+        <v>355</v>
+      </c>
+      <c r="D124" t="s">
+        <v>354</v>
+      </c>
+      <c r="E124" t="s">
+        <v>355</v>
+      </c>
+      <c r="F124" t="s">
+        <v>365</v>
+      </c>
+      <c r="G124" t="s">
+        <v>359</v>
+      </c>
+      <c r="H124">
+        <v>5</v>
+      </c>
+      <c r="I124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" t="s">
+        <v>339</v>
+      </c>
+      <c r="B125" t="s">
+        <v>389</v>
+      </c>
+      <c r="C125" t="s">
+        <v>355</v>
+      </c>
+      <c r="D125" t="s">
+        <v>354</v>
+      </c>
+      <c r="E125" t="s">
+        <v>355</v>
+      </c>
+      <c r="F125" t="s">
+        <v>365</v>
+      </c>
+      <c r="G125" t="s">
+        <v>360</v>
+      </c>
+      <c r="H125">
+        <v>5</v>
+      </c>
+      <c r="I125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" t="s">
+        <v>339</v>
+      </c>
+      <c r="B126" t="s">
+        <v>390</v>
+      </c>
+      <c r="C126" t="s">
+        <v>391</v>
+      </c>
+      <c r="D126" t="s">
+        <v>392</v>
+      </c>
+      <c r="E126" t="s">
+        <v>391</v>
+      </c>
+      <c r="F126" t="s">
+        <v>393</v>
+      </c>
+      <c r="G126" t="s">
+        <v>394</v>
+      </c>
+      <c r="H126">
+        <v>5</v>
+      </c>
+      <c r="I126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" t="s">
+        <v>339</v>
+      </c>
+      <c r="B127" t="s">
+        <v>395</v>
+      </c>
+      <c r="C127" t="s">
+        <v>169</v>
+      </c>
+      <c r="D127" t="s">
+        <v>360</v>
+      </c>
+      <c r="E127" t="s">
+        <v>169</v>
+      </c>
+      <c r="F127" t="s">
+        <v>343</v>
+      </c>
+      <c r="G127" t="s">
+        <v>369</v>
+      </c>
+      <c r="H127">
+        <v>5</v>
+      </c>
+      <c r="I127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" t="s">
+        <v>339</v>
+      </c>
+      <c r="B128" t="s">
+        <v>396</v>
+      </c>
+      <c r="C128" t="s">
+        <v>397</v>
+      </c>
+      <c r="D128" t="s">
+        <v>359</v>
+      </c>
+      <c r="E128" t="s">
+        <v>397</v>
+      </c>
+      <c r="F128" t="s">
+        <v>398</v>
+      </c>
+      <c r="G128" t="s">
+        <v>399</v>
+      </c>
+      <c r="H128">
+        <v>5</v>
+      </c>
+      <c r="I128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" t="s">
+        <v>339</v>
+      </c>
+      <c r="B129" t="s">
+        <v>400</v>
+      </c>
+      <c r="C129" t="s">
+        <v>384</v>
+      </c>
+      <c r="D129" t="s">
+        <v>143</v>
+      </c>
+      <c r="E129" t="s">
+        <v>384</v>
+      </c>
+      <c r="F129" t="s">
+        <v>383</v>
+      </c>
+      <c r="G129" t="s">
+        <v>54</v>
+      </c>
+      <c r="H129">
+        <v>5</v>
+      </c>
+      <c r="I129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" t="s">
+        <v>339</v>
+      </c>
+      <c r="B130" t="s">
+        <v>401</v>
+      </c>
+      <c r="C130" t="s">
+        <v>132</v>
+      </c>
+      <c r="D130" t="s">
+        <v>131</v>
+      </c>
+      <c r="E130" t="s">
+        <v>132</v>
+      </c>
+      <c r="F130" t="s">
+        <v>402</v>
+      </c>
+      <c r="G130" t="s">
+        <v>29</v>
+      </c>
+      <c r="H130">
+        <v>5</v>
+      </c>
+      <c r="I130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" t="s">
+        <v>339</v>
+      </c>
+      <c r="B131" t="s">
+        <v>403</v>
+      </c>
+      <c r="C131" t="s">
+        <v>398</v>
+      </c>
+      <c r="D131" t="s">
+        <v>365</v>
+      </c>
+      <c r="E131" t="s">
+        <v>398</v>
+      </c>
+      <c r="F131" t="s">
+        <v>354</v>
+      </c>
+      <c r="G131" t="s">
+        <v>363</v>
+      </c>
+      <c r="H131">
+        <v>5</v>
+      </c>
+      <c r="I131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" t="s">
+        <v>339</v>
+      </c>
+      <c r="B132" t="s">
+        <v>404</v>
+      </c>
+      <c r="C132" t="s">
+        <v>360</v>
+      </c>
+      <c r="D132" t="s">
+        <v>405</v>
+      </c>
+      <c r="E132" t="s">
+        <v>360</v>
+      </c>
+      <c r="F132" t="s">
+        <v>406</v>
+      </c>
+      <c r="G132" t="s">
+        <v>14</v>
+      </c>
+      <c r="H132">
+        <v>5</v>
+      </c>
+      <c r="I132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" t="s">
+        <v>339</v>
+      </c>
+      <c r="B133" t="s">
+        <v>144</v>
+      </c>
+      <c r="C133" t="s">
+        <v>145</v>
+      </c>
+      <c r="D133" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" t="s">
+        <v>145</v>
+      </c>
+      <c r="F133" t="s">
+        <v>58</v>
+      </c>
+      <c r="G133" t="s">
+        <v>18</v>
+      </c>
+      <c r="H133">
+        <v>5</v>
+      </c>
+      <c r="I133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" t="s">
+        <v>339</v>
+      </c>
+      <c r="B134" t="s">
+        <v>407</v>
+      </c>
+      <c r="C134" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" t="s">
+        <v>58</v>
+      </c>
+      <c r="E134" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" t="s">
+        <v>19</v>
+      </c>
+      <c r="G134" t="s">
+        <v>18</v>
+      </c>
+      <c r="H134">
+        <v>5</v>
+      </c>
+      <c r="I134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9">
+      <c r="A135" t="s">
+        <v>339</v>
+      </c>
+      <c r="B135" t="s">
+        <v>408</v>
+      </c>
+      <c r="C135" t="s">
+        <v>409</v>
+      </c>
+      <c r="D135" t="s">
+        <v>410</v>
+      </c>
+      <c r="E135" t="s">
+        <v>409</v>
+      </c>
+      <c r="F135" t="s">
+        <v>122</v>
+      </c>
+      <c r="G135" t="s">
+        <v>411</v>
+      </c>
+      <c r="H135">
+        <v>5</v>
+      </c>
+      <c r="I135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
+      <c r="A136" t="s">
+        <v>339</v>
+      </c>
+      <c r="B136" t="s">
+        <v>412</v>
+      </c>
+      <c r="C136" t="s">
+        <v>365</v>
+      </c>
+      <c r="D136" t="s">
+        <v>354</v>
+      </c>
+      <c r="E136" t="s">
+        <v>365</v>
+      </c>
+      <c r="F136" t="s">
+        <v>355</v>
+      </c>
+      <c r="G136" t="s">
+        <v>413</v>
+      </c>
+      <c r="H136">
+        <v>5</v>
+      </c>
+      <c r="I136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9">
+      <c r="A137" t="s">
+        <v>339</v>
+      </c>
+      <c r="B137" t="s">
+        <v>414</v>
+      </c>
+      <c r="C137" t="s">
+        <v>415</v>
+      </c>
+      <c r="D137" t="s">
+        <v>369</v>
+      </c>
+      <c r="E137" t="s">
+        <v>415</v>
+      </c>
+      <c r="F137" t="s">
+        <v>416</v>
+      </c>
+      <c r="G137" t="s">
+        <v>368</v>
+      </c>
+      <c r="H137">
+        <v>5</v>
+      </c>
+      <c r="I137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
+      <c r="A138" t="s">
+        <v>339</v>
+      </c>
+      <c r="B138" t="s">
+        <v>417</v>
+      </c>
+      <c r="C138" t="s">
+        <v>354</v>
+      </c>
+      <c r="D138" t="s">
+        <v>355</v>
+      </c>
+      <c r="E138" t="s">
+        <v>354</v>
+      </c>
+      <c r="F138" t="s">
+        <v>169</v>
+      </c>
+      <c r="G138" t="s">
+        <v>18</v>
+      </c>
+      <c r="H138">
+        <v>5</v>
+      </c>
+      <c r="I138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
+      <c r="A139" t="s">
+        <v>339</v>
+      </c>
+      <c r="B139" t="s">
+        <v>418</v>
+      </c>
+      <c r="C139" t="s">
+        <v>419</v>
+      </c>
+      <c r="D139" t="s">
+        <v>362</v>
+      </c>
+      <c r="E139" t="s">
+        <v>419</v>
+      </c>
+      <c r="F139" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" t="s">
+        <v>18</v>
+      </c>
+      <c r="H139">
+        <v>5</v>
+      </c>
+      <c r="I139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
+      <c r="A140" t="s">
+        <v>339</v>
+      </c>
+      <c r="B140" t="s">
+        <v>420</v>
+      </c>
+      <c r="C140" t="s">
+        <v>421</v>
+      </c>
+      <c r="D140" t="s">
+        <v>422</v>
+      </c>
+      <c r="E140" t="s">
+        <v>421</v>
+      </c>
+      <c r="F140" t="s">
+        <v>366</v>
+      </c>
+      <c r="G140" t="s">
+        <v>362</v>
+      </c>
+      <c r="H140">
+        <v>5</v>
+      </c>
+      <c r="I140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9">
+      <c r="A141" t="s">
+        <v>339</v>
+      </c>
+      <c r="B141" t="s">
+        <v>423</v>
+      </c>
+      <c r="C141" t="s">
+        <v>424</v>
+      </c>
+      <c r="D141" t="s">
+        <v>18</v>
+      </c>
+      <c r="E141" t="s">
+        <v>424</v>
+      </c>
+      <c r="F141" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" t="s">
+        <v>58</v>
+      </c>
+      <c r="H141">
+        <v>5</v>
+      </c>
+      <c r="I141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9">
+      <c r="A142" t="s">
+        <v>339</v>
+      </c>
+      <c r="B142" t="s">
+        <v>425</v>
+      </c>
+      <c r="C142" t="s">
+        <v>426</v>
+      </c>
+      <c r="D142" t="s">
+        <v>54</v>
+      </c>
+      <c r="E142" t="s">
+        <v>426</v>
+      </c>
+      <c r="F142" t="s">
+        <v>143</v>
+      </c>
+      <c r="G142" t="s">
+        <v>427</v>
+      </c>
+      <c r="H142">
+        <v>5</v>
+      </c>
+      <c r="I142" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" t="s">
+        <v>339</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" t="s">
+        <v>17</v>
+      </c>
+      <c r="F143" t="s">
+        <v>18</v>
+      </c>
+      <c r="G143" t="s">
+        <v>19</v>
+      </c>
+      <c r="H143">
+        <v>5</v>
+      </c>
+      <c r="I143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9">
+      <c r="A144" t="s">
+        <v>339</v>
+      </c>
+      <c r="B144" t="s">
+        <v>428</v>
+      </c>
+      <c r="C144" t="s">
+        <v>19</v>
+      </c>
+      <c r="D144" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" t="s">
+        <v>19</v>
+      </c>
+      <c r="F144" t="s">
+        <v>58</v>
+      </c>
+      <c r="G144" t="s">
+        <v>57</v>
+      </c>
+      <c r="H144">
+        <v>5</v>
+      </c>
+      <c r="I144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9">
+      <c r="A145" t="s">
+        <v>339</v>
+      </c>
+      <c r="B145" t="s">
+        <v>429</v>
+      </c>
+      <c r="C145" t="s">
+        <v>57</v>
+      </c>
+      <c r="D145" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" t="s">
+        <v>57</v>
+      </c>
+      <c r="F145" t="s">
+        <v>58</v>
+      </c>
+      <c r="G145" t="s">
+        <v>59</v>
+      </c>
+      <c r="H145">
+        <v>5</v>
+      </c>
+      <c r="I145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9">
+      <c r="A146" t="s">
+        <v>339</v>
+      </c>
+      <c r="B146" t="s">
+        <v>430</v>
+      </c>
+      <c r="C146" t="s">
+        <v>58</v>
+      </c>
+      <c r="D146" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" t="s">
+        <v>58</v>
+      </c>
+      <c r="F146" t="s">
+        <v>18</v>
+      </c>
+      <c r="G146" t="s">
+        <v>431</v>
+      </c>
+      <c r="H146">
+        <v>5</v>
+      </c>
+      <c r="I146" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
+      <c r="A147" t="s">
+        <v>339</v>
+      </c>
+      <c r="B147" t="s">
+        <v>432</v>
+      </c>
+      <c r="C147" t="s">
+        <v>433</v>
+      </c>
+      <c r="D147" t="s">
+        <v>434</v>
+      </c>
+      <c r="E147" t="s">
+        <v>433</v>
+      </c>
+      <c r="F147" t="s">
+        <v>435</v>
+      </c>
+      <c r="G147" t="s">
+        <v>436</v>
+      </c>
+      <c r="H147">
+        <v>5</v>
+      </c>
+      <c r="I147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
+      <c r="A148" t="s">
+        <v>339</v>
+      </c>
+      <c r="B148" t="s">
+        <v>96</v>
+      </c>
+      <c r="C148" t="s">
+        <v>74</v>
+      </c>
+      <c r="D148" t="s">
+        <v>97</v>
+      </c>
+      <c r="E148" t="s">
+        <v>74</v>
+      </c>
+      <c r="F148" t="s">
+        <v>98</v>
+      </c>
+      <c r="G148" t="s">
+        <v>18</v>
+      </c>
+      <c r="H148">
+        <v>5</v>
+      </c>
+      <c r="I148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
+      <c r="A149" t="s">
+        <v>339</v>
+      </c>
+      <c r="B149" t="s">
+        <v>135</v>
+      </c>
+      <c r="C149">
+        <v>40</v>
+      </c>
+      <c r="D149">
+        <v>7</v>
+      </c>
+      <c r="E149">
+        <v>40</v>
+      </c>
+      <c r="F149">
+        <v>12</v>
+      </c>
+      <c r="G149">
+        <v>30</v>
+      </c>
+      <c r="H149">
+        <v>5</v>
+      </c>
+      <c r="I149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>339</v>
+      </c>
+      <c r="B150" t="s">
+        <v>133</v>
+      </c>
+      <c r="C150" t="s">
+        <v>134</v>
+      </c>
+      <c r="D150" t="s">
+        <v>116</v>
+      </c>
+      <c r="E150" t="s">
+        <v>134</v>
+      </c>
+      <c r="F150" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" t="s">
+        <v>31</v>
+      </c>
+      <c r="H150">
+        <v>5</v>
+      </c>
+      <c r="I150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>339</v>
+      </c>
+      <c r="B151" t="s">
+        <v>437</v>
+      </c>
+      <c r="C151" t="s">
+        <v>153</v>
+      </c>
+      <c r="D151" t="s">
+        <v>66</v>
+      </c>
+      <c r="E151" t="s">
+        <v>153</v>
+      </c>
+      <c r="F151" t="s">
+        <v>65</v>
+      </c>
+      <c r="G151" t="s">
+        <v>64</v>
+      </c>
+      <c r="H151">
+        <v>5</v>
+      </c>
+      <c r="I151" t="b">
+        <v>0</v>
+      </c>
+    </row>
     <row r="527" spans="10:10">
       <c r="J527" t="b">
         <v>0</v>

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="624">
   <si>
     <t>Topic</t>
   </si>
@@ -1341,6 +1341,564 @@
   </si>
   <si>
     <t>What happened three days after Jesus died?</t>
+  </si>
+  <si>
+    <t>American History</t>
+  </si>
+  <si>
+    <t>Who was US President at the start of 1950?</t>
+  </si>
+  <si>
+    <t>Harry Truman</t>
+  </si>
+  <si>
+    <t>Dwight Eisenhower</t>
+  </si>
+  <si>
+    <t>John Kennedy</t>
+  </si>
+  <si>
+    <t>Richard Nixon</t>
+  </si>
+  <si>
+    <t>Which war began in 1950 involving North and South Korea?</t>
+  </si>
+  <si>
+    <t>Korean War</t>
+  </si>
+  <si>
+    <t>Vietnam War</t>
+  </si>
+  <si>
+    <t>Cold War</t>
+  </si>
+  <si>
+    <t>Gulf War</t>
+  </si>
+  <si>
+    <t>Who became US President in 1953?</t>
+  </si>
+  <si>
+    <t>Nixon</t>
+  </si>
+  <si>
+    <t>Truman</t>
+  </si>
+  <si>
+    <t>What movement fought racial segregation in the 1950s and 1960s?</t>
+  </si>
+  <si>
+    <t>Civil Rights Movement</t>
+  </si>
+  <si>
+    <t>Labor Movement</t>
+  </si>
+  <si>
+    <t>Women’s Movement</t>
+  </si>
+  <si>
+    <t>Green Movement</t>
+  </si>
+  <si>
+    <t>Who refused to give up her bus seat in 1955?</t>
+  </si>
+  <si>
+    <t>Rosa Parks</t>
+  </si>
+  <si>
+    <t>Maya Angelou</t>
+  </si>
+  <si>
+    <t>Harriet Tubman</t>
+  </si>
+  <si>
+    <t>Eleanor Roosevelt</t>
+  </si>
+  <si>
+    <t>Which organization fought for civil rights led by Martin Luther King Jr.?</t>
+  </si>
+  <si>
+    <t>SCLC</t>
+  </si>
+  <si>
+    <t>NAACP</t>
+  </si>
+  <si>
+    <t>FBI</t>
+  </si>
+  <si>
+    <t>CIA</t>
+  </si>
+  <si>
+    <t>Who was famous for the “I Have a Dream” speech?</t>
+  </si>
+  <si>
+    <t>Martin Luther King Jr.</t>
+  </si>
+  <si>
+    <t>Malcolm X</t>
+  </si>
+  <si>
+    <t>What was the first artificial satellite launched in 1957?</t>
+  </si>
+  <si>
+    <t>Sputnik</t>
+  </si>
+  <si>
+    <t>Apollo</t>
+  </si>
+  <si>
+    <t>Explorer</t>
+  </si>
+  <si>
+    <t>Hubble</t>
+  </si>
+  <si>
+    <t>Which US agency was created in 1958 for space exploration?</t>
+  </si>
+  <si>
+    <t>NASA</t>
+  </si>
+  <si>
+    <t>NOAA</t>
+  </si>
+  <si>
+    <t>Who became the youngest elected US President in 1961?</t>
+  </si>
+  <si>
+    <t>John F. Kennedy</t>
+  </si>
+  <si>
+    <t>Lyndon Johnson</t>
+  </si>
+  <si>
+    <t>Eisenhower</t>
+  </si>
+  <si>
+    <t>What wall divided East and West Berlin beginning in 1961?</t>
+  </si>
+  <si>
+    <t>Berlin Wall</t>
+  </si>
+  <si>
+    <t>Great Wall</t>
+  </si>
+  <si>
+    <t>Iron Curtain</t>
+  </si>
+  <si>
+    <t>Freedom Wall</t>
+  </si>
+  <si>
+    <t>Which crisis nearly caused nuclear war in 1962?</t>
+  </si>
+  <si>
+    <t>Cuban Missile Crisis</t>
+  </si>
+  <si>
+    <t>Who was assassinated in Dallas in 1963?</t>
+  </si>
+  <si>
+    <t>Robert Kennedy</t>
+  </si>
+  <si>
+    <t>Who became President after JFK’s assassination?</t>
+  </si>
+  <si>
+    <t>Reagan</t>
+  </si>
+  <si>
+    <t>Which law banned racial segregation in public places in 1964?</t>
+  </si>
+  <si>
+    <t>Civil Rights Act</t>
+  </si>
+  <si>
+    <t>Voting Rights Act</t>
+  </si>
+  <si>
+    <t>Fair Housing Act</t>
+  </si>
+  <si>
+    <t>New Deal</t>
+  </si>
+  <si>
+    <t>Which war escalated heavily during the 1960s?</t>
+  </si>
+  <si>
+    <t>Who was famous boxer refusing Vietnam draft?</t>
+  </si>
+  <si>
+    <t>Muhammad Ali</t>
+  </si>
+  <si>
+    <t>Joe Frazier</t>
+  </si>
+  <si>
+    <t>Mike Tyson</t>
+  </si>
+  <si>
+    <t>George Foreman</t>
+  </si>
+  <si>
+    <t>Who was assassinated in 1968 while supporting civil rights?</t>
+  </si>
+  <si>
+    <t>JFK</t>
+  </si>
+  <si>
+    <t>What mission landed first humans on Moon in 1969?</t>
+  </si>
+  <si>
+    <t>Apollo 11</t>
+  </si>
+  <si>
+    <t>Apollo 13</t>
+  </si>
+  <si>
+    <t>Gemini 7</t>
+  </si>
+  <si>
+    <t>Skylab</t>
+  </si>
+  <si>
+    <t>Who was first man on Moon?</t>
+  </si>
+  <si>
+    <t>Neil Armstrong</t>
+  </si>
+  <si>
+    <t>Buzz Aldrin</t>
+  </si>
+  <si>
+    <t>Yuri Gagarin</t>
+  </si>
+  <si>
+    <t>Michael Collins</t>
+  </si>
+  <si>
+    <t>Who was US President during Moon landing?</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Kennedy</t>
+  </si>
+  <si>
+    <t>What scandal forced Nixon to resign?</t>
+  </si>
+  <si>
+    <t>Watergate</t>
+  </si>
+  <si>
+    <t>Iran-Contra</t>
+  </si>
+  <si>
+    <t>Teapot Dome</t>
+  </si>
+  <si>
+    <t>Pentagon Papers</t>
+  </si>
+  <si>
+    <t>Who resigned as US President in 1974?</t>
+  </si>
+  <si>
+    <t>Ford</t>
+  </si>
+  <si>
+    <t>Carter</t>
+  </si>
+  <si>
+    <t>Who became President after Nixon resigned?</t>
+  </si>
+  <si>
+    <t>Gerald Ford</t>
+  </si>
+  <si>
+    <t>Which war officially ended for America in 1975?</t>
+  </si>
+  <si>
+    <t>World War II</t>
+  </si>
+  <si>
+    <t>Who became US President in 1977?</t>
+  </si>
+  <si>
+    <t>Jimmy Carter</t>
+  </si>
+  <si>
+    <t>What event in 1979 involved American hostages in Iran?</t>
+  </si>
+  <si>
+    <t>Iran Hostage Crisis</t>
+  </si>
+  <si>
+    <t>Cuban Crisis</t>
+  </si>
+  <si>
+    <t>Berlin Crisis</t>
+  </si>
+  <si>
+    <t>Which music style became hugely popular in 1970s America?</t>
+  </si>
+  <si>
+    <t>Disco</t>
+  </si>
+  <si>
+    <t>Rock</t>
+  </si>
+  <si>
+    <t>Jazz</t>
+  </si>
+  <si>
+    <t>Blues</t>
+  </si>
+  <si>
+    <t>What movement fought for women’s equality in the 1960s and 70s?</t>
+  </si>
+  <si>
+    <t>Feminist Movement</t>
+  </si>
+  <si>
+    <t>Who wrote “The Feminine Mystique”?</t>
+  </si>
+  <si>
+    <t>Betty Friedan</t>
+  </si>
+  <si>
+    <t>Gloria Steinem</t>
+  </si>
+  <si>
+    <t>Which amendment lowered voting age to 18?</t>
+  </si>
+  <si>
+    <t>26th Amendment</t>
+  </si>
+  <si>
+    <t>19th Amendment</t>
+  </si>
+  <si>
+    <t>21st Amendment</t>
+  </si>
+  <si>
+    <t>15th Amendment</t>
+  </si>
+  <si>
+    <t>Which President opened relations with China in 1972?</t>
+  </si>
+  <si>
+    <t>Which famous music festival happened in 1969?</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Coachella</t>
+  </si>
+  <si>
+    <t>Lollapalooza</t>
+  </si>
+  <si>
+    <t>Burning Man</t>
+  </si>
+  <si>
+    <t>Which civil rights leader promoted Black Power?</t>
+  </si>
+  <si>
+    <t>John Lewis</t>
+  </si>
+  <si>
+    <t>What Supreme Court case ended school segregation?</t>
+  </si>
+  <si>
+    <t>Brown v. Board of Education</t>
+  </si>
+  <si>
+    <t>Roe v. Wade</t>
+  </si>
+  <si>
+    <t>Miranda v. Arizona</t>
+  </si>
+  <si>
+    <t>Plessy v. Ferguson</t>
+  </si>
+  <si>
+    <t>Which law protected voting rights in 1965?</t>
+  </si>
+  <si>
+    <t>Who was famous anti-war activist during Vietnam era?</t>
+  </si>
+  <si>
+    <t>Jane Fonda</t>
+  </si>
+  <si>
+    <t>Marilyn Monroe</t>
+  </si>
+  <si>
+    <t>Betty White</t>
+  </si>
+  <si>
+    <t>Audrey Hepburn</t>
+  </si>
+  <si>
+    <t>What did hippie movement promote in 1960s?</t>
+  </si>
+  <si>
+    <t>Peace and love</t>
+  </si>
+  <si>
+    <t>War and power</t>
+  </si>
+  <si>
+    <t>Industrial growth</t>
+  </si>
+  <si>
+    <t>Capitalism</t>
+  </si>
+  <si>
+    <t>Which company became famous for personal computers in 1970s?</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>Who co-founded Apple in 1976?</t>
+  </si>
+  <si>
+    <t>Steve Jobs</t>
+  </si>
+  <si>
+    <t>Bill Gates</t>
+  </si>
+  <si>
+    <t>Elon Musk</t>
+  </si>
+  <si>
+    <t>Mark Zuckerberg</t>
+  </si>
+  <si>
+    <t>What environmental disaster happened in 1979 nuclear plant?</t>
+  </si>
+  <si>
+    <t>Three Mile Island</t>
+  </si>
+  <si>
+    <t>Chernobyl</t>
+  </si>
+  <si>
+    <t>Fukushima</t>
+  </si>
+  <si>
+    <t>Deepwater Horizon</t>
+  </si>
+  <si>
+    <t>Which amendment guaranteed women right to vote earlier in US history?</t>
+  </si>
+  <si>
+    <t>Who was famous for segregation policies in Alabama?</t>
+  </si>
+  <si>
+    <t>George Wallace</t>
+  </si>
+  <si>
+    <t>Ronald Reagan</t>
+  </si>
+  <si>
+    <t>Barry Goldwater</t>
+  </si>
+  <si>
+    <t>Which war protest event occurred at Kent State University?</t>
+  </si>
+  <si>
+    <t>Shooting of students</t>
+  </si>
+  <si>
+    <t>Boston Massacre</t>
+  </si>
+  <si>
+    <t>Civil Rights March</t>
+  </si>
+  <si>
+    <t>Tea Party</t>
+  </si>
+  <si>
+    <t>What was major fear between USA and USSR called?</t>
+  </si>
+  <si>
+    <t>Hot War</t>
+  </si>
+  <si>
+    <t>Space War</t>
+  </si>
+  <si>
+    <t>Which program helped poor Americans with healthcare in 1965?</t>
+  </si>
+  <si>
+    <t>Medicare</t>
+  </si>
+  <si>
+    <t>Obamacare</t>
+  </si>
+  <si>
+    <t>Medicaid</t>
+  </si>
+  <si>
+    <t>Social Security</t>
+  </si>
+  <si>
+    <t>Who became President in 1980?</t>
+  </si>
+  <si>
+    <t>What energy issue affected America during 1970s?</t>
+  </si>
+  <si>
+    <t>Oil Crisis</t>
+  </si>
+  <si>
+    <t>Bank Crisis</t>
+  </si>
+  <si>
+    <t>Housing Crisis</t>
+  </si>
+  <si>
+    <t>Internet Crash</t>
+  </si>
+  <si>
+    <t>Which famous speech included “Ask not what your country can do for you”?</t>
+  </si>
+  <si>
+    <t>JFK Inaugural Speech</t>
+  </si>
+  <si>
+    <t>MLK Speech</t>
+  </si>
+  <si>
+    <t>Nixon Address</t>
+  </si>
+  <si>
+    <t>Reagan Speech</t>
+  </si>
+  <si>
+    <t>What was the nickname of the 1970s burglary scandal?</t>
+  </si>
+  <si>
+    <t>Which American astronaut walked on Moon with Armstrong?</t>
+  </si>
+  <si>
+    <t>John Glenn</t>
+  </si>
+  <si>
+    <t>Alan Shepard</t>
   </si>
 </sst>
 </file>
@@ -6717,6 +7275,1485 @@
         <v>0</v>
       </c>
     </row>
+    <row r="152" spans="1:9">
+      <c r="A152" t="s">
+        <v>438</v>
+      </c>
+      <c r="B152" t="s">
+        <v>439</v>
+      </c>
+      <c r="C152" t="s">
+        <v>440</v>
+      </c>
+      <c r="D152" t="s">
+        <v>441</v>
+      </c>
+      <c r="E152" t="s">
+        <v>440</v>
+      </c>
+      <c r="F152" t="s">
+        <v>442</v>
+      </c>
+      <c r="G152" t="s">
+        <v>443</v>
+      </c>
+      <c r="H152">
+        <v>5</v>
+      </c>
+      <c r="I152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" t="s">
+        <v>438</v>
+      </c>
+      <c r="B153" t="s">
+        <v>444</v>
+      </c>
+      <c r="C153" t="s">
+        <v>445</v>
+      </c>
+      <c r="D153" t="s">
+        <v>446</v>
+      </c>
+      <c r="E153" t="s">
+        <v>445</v>
+      </c>
+      <c r="F153" t="s">
+        <v>447</v>
+      </c>
+      <c r="G153" t="s">
+        <v>448</v>
+      </c>
+      <c r="H153">
+        <v>5</v>
+      </c>
+      <c r="I153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" t="s">
+        <v>438</v>
+      </c>
+      <c r="B154" t="s">
+        <v>449</v>
+      </c>
+      <c r="C154" t="s">
+        <v>441</v>
+      </c>
+      <c r="D154" t="s">
+        <v>442</v>
+      </c>
+      <c r="E154" t="s">
+        <v>441</v>
+      </c>
+      <c r="F154" t="s">
+        <v>450</v>
+      </c>
+      <c r="G154" t="s">
+        <v>451</v>
+      </c>
+      <c r="H154">
+        <v>5</v>
+      </c>
+      <c r="I154" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" t="s">
+        <v>438</v>
+      </c>
+      <c r="B155" t="s">
+        <v>452</v>
+      </c>
+      <c r="C155" t="s">
+        <v>453</v>
+      </c>
+      <c r="D155" t="s">
+        <v>454</v>
+      </c>
+      <c r="E155" t="s">
+        <v>453</v>
+      </c>
+      <c r="F155" t="s">
+        <v>455</v>
+      </c>
+      <c r="G155" t="s">
+        <v>456</v>
+      </c>
+      <c r="H155">
+        <v>5</v>
+      </c>
+      <c r="I155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" t="s">
+        <v>438</v>
+      </c>
+      <c r="B156" t="s">
+        <v>457</v>
+      </c>
+      <c r="C156" t="s">
+        <v>458</v>
+      </c>
+      <c r="D156" t="s">
+        <v>459</v>
+      </c>
+      <c r="E156" t="s">
+        <v>458</v>
+      </c>
+      <c r="F156" t="s">
+        <v>460</v>
+      </c>
+      <c r="G156" t="s">
+        <v>461</v>
+      </c>
+      <c r="H156">
+        <v>5</v>
+      </c>
+      <c r="I156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" t="s">
+        <v>438</v>
+      </c>
+      <c r="B157" t="s">
+        <v>462</v>
+      </c>
+      <c r="C157" t="s">
+        <v>463</v>
+      </c>
+      <c r="D157" t="s">
+        <v>464</v>
+      </c>
+      <c r="E157" t="s">
+        <v>463</v>
+      </c>
+      <c r="F157" t="s">
+        <v>465</v>
+      </c>
+      <c r="G157" t="s">
+        <v>466</v>
+      </c>
+      <c r="H157">
+        <v>5</v>
+      </c>
+      <c r="I157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" t="s">
+        <v>438</v>
+      </c>
+      <c r="B158" t="s">
+        <v>467</v>
+      </c>
+      <c r="C158" t="s">
+        <v>468</v>
+      </c>
+      <c r="D158" t="s">
+        <v>469</v>
+      </c>
+      <c r="E158" t="s">
+        <v>468</v>
+      </c>
+      <c r="F158" t="s">
+        <v>442</v>
+      </c>
+      <c r="G158" t="s">
+        <v>458</v>
+      </c>
+      <c r="H158">
+        <v>5</v>
+      </c>
+      <c r="I158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" t="s">
+        <v>438</v>
+      </c>
+      <c r="B159" t="s">
+        <v>470</v>
+      </c>
+      <c r="C159" t="s">
+        <v>471</v>
+      </c>
+      <c r="D159" t="s">
+        <v>472</v>
+      </c>
+      <c r="E159" t="s">
+        <v>471</v>
+      </c>
+      <c r="F159" t="s">
+        <v>473</v>
+      </c>
+      <c r="G159" t="s">
+        <v>474</v>
+      </c>
+      <c r="H159">
+        <v>5</v>
+      </c>
+      <c r="I159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" t="s">
+        <v>438</v>
+      </c>
+      <c r="B160" t="s">
+        <v>475</v>
+      </c>
+      <c r="C160" t="s">
+        <v>476</v>
+      </c>
+      <c r="D160" t="s">
+        <v>466</v>
+      </c>
+      <c r="E160" t="s">
+        <v>476</v>
+      </c>
+      <c r="F160" t="s">
+        <v>465</v>
+      </c>
+      <c r="G160" t="s">
+        <v>477</v>
+      </c>
+      <c r="H160">
+        <v>5</v>
+      </c>
+      <c r="I160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" t="s">
+        <v>438</v>
+      </c>
+      <c r="B161" t="s">
+        <v>478</v>
+      </c>
+      <c r="C161" t="s">
+        <v>479</v>
+      </c>
+      <c r="D161" t="s">
+        <v>450</v>
+      </c>
+      <c r="E161" t="s">
+        <v>479</v>
+      </c>
+      <c r="F161" t="s">
+        <v>480</v>
+      </c>
+      <c r="G161" t="s">
+        <v>481</v>
+      </c>
+      <c r="H161">
+        <v>5</v>
+      </c>
+      <c r="I161" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" t="s">
+        <v>438</v>
+      </c>
+      <c r="B162" t="s">
+        <v>482</v>
+      </c>
+      <c r="C162" t="s">
+        <v>483</v>
+      </c>
+      <c r="D162" t="s">
+        <v>484</v>
+      </c>
+      <c r="E162" t="s">
+        <v>483</v>
+      </c>
+      <c r="F162" t="s">
+        <v>485</v>
+      </c>
+      <c r="G162" t="s">
+        <v>486</v>
+      </c>
+      <c r="H162">
+        <v>5</v>
+      </c>
+      <c r="I162" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" t="s">
+        <v>438</v>
+      </c>
+      <c r="B163" t="s">
+        <v>487</v>
+      </c>
+      <c r="C163" t="s">
+        <v>488</v>
+      </c>
+      <c r="D163" t="s">
+        <v>445</v>
+      </c>
+      <c r="E163" t="s">
+        <v>488</v>
+      </c>
+      <c r="F163" t="s">
+        <v>446</v>
+      </c>
+      <c r="G163" t="s">
+        <v>447</v>
+      </c>
+      <c r="H163">
+        <v>5</v>
+      </c>
+      <c r="I163" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" t="s">
+        <v>438</v>
+      </c>
+      <c r="B164" t="s">
+        <v>489</v>
+      </c>
+      <c r="C164" t="s">
+        <v>479</v>
+      </c>
+      <c r="D164" t="s">
+        <v>490</v>
+      </c>
+      <c r="E164" t="s">
+        <v>479</v>
+      </c>
+      <c r="F164" t="s">
+        <v>468</v>
+      </c>
+      <c r="G164" t="s">
+        <v>450</v>
+      </c>
+      <c r="H164">
+        <v>5</v>
+      </c>
+      <c r="I164" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" t="s">
+        <v>438</v>
+      </c>
+      <c r="B165" t="s">
+        <v>491</v>
+      </c>
+      <c r="C165" t="s">
+        <v>480</v>
+      </c>
+      <c r="D165" t="s">
+        <v>450</v>
+      </c>
+      <c r="E165" t="s">
+        <v>480</v>
+      </c>
+      <c r="F165" t="s">
+        <v>481</v>
+      </c>
+      <c r="G165" t="s">
+        <v>492</v>
+      </c>
+      <c r="H165">
+        <v>5</v>
+      </c>
+      <c r="I165" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" t="s">
+        <v>438</v>
+      </c>
+      <c r="B166" t="s">
+        <v>493</v>
+      </c>
+      <c r="C166" t="s">
+        <v>494</v>
+      </c>
+      <c r="D166" t="s">
+        <v>495</v>
+      </c>
+      <c r="E166" t="s">
+        <v>494</v>
+      </c>
+      <c r="F166" t="s">
+        <v>496</v>
+      </c>
+      <c r="G166" t="s">
+        <v>497</v>
+      </c>
+      <c r="H166">
+        <v>5</v>
+      </c>
+      <c r="I166" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" t="s">
+        <v>438</v>
+      </c>
+      <c r="B167" t="s">
+        <v>498</v>
+      </c>
+      <c r="C167" t="s">
+        <v>446</v>
+      </c>
+      <c r="D167" t="s">
+        <v>445</v>
+      </c>
+      <c r="E167" t="s">
+        <v>446</v>
+      </c>
+      <c r="F167" t="s">
+        <v>447</v>
+      </c>
+      <c r="G167" t="s">
+        <v>448</v>
+      </c>
+      <c r="H167">
+        <v>5</v>
+      </c>
+      <c r="I167" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" t="s">
+        <v>438</v>
+      </c>
+      <c r="B168" t="s">
+        <v>499</v>
+      </c>
+      <c r="C168" t="s">
+        <v>500</v>
+      </c>
+      <c r="D168" t="s">
+        <v>501</v>
+      </c>
+      <c r="E168" t="s">
+        <v>500</v>
+      </c>
+      <c r="F168" t="s">
+        <v>502</v>
+      </c>
+      <c r="G168" t="s">
+        <v>503</v>
+      </c>
+      <c r="H168">
+        <v>5</v>
+      </c>
+      <c r="I168" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>438</v>
+      </c>
+      <c r="B169" t="s">
+        <v>504</v>
+      </c>
+      <c r="C169" t="s">
+        <v>468</v>
+      </c>
+      <c r="D169" t="s">
+        <v>469</v>
+      </c>
+      <c r="E169" t="s">
+        <v>468</v>
+      </c>
+      <c r="F169" t="s">
+        <v>505</v>
+      </c>
+      <c r="G169" t="s">
+        <v>490</v>
+      </c>
+      <c r="H169">
+        <v>5</v>
+      </c>
+      <c r="I169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>438</v>
+      </c>
+      <c r="B170" t="s">
+        <v>506</v>
+      </c>
+      <c r="C170" t="s">
+        <v>507</v>
+      </c>
+      <c r="D170" t="s">
+        <v>508</v>
+      </c>
+      <c r="E170" t="s">
+        <v>507</v>
+      </c>
+      <c r="F170" t="s">
+        <v>509</v>
+      </c>
+      <c r="G170" t="s">
+        <v>510</v>
+      </c>
+      <c r="H170">
+        <v>5</v>
+      </c>
+      <c r="I170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" t="s">
+        <v>438</v>
+      </c>
+      <c r="B171" t="s">
+        <v>511</v>
+      </c>
+      <c r="C171" t="s">
+        <v>512</v>
+      </c>
+      <c r="D171" t="s">
+        <v>513</v>
+      </c>
+      <c r="E171" t="s">
+        <v>512</v>
+      </c>
+      <c r="F171" t="s">
+        <v>514</v>
+      </c>
+      <c r="G171" t="s">
+        <v>515</v>
+      </c>
+      <c r="H171">
+        <v>5</v>
+      </c>
+      <c r="I171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="A172" t="s">
+        <v>438</v>
+      </c>
+      <c r="B172" t="s">
+        <v>516</v>
+      </c>
+      <c r="C172" t="s">
+        <v>443</v>
+      </c>
+      <c r="D172" t="s">
+        <v>517</v>
+      </c>
+      <c r="E172" t="s">
+        <v>443</v>
+      </c>
+      <c r="F172" t="s">
+        <v>518</v>
+      </c>
+      <c r="G172" t="s">
+        <v>492</v>
+      </c>
+      <c r="H172">
+        <v>5</v>
+      </c>
+      <c r="I172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" t="s">
+        <v>438</v>
+      </c>
+      <c r="B173" t="s">
+        <v>519</v>
+      </c>
+      <c r="C173" t="s">
+        <v>520</v>
+      </c>
+      <c r="D173" t="s">
+        <v>521</v>
+      </c>
+      <c r="E173" t="s">
+        <v>520</v>
+      </c>
+      <c r="F173" t="s">
+        <v>522</v>
+      </c>
+      <c r="G173" t="s">
+        <v>523</v>
+      </c>
+      <c r="H173">
+        <v>5</v>
+      </c>
+      <c r="I173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" t="s">
+        <v>438</v>
+      </c>
+      <c r="B174" t="s">
+        <v>524</v>
+      </c>
+      <c r="C174" t="s">
+        <v>443</v>
+      </c>
+      <c r="D174" t="s">
+        <v>525</v>
+      </c>
+      <c r="E174" t="s">
+        <v>443</v>
+      </c>
+      <c r="F174" t="s">
+        <v>526</v>
+      </c>
+      <c r="G174" t="s">
+        <v>492</v>
+      </c>
+      <c r="H174">
+        <v>5</v>
+      </c>
+      <c r="I174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" t="s">
+        <v>438</v>
+      </c>
+      <c r="B175" t="s">
+        <v>527</v>
+      </c>
+      <c r="C175" t="s">
+        <v>528</v>
+      </c>
+      <c r="D175" t="s">
+        <v>526</v>
+      </c>
+      <c r="E175" t="s">
+        <v>528</v>
+      </c>
+      <c r="F175" t="s">
+        <v>517</v>
+      </c>
+      <c r="G175" t="s">
+        <v>492</v>
+      </c>
+      <c r="H175">
+        <v>5</v>
+      </c>
+      <c r="I175" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" t="s">
+        <v>438</v>
+      </c>
+      <c r="B176" t="s">
+        <v>529</v>
+      </c>
+      <c r="C176" t="s">
+        <v>446</v>
+      </c>
+      <c r="D176" t="s">
+        <v>445</v>
+      </c>
+      <c r="E176" t="s">
+        <v>446</v>
+      </c>
+      <c r="F176" t="s">
+        <v>447</v>
+      </c>
+      <c r="G176" t="s">
+        <v>530</v>
+      </c>
+      <c r="H176">
+        <v>5</v>
+      </c>
+      <c r="I176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" t="s">
+        <v>438</v>
+      </c>
+      <c r="B177" t="s">
+        <v>531</v>
+      </c>
+      <c r="C177" t="s">
+        <v>532</v>
+      </c>
+      <c r="D177" t="s">
+        <v>525</v>
+      </c>
+      <c r="E177" t="s">
+        <v>532</v>
+      </c>
+      <c r="F177" t="s">
+        <v>492</v>
+      </c>
+      <c r="G177" t="s">
+        <v>450</v>
+      </c>
+      <c r="H177">
+        <v>5</v>
+      </c>
+      <c r="I177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" t="s">
+        <v>438</v>
+      </c>
+      <c r="B178" t="s">
+        <v>533</v>
+      </c>
+      <c r="C178" t="s">
+        <v>534</v>
+      </c>
+      <c r="D178" t="s">
+        <v>535</v>
+      </c>
+      <c r="E178" t="s">
+        <v>534</v>
+      </c>
+      <c r="F178" t="s">
+        <v>520</v>
+      </c>
+      <c r="G178" t="s">
+        <v>536</v>
+      </c>
+      <c r="H178">
+        <v>5</v>
+      </c>
+      <c r="I178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="A179" t="s">
+        <v>438</v>
+      </c>
+      <c r="B179" t="s">
+        <v>537</v>
+      </c>
+      <c r="C179" t="s">
+        <v>538</v>
+      </c>
+      <c r="D179" t="s">
+        <v>539</v>
+      </c>
+      <c r="E179" t="s">
+        <v>538</v>
+      </c>
+      <c r="F179" t="s">
+        <v>540</v>
+      </c>
+      <c r="G179" t="s">
+        <v>541</v>
+      </c>
+      <c r="H179">
+        <v>5</v>
+      </c>
+      <c r="I179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" t="s">
+        <v>438</v>
+      </c>
+      <c r="B180" t="s">
+        <v>542</v>
+      </c>
+      <c r="C180" t="s">
+        <v>543</v>
+      </c>
+      <c r="D180" t="s">
+        <v>453</v>
+      </c>
+      <c r="E180" t="s">
+        <v>543</v>
+      </c>
+      <c r="F180" t="s">
+        <v>456</v>
+      </c>
+      <c r="G180" t="s">
+        <v>454</v>
+      </c>
+      <c r="H180">
+        <v>5</v>
+      </c>
+      <c r="I180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" t="s">
+        <v>438</v>
+      </c>
+      <c r="B181" t="s">
+        <v>544</v>
+      </c>
+      <c r="C181" t="s">
+        <v>545</v>
+      </c>
+      <c r="D181" t="s">
+        <v>546</v>
+      </c>
+      <c r="E181" t="s">
+        <v>545</v>
+      </c>
+      <c r="F181" t="s">
+        <v>461</v>
+      </c>
+      <c r="G181" t="s">
+        <v>458</v>
+      </c>
+      <c r="H181">
+        <v>5</v>
+      </c>
+      <c r="I181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" t="s">
+        <v>438</v>
+      </c>
+      <c r="B182" t="s">
+        <v>547</v>
+      </c>
+      <c r="C182" t="s">
+        <v>548</v>
+      </c>
+      <c r="D182" t="s">
+        <v>549</v>
+      </c>
+      <c r="E182" t="s">
+        <v>548</v>
+      </c>
+      <c r="F182" t="s">
+        <v>550</v>
+      </c>
+      <c r="G182" t="s">
+        <v>551</v>
+      </c>
+      <c r="H182">
+        <v>5</v>
+      </c>
+      <c r="I182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" t="s">
+        <v>438</v>
+      </c>
+      <c r="B183" t="s">
+        <v>552</v>
+      </c>
+      <c r="C183" t="s">
+        <v>443</v>
+      </c>
+      <c r="D183" t="s">
+        <v>492</v>
+      </c>
+      <c r="E183" t="s">
+        <v>443</v>
+      </c>
+      <c r="F183" t="s">
+        <v>526</v>
+      </c>
+      <c r="G183" t="s">
+        <v>517</v>
+      </c>
+      <c r="H183">
+        <v>5</v>
+      </c>
+      <c r="I183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" t="s">
+        <v>438</v>
+      </c>
+      <c r="B184" t="s">
+        <v>553</v>
+      </c>
+      <c r="C184" t="s">
+        <v>554</v>
+      </c>
+      <c r="D184" t="s">
+        <v>555</v>
+      </c>
+      <c r="E184" t="s">
+        <v>554</v>
+      </c>
+      <c r="F184" t="s">
+        <v>556</v>
+      </c>
+      <c r="G184" t="s">
+        <v>557</v>
+      </c>
+      <c r="H184">
+        <v>5</v>
+      </c>
+      <c r="I184" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" t="s">
+        <v>438</v>
+      </c>
+      <c r="B185" t="s">
+        <v>558</v>
+      </c>
+      <c r="C185" t="s">
+        <v>469</v>
+      </c>
+      <c r="D185" t="s">
+        <v>468</v>
+      </c>
+      <c r="E185" t="s">
+        <v>469</v>
+      </c>
+      <c r="F185" t="s">
+        <v>458</v>
+      </c>
+      <c r="G185" t="s">
+        <v>559</v>
+      </c>
+      <c r="H185">
+        <v>5</v>
+      </c>
+      <c r="I185" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" t="s">
+        <v>438</v>
+      </c>
+      <c r="B186" t="s">
+        <v>560</v>
+      </c>
+      <c r="C186" t="s">
+        <v>561</v>
+      </c>
+      <c r="D186" t="s">
+        <v>562</v>
+      </c>
+      <c r="E186" t="s">
+        <v>561</v>
+      </c>
+      <c r="F186" t="s">
+        <v>563</v>
+      </c>
+      <c r="G186" t="s">
+        <v>564</v>
+      </c>
+      <c r="H186">
+        <v>5</v>
+      </c>
+      <c r="I186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" t="s">
+        <v>438</v>
+      </c>
+      <c r="B187" t="s">
+        <v>565</v>
+      </c>
+      <c r="C187" t="s">
+        <v>495</v>
+      </c>
+      <c r="D187" t="s">
+        <v>494</v>
+      </c>
+      <c r="E187" t="s">
+        <v>495</v>
+      </c>
+      <c r="F187" t="s">
+        <v>496</v>
+      </c>
+      <c r="G187" t="s">
+        <v>497</v>
+      </c>
+      <c r="H187">
+        <v>5</v>
+      </c>
+      <c r="I187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" t="s">
+        <v>438</v>
+      </c>
+      <c r="B188" t="s">
+        <v>566</v>
+      </c>
+      <c r="C188" t="s">
+        <v>567</v>
+      </c>
+      <c r="D188" t="s">
+        <v>568</v>
+      </c>
+      <c r="E188" t="s">
+        <v>567</v>
+      </c>
+      <c r="F188" t="s">
+        <v>569</v>
+      </c>
+      <c r="G188" t="s">
+        <v>570</v>
+      </c>
+      <c r="H188">
+        <v>5</v>
+      </c>
+      <c r="I188" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" t="s">
+        <v>438</v>
+      </c>
+      <c r="B189" t="s">
+        <v>571</v>
+      </c>
+      <c r="C189" t="s">
+        <v>572</v>
+      </c>
+      <c r="D189" t="s">
+        <v>573</v>
+      </c>
+      <c r="E189" t="s">
+        <v>572</v>
+      </c>
+      <c r="F189" t="s">
+        <v>574</v>
+      </c>
+      <c r="G189" t="s">
+        <v>575</v>
+      </c>
+      <c r="H189">
+        <v>5</v>
+      </c>
+      <c r="I189" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" t="s">
+        <v>438</v>
+      </c>
+      <c r="B190" t="s">
+        <v>576</v>
+      </c>
+      <c r="C190" t="s">
+        <v>577</v>
+      </c>
+      <c r="D190" t="s">
+        <v>578</v>
+      </c>
+      <c r="E190" t="s">
+        <v>577</v>
+      </c>
+      <c r="F190" t="s">
+        <v>579</v>
+      </c>
+      <c r="G190" t="s">
+        <v>580</v>
+      </c>
+      <c r="H190">
+        <v>5</v>
+      </c>
+      <c r="I190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" t="s">
+        <v>438</v>
+      </c>
+      <c r="B191" t="s">
+        <v>581</v>
+      </c>
+      <c r="C191" t="s">
+        <v>582</v>
+      </c>
+      <c r="D191" t="s">
+        <v>583</v>
+      </c>
+      <c r="E191" t="s">
+        <v>582</v>
+      </c>
+      <c r="F191" t="s">
+        <v>584</v>
+      </c>
+      <c r="G191" t="s">
+        <v>585</v>
+      </c>
+      <c r="H191">
+        <v>5</v>
+      </c>
+      <c r="I191" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" t="s">
+        <v>438</v>
+      </c>
+      <c r="B192" t="s">
+        <v>586</v>
+      </c>
+      <c r="C192" t="s">
+        <v>587</v>
+      </c>
+      <c r="D192" t="s">
+        <v>588</v>
+      </c>
+      <c r="E192" t="s">
+        <v>587</v>
+      </c>
+      <c r="F192" t="s">
+        <v>589</v>
+      </c>
+      <c r="G192" t="s">
+        <v>590</v>
+      </c>
+      <c r="H192">
+        <v>5</v>
+      </c>
+      <c r="I192" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" t="s">
+        <v>438</v>
+      </c>
+      <c r="B193" t="s">
+        <v>591</v>
+      </c>
+      <c r="C193" t="s">
+        <v>549</v>
+      </c>
+      <c r="D193" t="s">
+        <v>551</v>
+      </c>
+      <c r="E193" t="s">
+        <v>549</v>
+      </c>
+      <c r="F193" t="s">
+        <v>550</v>
+      </c>
+      <c r="G193" t="s">
+        <v>548</v>
+      </c>
+      <c r="H193">
+        <v>5</v>
+      </c>
+      <c r="I193" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" t="s">
+        <v>438</v>
+      </c>
+      <c r="B194" t="s">
+        <v>592</v>
+      </c>
+      <c r="C194" t="s">
+        <v>593</v>
+      </c>
+      <c r="D194" t="s">
+        <v>594</v>
+      </c>
+      <c r="E194" t="s">
+        <v>593</v>
+      </c>
+      <c r="F194" t="s">
+        <v>532</v>
+      </c>
+      <c r="G194" t="s">
+        <v>595</v>
+      </c>
+      <c r="H194">
+        <v>5</v>
+      </c>
+      <c r="I194" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" t="s">
+        <v>438</v>
+      </c>
+      <c r="B195" t="s">
+        <v>596</v>
+      </c>
+      <c r="C195" t="s">
+        <v>597</v>
+      </c>
+      <c r="D195" t="s">
+        <v>598</v>
+      </c>
+      <c r="E195" t="s">
+        <v>597</v>
+      </c>
+      <c r="F195" t="s">
+        <v>599</v>
+      </c>
+      <c r="G195" t="s">
+        <v>600</v>
+      </c>
+      <c r="H195">
+        <v>5</v>
+      </c>
+      <c r="I195" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" t="s">
+        <v>438</v>
+      </c>
+      <c r="B196" t="s">
+        <v>601</v>
+      </c>
+      <c r="C196" t="s">
+        <v>447</v>
+      </c>
+      <c r="D196" t="s">
+        <v>602</v>
+      </c>
+      <c r="E196" t="s">
+        <v>447</v>
+      </c>
+      <c r="F196" t="s">
+        <v>603</v>
+      </c>
+      <c r="G196" t="s">
+        <v>445</v>
+      </c>
+      <c r="H196">
+        <v>5</v>
+      </c>
+      <c r="I196" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" t="s">
+        <v>438</v>
+      </c>
+      <c r="B197" t="s">
+        <v>604</v>
+      </c>
+      <c r="C197" t="s">
+        <v>605</v>
+      </c>
+      <c r="D197" t="s">
+        <v>606</v>
+      </c>
+      <c r="E197" t="s">
+        <v>605</v>
+      </c>
+      <c r="F197" t="s">
+        <v>607</v>
+      </c>
+      <c r="G197" t="s">
+        <v>608</v>
+      </c>
+      <c r="H197">
+        <v>5</v>
+      </c>
+      <c r="I197" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" t="s">
+        <v>438</v>
+      </c>
+      <c r="B198" t="s">
+        <v>609</v>
+      </c>
+      <c r="C198" t="s">
+        <v>594</v>
+      </c>
+      <c r="D198" t="s">
+        <v>532</v>
+      </c>
+      <c r="E198" t="s">
+        <v>594</v>
+      </c>
+      <c r="F198" t="s">
+        <v>525</v>
+      </c>
+      <c r="G198" t="s">
+        <v>450</v>
+      </c>
+      <c r="H198">
+        <v>5</v>
+      </c>
+      <c r="I198" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" t="s">
+        <v>438</v>
+      </c>
+      <c r="B199" t="s">
+        <v>610</v>
+      </c>
+      <c r="C199" t="s">
+        <v>611</v>
+      </c>
+      <c r="D199" t="s">
+        <v>612</v>
+      </c>
+      <c r="E199" t="s">
+        <v>611</v>
+      </c>
+      <c r="F199" t="s">
+        <v>613</v>
+      </c>
+      <c r="G199" t="s">
+        <v>614</v>
+      </c>
+      <c r="H199">
+        <v>5</v>
+      </c>
+      <c r="I199" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" t="s">
+        <v>438</v>
+      </c>
+      <c r="B200" t="s">
+        <v>615</v>
+      </c>
+      <c r="C200" t="s">
+        <v>616</v>
+      </c>
+      <c r="D200" t="s">
+        <v>617</v>
+      </c>
+      <c r="E200" t="s">
+        <v>616</v>
+      </c>
+      <c r="F200" t="s">
+        <v>618</v>
+      </c>
+      <c r="G200" t="s">
+        <v>619</v>
+      </c>
+      <c r="H200">
+        <v>5</v>
+      </c>
+      <c r="I200" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201" t="s">
+        <v>438</v>
+      </c>
+      <c r="B201" t="s">
+        <v>620</v>
+      </c>
+      <c r="C201" t="s">
+        <v>520</v>
+      </c>
+      <c r="D201" t="s">
+        <v>522</v>
+      </c>
+      <c r="E201" t="s">
+        <v>520</v>
+      </c>
+      <c r="F201" t="s">
+        <v>521</v>
+      </c>
+      <c r="G201" t="s">
+        <v>523</v>
+      </c>
+      <c r="H201">
+        <v>5</v>
+      </c>
+      <c r="I201" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202" t="s">
+        <v>438</v>
+      </c>
+      <c r="B202" t="s">
+        <v>621</v>
+      </c>
+      <c r="C202" t="s">
+        <v>513</v>
+      </c>
+      <c r="D202" t="s">
+        <v>515</v>
+      </c>
+      <c r="E202" t="s">
+        <v>513</v>
+      </c>
+      <c r="F202" t="s">
+        <v>622</v>
+      </c>
+      <c r="G202" t="s">
+        <v>623</v>
+      </c>
+      <c r="H202">
+        <v>5</v>
+      </c>
+      <c r="I202" t="b">
+        <v>0</v>
+      </c>
+    </row>
     <row r="527" spans="10:10">
       <c r="J527" t="b">
         <v>0</v>

--- a/quiz_template/data/quizzes_text.xlsx
+++ b/quiz_template/data/quizzes_text.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6780"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="798">
   <si>
     <t>Topic</t>
   </si>
@@ -1049,115 +1049,475 @@
     <t>Bible</t>
   </si>
   <si>
-    <t>What is the longest book in the Bible?</t>
-  </si>
-  <si>
-    <t>Psalms</t>
-  </si>
-  <si>
-    <t>Genesis</t>
+    <t>Who built an altar after seeing angels ascending to heaven?</t>
+  </si>
+  <si>
+    <t>Jacob</t>
+  </si>
+  <si>
+    <t>Isaac</t>
+  </si>
+  <si>
+    <t>Abraham</t>
+  </si>
+  <si>
+    <t>Who slept in a den of lions and survived?</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Samson</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Who challenged prophets of Baal on Mount Carmel?</t>
+  </si>
+  <si>
+    <t>Elijah</t>
+  </si>
+  <si>
+    <t>Elisha</t>
   </si>
   <si>
     <t>Isaiah</t>
   </si>
   <si>
-    <t>Exodus</t>
-  </si>
-  <si>
-    <t>What is the shortest book in the Bible?</t>
-  </si>
-  <si>
-    <t>3 John</t>
-  </si>
-  <si>
-    <t>Jude</t>
-  </si>
-  <si>
-    <t>Obadiah</t>
-  </si>
-  <si>
-    <t>Philemon</t>
-  </si>
-  <si>
-    <t>How many books are in the Bible?</t>
-  </si>
-  <si>
-    <t>How many books are in the New Testament?</t>
-  </si>
-  <si>
-    <t>How many books are in the Old Testament?</t>
-  </si>
-  <si>
-    <t>Who wrote the first five books of Bible?</t>
-  </si>
-  <si>
-    <t>David</t>
+    <t>Jeremiah</t>
+  </si>
+  <si>
+    <t>Who asked Jesus “What is truth?”</t>
+  </si>
+  <si>
+    <t>Pontius Pilate</t>
+  </si>
+  <si>
+    <t>Caiaphas</t>
+  </si>
+  <si>
+    <t>Who climbed Mount Sinai to receive commandments?</t>
+  </si>
+  <si>
+    <t>Aaron</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>Who replaced Judas among the disciples?</t>
+  </si>
+  <si>
+    <t>Matthias</t>
+  </si>
+  <si>
+    <t>Barnabas</t>
+  </si>
+  <si>
+    <t>Luke</t>
+  </si>
+  <si>
+    <t>Who was thrown into sea during storm to calm waters?</t>
+  </si>
+  <si>
+    <t>Jonah</t>
+  </si>
+  <si>
+    <t>Who interpreted handwriting on palace wall?</t>
+  </si>
+  <si>
+    <t>Who prayed for wisdom instead of riches?</t>
   </si>
   <si>
     <t>Solomon</t>
   </si>
   <si>
-    <t>What is the final book of Bible?</t>
-  </si>
-  <si>
-    <t>Revelation</t>
-  </si>
-  <si>
-    <t>Who built the giant ark?</t>
+    <t>Saul</t>
+  </si>
+  <si>
+    <t>Who saw dry bones come alive in vision?</t>
+  </si>
+  <si>
+    <t>Ezekiel</t>
+  </si>
+  <si>
+    <t>Who was blinded by heavenly light on road to Damascus?</t>
+  </si>
+  <si>
+    <t>Who hid Israelite spies in Jericho?</t>
+  </si>
+  <si>
+    <t>Rahab</t>
+  </si>
+  <si>
+    <t>Esther</t>
+  </si>
+  <si>
+    <t>Deborah</t>
+  </si>
+  <si>
+    <t>Who lost his strength after hair was cut?</t>
+  </si>
+  <si>
+    <t>Absalom</t>
+  </si>
+  <si>
+    <t>Who built the golden calf while Moses was away?</t>
+  </si>
+  <si>
+    <t>Caleb</t>
+  </si>
+  <si>
+    <t>Who prayed inside a giant fish?</t>
   </si>
   <si>
     <t>Noah</t>
   </si>
   <si>
-    <t>Abraham</t>
-  </si>
-  <si>
-    <t>Who was thrown into lion’s den?</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Samson</t>
-  </si>
-  <si>
-    <t>Who defeated giant Goliath?</t>
-  </si>
-  <si>
-    <t>Saul</t>
-  </si>
-  <si>
-    <t>Joshua</t>
+    <t>Who asked for Jesus’ body after crucifixion?</t>
+  </si>
+  <si>
+    <t>Who was chosen to replace Queen Vashti?</t>
+  </si>
+  <si>
+    <t>Who fell asleep and fell from a window while Paul preached?</t>
+  </si>
+  <si>
+    <t>Eutychus</t>
+  </si>
+  <si>
+    <t>Timothy</t>
+  </si>
+  <si>
+    <t>Who was called “a man after God’s own heart”?</t>
+  </si>
+  <si>
+    <t>Who became blind after disobeying prophet Elisha?</t>
+  </si>
+  <si>
+    <t>Gehazi</t>
+  </si>
+  <si>
+    <t>Naaman</t>
+  </si>
+  <si>
+    <t>Who climbed sycamore tree to see Jesus?</t>
+  </si>
+  <si>
+    <t>Who wrote most of the New Testament letters?</t>
+  </si>
+  <si>
+    <t>Who survived the fiery furnace with three Hebrews?</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>Who heard God speak through burning bush?</t>
+  </si>
+  <si>
+    <t>Who was thrown into prison with Silas?</t>
+  </si>
+  <si>
+    <t>Who was healed after washing seven times in Jordan River?</t>
+  </si>
+  <si>
+    <t>Who dreamt about cows and famine in Egypt?</t>
+  </si>
+  <si>
+    <t>Pharaoh</t>
+  </si>
+  <si>
+    <t>Nebuchadnezzar</t>
+  </si>
+  <si>
+    <t>Darius</t>
+  </si>
+  <si>
+    <t>Who asked Jesus to remember him on the cross?</t>
+  </si>
+  <si>
+    <t>Repentant thief</t>
+  </si>
+  <si>
+    <t>Who was first Christian martyr?</t>
+  </si>
+  <si>
+    <t>Who was called “the rock” by Jesus?</t>
+  </si>
+  <si>
+    <t>Who fell from heaven because of pride according to Bible tradition?</t>
+  </si>
+  <si>
+    <t>Lucifer</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Gabriel</t>
+  </si>
+  <si>
+    <t>Who became queen and risked life before king?</t>
+  </si>
+  <si>
+    <t>Who led worship with harp before King Saul?</t>
+  </si>
+  <si>
+    <t>Asaph</t>
+  </si>
+  <si>
+    <t>Who prayed and sun stood still in battle?</t>
+  </si>
+  <si>
+    <t>Gideon</t>
+  </si>
+  <si>
+    <t>Who saw a giant sheet descending from heaven in vision?</t>
+  </si>
+  <si>
+    <t>Who escaped Egypt with baby Jesus?</t>
+  </si>
+  <si>
+    <t>Who baptized Ethiopian official on desert road?</t>
+  </si>
+  <si>
+    <t>Who touched Ark of Covenant and died instantly?</t>
+  </si>
+  <si>
+    <t>Uzzah</t>
+  </si>
+  <si>
+    <t>Who became queen after winning beauty contest in Persia?</t>
+  </si>
+  <si>
+    <t>Who was known for interpreting dreams in Babylon?</t>
+  </si>
+  <si>
+    <t>Who was lowered through roof to meet Jesus?</t>
+  </si>
+  <si>
+    <t>Paralyzed man</t>
+  </si>
+  <si>
+    <t>Who lost everything but remained faithful to God?</t>
+  </si>
+  <si>
+    <t>Job</t>
+  </si>
+  <si>
+    <t>Who struck giant Goliath with sling stone?</t>
+  </si>
+  <si>
+    <t>Jonathan</t>
+  </si>
+  <si>
+    <t>Who was known as beloved disciple?</t>
+  </si>
+  <si>
+    <t>Who doubted Jesus’ resurrection until seeing wounds?</t>
+  </si>
+  <si>
+    <t>Who was famous tax collector that became disciple?</t>
+  </si>
+  <si>
+    <t>Who saw Jesus transfigured on mountain?</t>
+  </si>
+  <si>
+    <t>Peter James John</t>
+  </si>
+  <si>
+    <t>Who was chained in prison when angel freed him?</t>
+  </si>
+  <si>
+    <t>Who was prophet taken to heaven in whirlwind?</t>
+  </si>
+  <si>
+    <t>Who survived shipwreck while traveling to Rome?</t>
+  </si>
+  <si>
+    <t>Who built the ark before the great flood?</t>
+  </si>
+  <si>
+    <t>Who received the Ten Commandments from God?</t>
+  </si>
+  <si>
+    <t>Who defeated giant Goliath with a sling?</t>
+  </si>
+  <si>
+    <t>Who was swallowed by a great fish?</t>
+  </si>
+  <si>
+    <t>Who was thrown into the lion’s den?</t>
+  </si>
+  <si>
+    <t>Who built the temple in Jerusalem?</t>
+  </si>
+  <si>
+    <t>Who was known as the wisest king?</t>
+  </si>
+  <si>
+    <t>Who led Israelites out of Egypt?</t>
+  </si>
+  <si>
+    <t>Who was first man created by God?</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Cain</t>
+  </si>
+  <si>
+    <t>Abel</t>
+  </si>
+  <si>
+    <t>Who was first woman created by God?</t>
+  </si>
+  <si>
+    <t>Eve</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>What garden did Adam and Eve live in?</t>
+  </si>
+  <si>
+    <t>Babylon</t>
+  </si>
+  <si>
+    <t>Who betrayed Jesus for thirty silver coins?</t>
+  </si>
+  <si>
+    <t>Who denied Jesus three times?</t>
+  </si>
+  <si>
+    <t>Who baptized Jesus in the Jordan River?</t>
+  </si>
+  <si>
+    <t>Where was Jesus born?</t>
+  </si>
+  <si>
+    <t>Rome</t>
+  </si>
+  <si>
+    <t>Who was mother of Jesus?</t>
+  </si>
+  <si>
+    <t>Who was earthly father of Jesus?</t>
+  </si>
+  <si>
+    <t>How many disciples did Jesus have?</t>
+  </si>
+  <si>
+    <t>Who walked on water with Jesus?</t>
+  </si>
+  <si>
+    <t>Who wrote many Psalms in the Bible?</t>
+  </si>
+  <si>
+    <t>Who survived the fiery furnace unharmed?</t>
+  </si>
+  <si>
+    <t>Shadrach Meshach Abednego</t>
+  </si>
+  <si>
+    <t>Who was famous for patience during suffering?</t>
+  </si>
+  <si>
+    <t>What was Jesus’ first miracle?</t>
+  </si>
+  <si>
+    <t>Turning water into wine</t>
+  </si>
+  <si>
+    <t>Healing blind</t>
+  </si>
+  <si>
+    <t>Feeding crowd</t>
   </si>
   <si>
     <t>Who parted the Red Sea?</t>
   </si>
   <si>
-    <t>Aaron</t>
-  </si>
-  <si>
-    <t>Elijah</t>
-  </si>
-  <si>
-    <t>Who was swallowed by a great fish?</t>
-  </si>
-  <si>
-    <t>Jonah</t>
-  </si>
-  <si>
-    <t>How many disciples did Jesus have?</t>
-  </si>
-  <si>
-    <t>Who denied Jesus three times?</t>
-  </si>
-  <si>
-    <t>What city was Jesus born in?</t>
-  </si>
-  <si>
-    <t>Rome</t>
-  </si>
-  <si>
-    <t>Who baptized Jesus?</t>
+    <t>Who interpreted Pharaoh’s dreams?</t>
+  </si>
+  <si>
+    <t>Who became queen and saved the Jewish people?</t>
+  </si>
+  <si>
+    <t>Who saw a burning bush that was not consumed?</t>
+  </si>
+  <si>
+    <t>Who was strongest man in the Bible?</t>
+  </si>
+  <si>
+    <t>Who was first king of Israel?</t>
+  </si>
+  <si>
+    <t>Who anointed David as king?</t>
+  </si>
+  <si>
+    <t>Nathan</t>
+  </si>
+  <si>
+    <t>Who was father of many nations?</t>
+  </si>
+  <si>
+    <t>Who dreamed of ladder reaching heaven?</t>
+  </si>
+  <si>
+    <t>Who was sold into Egypt by his brothers?</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>Reuben</t>
+  </si>
+  <si>
+    <t>Who rebuilt walls of Jerusalem?</t>
+  </si>
+  <si>
+    <t>Nehemiah</t>
+  </si>
+  <si>
+    <t>Ezra</t>
+  </si>
+  <si>
+    <t>Who wrote Book of Revelation?</t>
+  </si>
+  <si>
+    <t>Who prayed in garden before arrest?</t>
+  </si>
+  <si>
+    <t>What mountain did Moses receive commandments on?</t>
+  </si>
+  <si>
+    <t>Mount Sinai</t>
+  </si>
+  <si>
+    <t>Zion</t>
+  </si>
+  <si>
+    <t>Carmel</t>
+  </si>
+  <si>
+    <t>Olivet</t>
+  </si>
+  <si>
+    <t>Who doubted Jesus’ resurrection at first?</t>
+  </si>
+  <si>
+    <t>Who rolled away stone from Jesus’ tomb?</t>
+  </si>
+  <si>
+    <t>What happened three days after Jesus died?</t>
   </si>
   <si>
     <t>What river was Jesus baptized in?</t>
@@ -1175,253 +1535,586 @@
     <t>Red Sea</t>
   </si>
   <si>
-    <t>Who was mother of Jesus?</t>
-  </si>
-  <si>
-    <t>Sarah</t>
-  </si>
-  <si>
-    <t>Eve</t>
-  </si>
-  <si>
-    <t>Who was earthly father of Jesus?</t>
-  </si>
-  <si>
-    <t>Who was strongest man in Bible?</t>
-  </si>
-  <si>
-    <t>Who interpreted Pharaoh’s dreams?</t>
-  </si>
-  <si>
-    <t>Who built the temple in Jerusalem?</t>
-  </si>
-  <si>
-    <t>Who was wisest king in Bible?</t>
-  </si>
-  <si>
-    <t>What is shortest verse in Bible?</t>
-  </si>
-  <si>
-    <t>Jesus wept</t>
-  </si>
-  <si>
-    <t>Pray always</t>
-  </si>
-  <si>
-    <t>Amen</t>
-  </si>
-  <si>
-    <t>Hallelujah</t>
-  </si>
-  <si>
-    <t>Who saw a burning bush?</t>
-  </si>
-  <si>
-    <t>Who was first man created by God?</t>
-  </si>
-  <si>
-    <t>Adam</t>
-  </si>
-  <si>
-    <t>Cain</t>
-  </si>
-  <si>
-    <t>Abel</t>
-  </si>
-  <si>
-    <t>Who was first woman created by God?</t>
-  </si>
-  <si>
-    <t>What garden did Adam and Eve live in?</t>
-  </si>
-  <si>
-    <t>Babylon</t>
-  </si>
-  <si>
-    <t>Who killed Abel?</t>
-  </si>
-  <si>
-    <t>Who was father of many nations?</t>
-  </si>
-  <si>
-    <t>Isaac</t>
-  </si>
-  <si>
-    <t>Jacob</t>
-  </si>
-  <si>
-    <t>Who walked on water with Jesus?</t>
-  </si>
-  <si>
-    <t>What was Jesus’ first miracle?</t>
-  </si>
-  <si>
-    <t>Turning water into wine</t>
-  </si>
-  <si>
-    <t>Healing blind</t>
-  </si>
-  <si>
-    <t>Feeding crowd</t>
-  </si>
-  <si>
-    <t>Who was first king of Israel?</t>
-  </si>
-  <si>
-    <t>Jonathan</t>
-  </si>
-  <si>
-    <t>Who anointed David as king?</t>
-  </si>
-  <si>
-    <t>Samuel</t>
-  </si>
-  <si>
-    <t>Nathan</t>
-  </si>
-  <si>
-    <t>Who wrote many Psalms?</t>
-  </si>
-  <si>
-    <t>Who survived fiery furnace unharmed?</t>
-  </si>
-  <si>
-    <t>Shadrach Meshach Abednego</t>
-  </si>
-  <si>
-    <t>Who rebuilt walls of Jerusalem?</t>
-  </si>
-  <si>
-    <t>Nehemiah</t>
-  </si>
-  <si>
-    <t>Ezra</t>
-  </si>
-  <si>
-    <t>Who was famous for patience during suffering?</t>
-  </si>
-  <si>
-    <t>Job</t>
-  </si>
-  <si>
-    <t>Who became queen and saved Jews?</t>
-  </si>
-  <si>
-    <t>Esther</t>
-  </si>
-  <si>
-    <t>Deborah</t>
-  </si>
-  <si>
-    <t>What disciple doubted resurrection until seeing Jesus?</t>
-  </si>
-  <si>
-    <t>What disciple was tax collector?</t>
-  </si>
-  <si>
-    <t>Who wrote Book of Revelation?</t>
-  </si>
-  <si>
-    <t>Luke</t>
-  </si>
-  <si>
-    <t>What mountain did Moses receive commandments on?</t>
-  </si>
-  <si>
-    <t>Mount Sinai</t>
-  </si>
-  <si>
-    <t>Zion</t>
-  </si>
-  <si>
-    <t>Carmel</t>
-  </si>
-  <si>
-    <t>Olivet</t>
-  </si>
-  <si>
-    <t>What happened three days after Jesus died?</t>
+    <t>Who was taken to heaven in whirlwind?</t>
+  </si>
+  <si>
+    <t>Who built giant ark to save animals from flood?</t>
+  </si>
+  <si>
+    <t>US States</t>
+  </si>
+  <si>
+    <t>Which US state is known as the Sunshine State?</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Hollywood?</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Which US state is called the Lone Star State?</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Which US state is known for the Grand Canyon?</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Which US state has New York City?</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Las Vegas?</t>
+  </si>
+  <si>
+    <t>Which US state is known for peaches?</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>Which US state is called Aloha State?</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>Which US state is largest by area?</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Which US state is known for potatoes?</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Which US state is home to Mount Rushmore?</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>Wyoming</t>
+  </si>
+  <si>
+    <t>Which US state is known for country music city Nashville?</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Which US state has the city of Miami?</t>
+  </si>
+  <si>
+    <t>Which US state is famous for maple syrup?</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>Which US state has the nickname Empire State?</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Disney World?</t>
+  </si>
+  <si>
+    <t>Which US state is known for corn farming?</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Which US state is famous for bourbon whiskey?</t>
+  </si>
+  <si>
+    <t>Which US state is known as the Golden State?</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Yellowstone National Park?</t>
+  </si>
+  <si>
+    <t>Which US state is known for the city of Chicago?</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Which US state is famous for lobster?</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Which US state has the city of New Orleans?</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Which US state is known for the Rocky Mountains?</t>
+  </si>
+  <si>
+    <t>Which US state has the nickname Garden State?</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Route 66 starting point Chicago?</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>Which US state is known for Niagara Falls?</t>
+  </si>
+  <si>
+    <t>Which US state is famous for pineapples?</t>
+  </si>
+  <si>
+    <t>Which US state is called the Last Frontier?</t>
+  </si>
+  <si>
+    <t>Which US state has the city of Dallas?</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Amish communities?</t>
+  </si>
+  <si>
+    <t>Which US state has Mount McKinley also called Denali?</t>
+  </si>
+  <si>
+    <t>Which US state is known for hot jazz music heritage?</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Detroit automobiles?</t>
+  </si>
+  <si>
+    <t>Which US state is known for the city of Seattle?</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Which US state is known as Land of Lincoln?</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Atlantic City?</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>Which US state is known for orange production?</t>
+  </si>
+  <si>
+    <t>Which US state is home to the Alamo?</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>Which US state has the city of Boston?</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Independence Hall?</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Which US state is known for the Everglades?</t>
+  </si>
+  <si>
+    <t>Which US state has the city of Las Vegas?</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Harvard University?</t>
+  </si>
+  <si>
+    <t>Which US state is known for giant redwood trees?</t>
+  </si>
+  <si>
+    <t>Which US state is famous for cowboy culture?</t>
+  </si>
+  <si>
+    <t>Which US state is known for the Liberty Bell?</t>
+  </si>
+  <si>
+    <t>Which US state has the city of Phoenix?</t>
+  </si>
+  <si>
+    <t>Which US state is known for potatoes and farmland?</t>
+  </si>
+  <si>
+    <t>Which US state is famous for Times Square?</t>
   </si>
   <si>
     <t>American History</t>
   </si>
   <si>
-    <t>Who was US President at the start of 1950?</t>
+    <t>Which war began in 1950 between North and South Korea?</t>
+  </si>
+  <si>
+    <t>Korean War</t>
+  </si>
+  <si>
+    <t>Vietnam War</t>
+  </si>
+  <si>
+    <t>Cold War</t>
+  </si>
+  <si>
+    <t>Gulf War</t>
+  </si>
+  <si>
+    <t>Who was President during most of the 1950s?</t>
+  </si>
+  <si>
+    <t>Dwight Eisenhower</t>
   </si>
   <si>
     <t>Harry Truman</t>
   </si>
   <si>
-    <t>Dwight Eisenhower</t>
-  </si>
-  <si>
     <t>John Kennedy</t>
   </si>
   <si>
+    <t>Nixon</t>
+  </si>
+  <si>
+    <t>What movement fought racial segregation in America?</t>
+  </si>
+  <si>
+    <t>Civil Rights Movement</t>
+  </si>
+  <si>
+    <t>Labor Movement</t>
+  </si>
+  <si>
+    <t>Green Movement</t>
+  </si>
+  <si>
+    <t>Women’s Movement</t>
+  </si>
+  <si>
+    <t>Who refused to give up her bus seat in Alabama?</t>
+  </si>
+  <si>
+    <t>Rosa Parks</t>
+  </si>
+  <si>
+    <t>Maya Angelou</t>
+  </si>
+  <si>
+    <t>Harriet Tubman</t>
+  </si>
+  <si>
+    <t>Eleanor Roosevelt</t>
+  </si>
+  <si>
+    <t>Which famous speech included “I Have a Dream”?</t>
+  </si>
+  <si>
+    <t>Martin Luther King Jr. Speech</t>
+  </si>
+  <si>
+    <t>JFK Speech</t>
+  </si>
+  <si>
+    <t>Nixon Speech</t>
+  </si>
+  <si>
+    <t>Reagan Speech</t>
+  </si>
+  <si>
+    <t>Who became the first Catholic US President in 1961?</t>
+  </si>
+  <si>
+    <t>John F. Kennedy</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Reagan</t>
+  </si>
+  <si>
+    <t>What wall divided East and West Berlin in 1961?</t>
+  </si>
+  <si>
+    <t>Berlin Wall</t>
+  </si>
+  <si>
+    <t>Great Wall</t>
+  </si>
+  <si>
+    <t>Iron Curtain</t>
+  </si>
+  <si>
+    <t>Freedom Wall</t>
+  </si>
+  <si>
+    <t>Which crisis nearly caused nuclear war in 1962?</t>
+  </si>
+  <si>
+    <t>Cuban Missile Crisis</t>
+  </si>
+  <si>
+    <t>Who was assassinated in Dallas in 1963?</t>
+  </si>
+  <si>
+    <t>Robert Kennedy</t>
+  </si>
+  <si>
+    <t>Martin Luther King Jr.</t>
+  </si>
+  <si>
+    <t>Who became President after JFK’s assassination?</t>
+  </si>
+  <si>
+    <t>Lyndon Johnson</t>
+  </si>
+  <si>
+    <t>Eisenhower</t>
+  </si>
+  <si>
+    <t>Ford</t>
+  </si>
+  <si>
+    <t>Which law ended segregation in public places in 1964?</t>
+  </si>
+  <si>
+    <t>Civil Rights Act</t>
+  </si>
+  <si>
+    <t>Voting Rights Act</t>
+  </si>
+  <si>
+    <t>Fair Housing Act</t>
+  </si>
+  <si>
+    <t>New Deal</t>
+  </si>
+  <si>
+    <t>Which war heavily involved America during the 1960s?</t>
+  </si>
+  <si>
+    <t>World War II</t>
+  </si>
+  <si>
+    <t>Who was famous boxer opposing Vietnam War draft?</t>
+  </si>
+  <si>
+    <t>Muhammad Ali</t>
+  </si>
+  <si>
+    <t>Joe Frazier</t>
+  </si>
+  <si>
+    <t>Mike Tyson</t>
+  </si>
+  <si>
+    <t>George Foreman</t>
+  </si>
+  <si>
+    <t>Who was assassinated in 1968 after civil rights activism?</t>
+  </si>
+  <si>
+    <t>Malcolm X</t>
+  </si>
+  <si>
+    <t>John Lewis</t>
+  </si>
+  <si>
+    <t>What mission landed first humans on the Moon?</t>
+  </si>
+  <si>
+    <t>Apollo 11</t>
+  </si>
+  <si>
+    <t>Apollo 13</t>
+  </si>
+  <si>
+    <t>Gemini 8</t>
+  </si>
+  <si>
+    <t>Skylab</t>
+  </si>
+  <si>
+    <t>Who was first man to walk on the Moon?</t>
+  </si>
+  <si>
+    <t>Neil Armstrong</t>
+  </si>
+  <si>
+    <t>Buzz Aldrin</t>
+  </si>
+  <si>
+    <t>Yuri Gagarin</t>
+  </si>
+  <si>
+    <t>Michael Collins</t>
+  </si>
+  <si>
+    <t>Who was President during Moon landing?</t>
+  </si>
+  <si>
     <t>Richard Nixon</t>
   </si>
   <si>
-    <t>Which war began in 1950 involving North and South Korea?</t>
-  </si>
-  <si>
-    <t>Korean War</t>
-  </si>
-  <si>
-    <t>Vietnam War</t>
-  </si>
-  <si>
-    <t>Cold War</t>
-  </si>
-  <si>
-    <t>Gulf War</t>
-  </si>
-  <si>
-    <t>Who became US President in 1953?</t>
-  </si>
-  <si>
-    <t>Nixon</t>
-  </si>
-  <si>
-    <t>Truman</t>
-  </si>
-  <si>
-    <t>What movement fought racial segregation in the 1950s and 1960s?</t>
-  </si>
-  <si>
-    <t>Civil Rights Movement</t>
-  </si>
-  <si>
-    <t>Labor Movement</t>
-  </si>
-  <si>
-    <t>Women’s Movement</t>
-  </si>
-  <si>
-    <t>Green Movement</t>
-  </si>
-  <si>
-    <t>Who refused to give up her bus seat in 1955?</t>
-  </si>
-  <si>
-    <t>Rosa Parks</t>
-  </si>
-  <si>
-    <t>Maya Angelou</t>
-  </si>
-  <si>
-    <t>Harriet Tubman</t>
-  </si>
-  <si>
-    <t>Eleanor Roosevelt</t>
-  </si>
-  <si>
-    <t>Which organization fought for civil rights led by Martin Luther King Jr.?</t>
-  </si>
-  <si>
-    <t>SCLC</t>
-  </si>
-  <si>
-    <t>NAACP</t>
+    <t>Kennedy</t>
+  </si>
+  <si>
+    <t>Which music festival became symbol of 1960s culture?</t>
+  </si>
+  <si>
+    <t>Woodstock</t>
+  </si>
+  <si>
+    <t>Coachella</t>
+  </si>
+  <si>
+    <t>Lollapalooza</t>
+  </si>
+  <si>
+    <t>Burning Man</t>
+  </si>
+  <si>
+    <t>What movement promoted peace and anti-war ideals in 1960s?</t>
+  </si>
+  <si>
+    <t>Hippie Movement</t>
+  </si>
+  <si>
+    <t>Industrial Movement</t>
+  </si>
+  <si>
+    <t>Which scandal forced President Nixon to resign?</t>
+  </si>
+  <si>
+    <t>Watergate</t>
+  </si>
+  <si>
+    <t>Iran-Contra</t>
+  </si>
+  <si>
+    <t>Teapot Dome</t>
+  </si>
+  <si>
+    <t>Pentagon Papers</t>
+  </si>
+  <si>
+    <t>Who resigned as US President in 1974?</t>
+  </si>
+  <si>
+    <t>Carter</t>
+  </si>
+  <si>
+    <t>Who became President after Nixon resigned?</t>
+  </si>
+  <si>
+    <t>Gerald Ford</t>
+  </si>
+  <si>
+    <t>Which war officially ended for America in 1975?</t>
+  </si>
+  <si>
+    <t>Who became US President in 1977?</t>
+  </si>
+  <si>
+    <t>Jimmy Carter</t>
+  </si>
+  <si>
+    <t>What hostage crisis hurt Jimmy Carter’s presidency?</t>
+  </si>
+  <si>
+    <t>Iran Hostage Crisis</t>
+  </si>
+  <si>
+    <t>Berlin Crisis</t>
+  </si>
+  <si>
+    <t>Which agency was created for US space exploration in 1958?</t>
+  </si>
+  <si>
+    <t>NASA</t>
   </si>
   <si>
     <t>FBI</t>
@@ -1430,16 +2123,10 @@
     <t>CIA</t>
   </si>
   <si>
-    <t>Who was famous for the “I Have a Dream” speech?</t>
-  </si>
-  <si>
-    <t>Martin Luther King Jr.</t>
-  </si>
-  <si>
-    <t>Malcolm X</t>
-  </si>
-  <si>
-    <t>What was the first artificial satellite launched in 1957?</t>
+    <t>NOAA</t>
+  </si>
+  <si>
+    <t>What Soviet satellite shocked America in 1957?</t>
   </si>
   <si>
     <t>Sputnik</t>
@@ -1448,286 +2135,148 @@
     <t>Apollo</t>
   </si>
   <si>
+    <t>Hubble</t>
+  </si>
+  <si>
     <t>Explorer</t>
   </si>
   <si>
-    <t>Hubble</t>
-  </si>
-  <si>
-    <t>Which US agency was created in 1958 for space exploration?</t>
-  </si>
-  <si>
-    <t>NASA</t>
-  </si>
-  <si>
-    <t>NOAA</t>
-  </si>
-  <si>
-    <t>Who became the youngest elected US President in 1961?</t>
-  </si>
-  <si>
-    <t>John F. Kennedy</t>
-  </si>
-  <si>
-    <t>Lyndon Johnson</t>
-  </si>
-  <si>
-    <t>Eisenhower</t>
-  </si>
-  <si>
-    <t>What wall divided East and West Berlin beginning in 1961?</t>
-  </si>
-  <si>
-    <t>Berlin Wall</t>
-  </si>
-  <si>
-    <t>Great Wall</t>
-  </si>
-  <si>
-    <t>Iron Curtain</t>
-  </si>
-  <si>
-    <t>Freedom Wall</t>
-  </si>
-  <si>
-    <t>Which crisis nearly caused nuclear war in 1962?</t>
-  </si>
-  <si>
-    <t>Cuban Missile Crisis</t>
-  </si>
-  <si>
-    <t>Who was assassinated in Dallas in 1963?</t>
-  </si>
-  <si>
-    <t>Robert Kennedy</t>
-  </si>
-  <si>
-    <t>Who became President after JFK’s assassination?</t>
-  </si>
-  <si>
-    <t>Reagan</t>
-  </si>
-  <si>
-    <t>Which law banned racial segregation in public places in 1964?</t>
-  </si>
-  <si>
-    <t>Civil Rights Act</t>
-  </si>
-  <si>
-    <t>Voting Rights Act</t>
-  </si>
-  <si>
-    <t>Fair Housing Act</t>
-  </si>
-  <si>
-    <t>New Deal</t>
-  </si>
-  <si>
-    <t>Which war escalated heavily during the 1960s?</t>
-  </si>
-  <si>
-    <t>Who was famous boxer refusing Vietnam draft?</t>
-  </si>
-  <si>
-    <t>Muhammad Ali</t>
-  </si>
-  <si>
-    <t>Joe Frazier</t>
-  </si>
-  <si>
-    <t>Mike Tyson</t>
-  </si>
-  <si>
-    <t>George Foreman</t>
-  </si>
-  <si>
-    <t>Who was assassinated in 1968 while supporting civil rights?</t>
-  </si>
-  <si>
-    <t>JFK</t>
-  </si>
-  <si>
-    <t>What mission landed first humans on Moon in 1969?</t>
-  </si>
-  <si>
-    <t>Apollo 11</t>
-  </si>
-  <si>
-    <t>Apollo 13</t>
-  </si>
-  <si>
-    <t>Gemini 7</t>
-  </si>
-  <si>
-    <t>Skylab</t>
-  </si>
-  <si>
-    <t>Who was first man on Moon?</t>
-  </si>
-  <si>
-    <t>Neil Armstrong</t>
-  </si>
-  <si>
-    <t>Buzz Aldrin</t>
-  </si>
-  <si>
-    <t>Yuri Gagarin</t>
-  </si>
-  <si>
-    <t>Michael Collins</t>
-  </si>
-  <si>
-    <t>Who was US President during Moon landing?</t>
-  </si>
-  <si>
-    <t>Johnson</t>
-  </si>
-  <si>
-    <t>Kennedy</t>
-  </si>
-  <si>
-    <t>What scandal forced Nixon to resign?</t>
-  </si>
-  <si>
-    <t>Watergate</t>
-  </si>
-  <si>
-    <t>Iran-Contra</t>
-  </si>
-  <si>
-    <t>Teapot Dome</t>
-  </si>
-  <si>
-    <t>Pentagon Papers</t>
-  </si>
-  <si>
-    <t>Who resigned as US President in 1974?</t>
-  </si>
-  <si>
-    <t>Ford</t>
-  </si>
-  <si>
-    <t>Carter</t>
-  </si>
-  <si>
-    <t>Who became President after Nixon resigned?</t>
-  </si>
-  <si>
-    <t>Gerald Ford</t>
-  </si>
-  <si>
-    <t>Which war officially ended for America in 1975?</t>
-  </si>
-  <si>
-    <t>World War II</t>
-  </si>
-  <si>
-    <t>Who became US President in 1977?</t>
-  </si>
-  <si>
-    <t>Jimmy Carter</t>
-  </si>
-  <si>
-    <t>What event in 1979 involved American hostages in Iran?</t>
-  </si>
-  <si>
-    <t>Iran Hostage Crisis</t>
-  </si>
-  <si>
-    <t>Cuban Crisis</t>
-  </si>
-  <si>
-    <t>Berlin Crisis</t>
-  </si>
-  <si>
-    <t>Which music style became hugely popular in 1970s America?</t>
+    <t>What Supreme Court case ended school segregation?</t>
+  </si>
+  <si>
+    <t>Brown v. Board of Education</t>
+  </si>
+  <si>
+    <t>Roe v. Wade</t>
+  </si>
+  <si>
+    <t>Miranda v. Arizona</t>
+  </si>
+  <si>
+    <t>Plessy v. Ferguson</t>
+  </si>
+  <si>
+    <t>Which amendment lowered voting age to 18?</t>
+  </si>
+  <si>
+    <t>26th Amendment</t>
+  </si>
+  <si>
+    <t>19th Amendment</t>
+  </si>
+  <si>
+    <t>21st Amendment</t>
+  </si>
+  <si>
+    <t>15th Amendment</t>
+  </si>
+  <si>
+    <t>Who led the Southern Christian Leadership Conference?</t>
+  </si>
+  <si>
+    <t>Jesse Jackson</t>
+  </si>
+  <si>
+    <t>What famous prison island closed in 1963?</t>
+  </si>
+  <si>
+    <t>Alcatraz</t>
+  </si>
+  <si>
+    <t>Sing Sing</t>
+  </si>
+  <si>
+    <t>Rikers</t>
+  </si>
+  <si>
+    <t>Island Prison</t>
+  </si>
+  <si>
+    <t>What famous route symbolized classic American road travel?</t>
+  </si>
+  <si>
+    <t>Route 66</t>
+  </si>
+  <si>
+    <t>Route 95</t>
+  </si>
+  <si>
+    <t>Route 1</t>
+  </si>
+  <si>
+    <t>Route 50</t>
+  </si>
+  <si>
+    <t>Which President opened relations with China in 1972?</t>
+  </si>
+  <si>
+    <t>Which famous fast food chain expanded rapidly in the 1950s?</t>
+  </si>
+  <si>
+    <t>McDonald’s</t>
+  </si>
+  <si>
+    <t>Burger King</t>
+  </si>
+  <si>
+    <t>Subway</t>
+  </si>
+  <si>
+    <t>KFC</t>
+  </si>
+  <si>
+    <t>What type of music became hugely popular in 1970s America?</t>
   </si>
   <si>
     <t>Disco</t>
   </si>
   <si>
-    <t>Rock</t>
-  </si>
-  <si>
     <t>Jazz</t>
   </si>
   <si>
     <t>Blues</t>
   </si>
   <si>
-    <t>What movement fought for women’s equality in the 1960s and 70s?</t>
+    <t>Classical</t>
+  </si>
+  <si>
+    <t>Who wrote “The Feminine Mystique”?</t>
+  </si>
+  <si>
+    <t>Betty Friedan</t>
+  </si>
+  <si>
+    <t>Gloria Steinem</t>
+  </si>
+  <si>
+    <t>What women’s movement grew strongly during the 1960s and 70s?</t>
   </si>
   <si>
     <t>Feminist Movement</t>
   </si>
   <si>
-    <t>Who wrote “The Feminine Mystique”?</t>
-  </si>
-  <si>
-    <t>Betty Friedan</t>
-  </si>
-  <si>
-    <t>Gloria Steinem</t>
-  </si>
-  <si>
-    <t>Which amendment lowered voting age to 18?</t>
-  </si>
-  <si>
-    <t>26th Amendment</t>
-  </si>
-  <si>
-    <t>19th Amendment</t>
-  </si>
-  <si>
-    <t>21st Amendment</t>
-  </si>
-  <si>
-    <t>15th Amendment</t>
-  </si>
-  <si>
-    <t>Which President opened relations with China in 1972?</t>
-  </si>
-  <si>
-    <t>Which famous music festival happened in 1969?</t>
-  </si>
-  <si>
-    <t>Woodstock</t>
-  </si>
-  <si>
-    <t>Coachella</t>
-  </si>
-  <si>
-    <t>Lollapalooza</t>
-  </si>
-  <si>
-    <t>Burning Man</t>
-  </si>
-  <si>
-    <t>Which civil rights leader promoted Black Power?</t>
-  </si>
-  <si>
-    <t>John Lewis</t>
-  </si>
-  <si>
-    <t>What Supreme Court case ended school segregation?</t>
-  </si>
-  <si>
-    <t>Brown v. Board of Education</t>
-  </si>
-  <si>
-    <t>Roe v. Wade</t>
-  </si>
-  <si>
-    <t>Miranda v. Arizona</t>
-  </si>
-  <si>
-    <t>Plessy v. Ferguson</t>
-  </si>
-  <si>
-    <t>Which law protected voting rights in 1965?</t>
-  </si>
-  <si>
-    <t>Who was famous anti-war activist during Vietnam era?</t>
+    <t>Peace Movement</t>
+  </si>
+  <si>
+    <t>What was the major fear between USA and USSR called?</t>
+  </si>
+  <si>
+    <t>World War III</t>
+  </si>
+  <si>
+    <t>Space Race</t>
+  </si>
+  <si>
+    <t>What race between USA and USSR focused on space exploration?</t>
+  </si>
+  <si>
+    <t>Arms Race</t>
+  </si>
+  <si>
+    <t>Tech War</t>
+  </si>
+  <si>
+    <t>Who became famous for anti-war protests during Vietnam era?</t>
   </si>
   <si>
     <t>Jane Fonda</t>
@@ -1742,163 +2291,136 @@
     <t>Audrey Hepburn</t>
   </si>
   <si>
-    <t>What did hippie movement promote in 1960s?</t>
-  </si>
-  <si>
-    <t>Peace and love</t>
-  </si>
-  <si>
-    <t>War and power</t>
-  </si>
-  <si>
-    <t>Industrial growth</t>
-  </si>
-  <si>
-    <t>Capitalism</t>
-  </si>
-  <si>
-    <t>Which company became famous for personal computers in 1970s?</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>Intel</t>
-  </si>
-  <si>
-    <t>Who co-founded Apple in 1976?</t>
-  </si>
-  <si>
-    <t>Steve Jobs</t>
-  </si>
-  <si>
-    <t>Bill Gates</t>
-  </si>
-  <si>
-    <t>Elon Musk</t>
-  </si>
-  <si>
-    <t>Mark Zuckerberg</t>
-  </si>
-  <si>
-    <t>What environmental disaster happened in 1979 nuclear plant?</t>
-  </si>
-  <si>
-    <t>Three Mile Island</t>
-  </si>
-  <si>
-    <t>Chernobyl</t>
-  </si>
-  <si>
-    <t>Fukushima</t>
-  </si>
-  <si>
-    <t>Deepwater Horizon</t>
-  </si>
-  <si>
-    <t>Which amendment guaranteed women right to vote earlier in US history?</t>
-  </si>
-  <si>
-    <t>Who was famous for segregation policies in Alabama?</t>
-  </si>
-  <si>
-    <t>George Wallace</t>
+    <t>What environmental celebration began in 1970?</t>
+  </si>
+  <si>
+    <t>Earth Day</t>
+  </si>
+  <si>
+    <t>Independence Day</t>
+  </si>
+  <si>
+    <t>Memorial Day</t>
+  </si>
+  <si>
+    <t>Labor Day</t>
+  </si>
+  <si>
+    <t>Which city hosted massive civil rights marches in 1963?</t>
+  </si>
+  <si>
+    <t>Washington D.C.</t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>Who said “Ask not what your country can do for you”?</t>
+  </si>
+  <si>
+    <t>Which television event showed first Moon landing live?</t>
+  </si>
+  <si>
+    <t>Apollo 11 Broadcast</t>
+  </si>
+  <si>
+    <t>Super Bowl</t>
+  </si>
+  <si>
+    <t>Watergate Hearing</t>
+  </si>
+  <si>
+    <t>Space Race Show</t>
+  </si>
+  <si>
+    <t>Which car became symbol of American muscle cars in 1960s?</t>
+  </si>
+  <si>
+    <t>Ford Mustang</t>
+  </si>
+  <si>
+    <t>Chevrolet Volt</t>
+  </si>
+  <si>
+    <t>Model T</t>
+  </si>
+  <si>
+    <t>Which newspaper exposed parts of Watergate scandal?</t>
+  </si>
+  <si>
+    <t>Washington Post</t>
+  </si>
+  <si>
+    <t>New York Times</t>
+  </si>
+  <si>
+    <t>Chicago Tribune</t>
+  </si>
+  <si>
+    <t>Time Magazine</t>
+  </si>
+  <si>
+    <t>Who were the two reporters investigating Watergate?</t>
+  </si>
+  <si>
+    <t>Woodward and Bernstein</t>
+  </si>
+  <si>
+    <t>Cronkite and Rather</t>
+  </si>
+  <si>
+    <t>Murrow and Cronkite</t>
+  </si>
+  <si>
+    <t>Hunt and Dean</t>
+  </si>
+  <si>
+    <t>Which TV medium became dominant in American homes during 1950s?</t>
+  </si>
+  <si>
+    <t>Television</t>
+  </si>
+  <si>
+    <t>Radio</t>
+  </si>
+  <si>
+    <t>Newspaper</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>Which famous concert event represented peace and music culture?</t>
+  </si>
+  <si>
+    <t>Live Aid</t>
+  </si>
+  <si>
+    <t>Who won presidency in 1980 ending the 1970s era?</t>
   </si>
   <si>
     <t>Ronald Reagan</t>
   </si>
   <si>
-    <t>Barry Goldwater</t>
-  </si>
-  <si>
-    <t>Which war protest event occurred at Kent State University?</t>
-  </si>
-  <si>
-    <t>Shooting of students</t>
-  </si>
-  <si>
-    <t>Boston Massacre</t>
-  </si>
-  <si>
-    <t>Civil Rights March</t>
-  </si>
-  <si>
-    <t>Tea Party</t>
-  </si>
-  <si>
-    <t>What was major fear between USA and USSR called?</t>
-  </si>
-  <si>
-    <t>Hot War</t>
-  </si>
-  <si>
-    <t>Space War</t>
-  </si>
-  <si>
-    <t>Which program helped poor Americans with healthcare in 1965?</t>
-  </si>
-  <si>
-    <t>Medicare</t>
-  </si>
-  <si>
-    <t>Obamacare</t>
-  </si>
-  <si>
-    <t>Medicaid</t>
-  </si>
-  <si>
-    <t>Social Security</t>
-  </si>
-  <si>
-    <t>Who became President in 1980?</t>
-  </si>
-  <si>
-    <t>What energy issue affected America during 1970s?</t>
+    <t>Which crisis caused gas shortages in 1970s America?</t>
   </si>
   <si>
     <t>Oil Crisis</t>
   </si>
   <si>
+    <t>Housing Crisis</t>
+  </si>
+  <si>
     <t>Bank Crisis</t>
   </si>
   <si>
-    <t>Housing Crisis</t>
-  </si>
-  <si>
     <t>Internet Crash</t>
-  </si>
-  <si>
-    <t>Which famous speech included “Ask not what your country can do for you”?</t>
-  </si>
-  <si>
-    <t>JFK Inaugural Speech</t>
-  </si>
-  <si>
-    <t>MLK Speech</t>
-  </si>
-  <si>
-    <t>Nixon Address</t>
-  </si>
-  <si>
-    <t>Reagan Speech</t>
-  </si>
-  <si>
-    <t>What was the nickname of the 1970s burglary scandal?</t>
-  </si>
-  <si>
-    <t>Which American astronaut walked on Moon with Armstrong?</t>
-  </si>
-  <si>
-    <t>John Glenn</t>
-  </si>
-  <si>
-    <t>Alan Shepard</t>
   </si>
 </sst>
 </file>
@@ -5845,7 +6367,7 @@
         <v>343</v>
       </c>
       <c r="G102" t="s">
-        <v>344</v>
+        <v>169</v>
       </c>
       <c r="H102">
         <v>5</v>
@@ -5859,22 +6381,22 @@
         <v>339</v>
       </c>
       <c r="B103" t="s">
+        <v>344</v>
+      </c>
+      <c r="C103" t="s">
         <v>345</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>346</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>345</v>
+      </c>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" t="s">
         <v>347</v>
-      </c>
-      <c r="E103" t="s">
-        <v>346</v>
-      </c>
-      <c r="F103" t="s">
-        <v>348</v>
-      </c>
-      <c r="G103" t="s">
-        <v>349</v>
       </c>
       <c r="H103">
         <v>5</v>
@@ -5888,22 +6410,22 @@
         <v>339</v>
       </c>
       <c r="B104" t="s">
+        <v>348</v>
+      </c>
+      <c r="C104" t="s">
+        <v>349</v>
+      </c>
+      <c r="D104" t="s">
         <v>350</v>
       </c>
-      <c r="C104">
-        <v>66</v>
-      </c>
-      <c r="D104">
-        <v>39</v>
-      </c>
-      <c r="E104">
-        <v>66</v>
-      </c>
-      <c r="F104">
-        <v>72</v>
-      </c>
-      <c r="G104">
-        <v>100</v>
+      <c r="E104" t="s">
+        <v>349</v>
+      </c>
+      <c r="F104" t="s">
+        <v>351</v>
+      </c>
+      <c r="G104" t="s">
+        <v>352</v>
       </c>
       <c r="H104">
         <v>5</v>
@@ -5917,22 +6439,22 @@
         <v>339</v>
       </c>
       <c r="B105" t="s">
-        <v>351</v>
-      </c>
-      <c r="C105">
-        <v>27</v>
-      </c>
-      <c r="D105">
-        <v>20</v>
-      </c>
-      <c r="E105">
-        <v>27</v>
-      </c>
-      <c r="F105">
-        <v>39</v>
-      </c>
-      <c r="G105">
-        <v>12</v>
+        <v>353</v>
+      </c>
+      <c r="C105" t="s">
+        <v>354</v>
+      </c>
+      <c r="D105" t="s">
+        <v>31</v>
+      </c>
+      <c r="E105" t="s">
+        <v>354</v>
+      </c>
+      <c r="F105" t="s">
+        <v>355</v>
+      </c>
+      <c r="G105" t="s">
+        <v>116</v>
       </c>
       <c r="H105">
         <v>5</v>
@@ -5946,22 +6468,22 @@
         <v>339</v>
       </c>
       <c r="B106" t="s">
-        <v>352</v>
-      </c>
-      <c r="C106">
-        <v>39</v>
-      </c>
-      <c r="D106">
-        <v>27</v>
-      </c>
-      <c r="E106">
-        <v>39</v>
-      </c>
-      <c r="F106">
-        <v>50</v>
-      </c>
-      <c r="G106">
-        <v>66</v>
+        <v>356</v>
+      </c>
+      <c r="C106" t="s">
+        <v>169</v>
+      </c>
+      <c r="D106" t="s">
+        <v>357</v>
+      </c>
+      <c r="E106" t="s">
+        <v>169</v>
+      </c>
+      <c r="F106" t="s">
+        <v>358</v>
+      </c>
+      <c r="G106" t="s">
+        <v>359</v>
       </c>
       <c r="H106">
         <v>5</v>
@@ -5975,22 +6497,22 @@
         <v>339</v>
       </c>
       <c r="B107" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C107" t="s">
-        <v>169</v>
+        <v>361</v>
       </c>
       <c r="D107" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="E107" t="s">
-        <v>169</v>
+        <v>361</v>
       </c>
       <c r="F107" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="G107" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="H107">
         <v>5</v>
@@ -6004,22 +6526,22 @@
         <v>339</v>
       </c>
       <c r="B108" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C108" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="D108" t="s">
-        <v>342</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F108" t="s">
-        <v>347</v>
+        <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>341</v>
+        <v>58</v>
       </c>
       <c r="H108">
         <v>5</v>
@@ -6033,22 +6555,22 @@
         <v>339</v>
       </c>
       <c r="B109" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C109" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="D109" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s">
+        <v>345</v>
+      </c>
+      <c r="F109" t="s">
         <v>169</v>
       </c>
-      <c r="E109" t="s">
-        <v>359</v>
-      </c>
-      <c r="F109" t="s">
-        <v>360</v>
-      </c>
       <c r="G109" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="H109">
         <v>5</v>
@@ -6062,22 +6584,22 @@
         <v>339</v>
       </c>
       <c r="B110" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C110" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D110" t="s">
-        <v>14</v>
+        <v>347</v>
       </c>
       <c r="E110" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="F110" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="G110" t="s">
-        <v>13</v>
+        <v>343</v>
       </c>
       <c r="H110">
         <v>5</v>
@@ -6091,22 +6613,22 @@
         <v>339</v>
       </c>
       <c r="B111" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C111" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="D111" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="E111" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="F111" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="G111" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="H111">
         <v>5</v>
@@ -6120,22 +6642,22 @@
         <v>339</v>
       </c>
       <c r="B112" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C112" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>368</v>
+        <v>13</v>
       </c>
       <c r="E112" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
       <c r="F112" t="s">
-        <v>369</v>
+        <v>19</v>
       </c>
       <c r="G112" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="H112">
         <v>5</v>
@@ -6149,22 +6671,22 @@
         <v>339</v>
       </c>
       <c r="B113" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C113" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D113" t="s">
-        <v>13</v>
+        <v>375</v>
       </c>
       <c r="E113" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F113" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G113" t="s">
-        <v>18</v>
+        <v>376</v>
       </c>
       <c r="H113">
         <v>5</v>
@@ -6178,22 +6700,22 @@
         <v>339</v>
       </c>
       <c r="B114" t="s">
-        <v>115</v>
+        <v>377</v>
       </c>
       <c r="C114" t="s">
-        <v>116</v>
+        <v>346</v>
       </c>
       <c r="D114" t="s">
-        <v>13</v>
+        <v>369</v>
       </c>
       <c r="E114" t="s">
-        <v>116</v>
+        <v>346</v>
       </c>
       <c r="F114" t="s">
-        <v>19</v>
+        <v>347</v>
       </c>
       <c r="G114" t="s">
-        <v>58</v>
+        <v>378</v>
       </c>
       <c r="H114">
         <v>5</v>
@@ -6207,22 +6729,22 @@
         <v>339</v>
       </c>
       <c r="B115" t="s">
-        <v>372</v>
-      </c>
-      <c r="C115">
-        <v>12</v>
-      </c>
-      <c r="D115">
-        <v>10</v>
-      </c>
-      <c r="E115">
-        <v>12</v>
-      </c>
-      <c r="F115">
-        <v>7</v>
-      </c>
-      <c r="G115">
-        <v>15</v>
+        <v>379</v>
+      </c>
+      <c r="C115" t="s">
+        <v>357</v>
+      </c>
+      <c r="D115" t="s">
+        <v>358</v>
+      </c>
+      <c r="E115" t="s">
+        <v>357</v>
+      </c>
+      <c r="F115" t="s">
+        <v>380</v>
+      </c>
+      <c r="G115" t="s">
+        <v>359</v>
       </c>
       <c r="H115">
         <v>5</v>
@@ -6236,22 +6758,22 @@
         <v>339</v>
       </c>
       <c r="B116" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C116" t="s">
+        <v>365</v>
+      </c>
+      <c r="D116" t="s">
+        <v>18</v>
+      </c>
+      <c r="E116" t="s">
+        <v>365</v>
+      </c>
+      <c r="F116" t="s">
         <v>13</v>
       </c>
-      <c r="D116" t="s">
-        <v>58</v>
-      </c>
-      <c r="E116" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" t="s">
-        <v>116</v>
-      </c>
       <c r="G116" t="s">
-        <v>18</v>
+        <v>382</v>
       </c>
       <c r="H116">
         <v>5</v>
@@ -6265,22 +6787,22 @@
         <v>339</v>
       </c>
       <c r="B117" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C117" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="D117" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E117" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="F117" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="G117" t="s">
-        <v>375</v>
+        <v>94</v>
       </c>
       <c r="H117">
         <v>5</v>
@@ -6294,22 +6816,22 @@
         <v>339</v>
       </c>
       <c r="B118" t="s">
+        <v>384</v>
+      </c>
+      <c r="C118" t="s">
+        <v>375</v>
+      </c>
+      <c r="D118" t="s">
+        <v>54</v>
+      </c>
+      <c r="E118" t="s">
+        <v>375</v>
+      </c>
+      <c r="F118" t="s">
+        <v>143</v>
+      </c>
+      <c r="G118" t="s">
         <v>376</v>
-      </c>
-      <c r="C118" t="s">
-        <v>17</v>
-      </c>
-      <c r="D118" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" t="s">
-        <v>17</v>
-      </c>
-      <c r="F118" t="s">
-        <v>18</v>
-      </c>
-      <c r="G118" t="s">
-        <v>169</v>
       </c>
       <c r="H118">
         <v>5</v>
@@ -6323,22 +6845,22 @@
         <v>339</v>
       </c>
       <c r="B119" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C119" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="D119" t="s">
-        <v>379</v>
+        <v>98</v>
       </c>
       <c r="E119" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="F119" t="s">
-        <v>380</v>
+        <v>74</v>
       </c>
       <c r="G119" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H119">
         <v>5</v>
@@ -6352,22 +6874,22 @@
         <v>339</v>
       </c>
       <c r="B120" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C120" t="s">
-        <v>143</v>
+        <v>347</v>
       </c>
       <c r="D120" t="s">
-        <v>54</v>
+        <v>368</v>
       </c>
       <c r="E120" t="s">
-        <v>143</v>
+        <v>347</v>
       </c>
       <c r="F120" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="G120" t="s">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="H120">
         <v>5</v>
@@ -6381,22 +6903,22 @@
         <v>339</v>
       </c>
       <c r="B121" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C121" t="s">
-        <v>14</v>
+        <v>390</v>
       </c>
       <c r="D121" t="s">
-        <v>13</v>
+        <v>391</v>
       </c>
       <c r="E121" t="s">
-        <v>14</v>
+        <v>390</v>
       </c>
       <c r="F121" t="s">
-        <v>58</v>
+        <v>369</v>
       </c>
       <c r="G121" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="H121">
         <v>5</v>
@@ -6410,22 +6932,22 @@
         <v>339</v>
       </c>
       <c r="B122" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C122" t="s">
-        <v>363</v>
+        <v>145</v>
       </c>
       <c r="D122" t="s">
-        <v>354</v>
+        <v>57</v>
       </c>
       <c r="E122" t="s">
-        <v>363</v>
+        <v>145</v>
       </c>
       <c r="F122" t="s">
-        <v>365</v>
+        <v>13</v>
       </c>
       <c r="G122" t="s">
-        <v>366</v>
+        <v>19</v>
       </c>
       <c r="H122">
         <v>5</v>
@@ -6439,22 +6961,22 @@
         <v>339</v>
       </c>
       <c r="B123" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C123" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>362</v>
+        <v>13</v>
       </c>
       <c r="E123" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F123" t="s">
-        <v>169</v>
+        <v>58</v>
       </c>
       <c r="G123" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H123">
         <v>5</v>
@@ -6468,22 +6990,22 @@
         <v>339</v>
       </c>
       <c r="B124" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C124" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="D124" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="E124" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="F124" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="G124" t="s">
-        <v>359</v>
+        <v>169</v>
       </c>
       <c r="H124">
         <v>5</v>
@@ -6497,22 +7019,22 @@
         <v>339</v>
       </c>
       <c r="B125" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C125" t="s">
-        <v>355</v>
+        <v>169</v>
       </c>
       <c r="D125" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E125" t="s">
-        <v>355</v>
+        <v>169</v>
       </c>
       <c r="F125" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="G125" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H125">
         <v>5</v>
@@ -6526,22 +7048,22 @@
         <v>339</v>
       </c>
       <c r="B126" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C126" t="s">
-        <v>391</v>
+        <v>18</v>
       </c>
       <c r="D126" t="s">
-        <v>392</v>
+        <v>13</v>
       </c>
       <c r="E126" t="s">
-        <v>391</v>
+        <v>18</v>
       </c>
       <c r="F126" t="s">
-        <v>393</v>
+        <v>58</v>
       </c>
       <c r="G126" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="H126">
         <v>5</v>
@@ -6555,22 +7077,22 @@
         <v>339</v>
       </c>
       <c r="B127" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C127" t="s">
-        <v>169</v>
+        <v>391</v>
       </c>
       <c r="D127" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="E127" t="s">
-        <v>169</v>
+        <v>391</v>
       </c>
       <c r="F127" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G127" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="H127">
         <v>5</v>
@@ -6584,22 +7106,22 @@
         <v>339</v>
       </c>
       <c r="B128" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C128" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D128" t="s">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="E128" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F128" t="s">
-        <v>398</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="H128">
         <v>5</v>
@@ -6613,22 +7135,22 @@
         <v>339</v>
       </c>
       <c r="B129" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C129" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="D129" t="s">
-        <v>143</v>
+        <v>13</v>
       </c>
       <c r="E129" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="F129" t="s">
-        <v>383</v>
+        <v>58</v>
       </c>
       <c r="G129" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="H129">
         <v>5</v>
@@ -6642,22 +7164,22 @@
         <v>339</v>
       </c>
       <c r="B130" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C130" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="D130" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="E130" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="F130" t="s">
-        <v>402</v>
+        <v>13</v>
       </c>
       <c r="G130" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="H130">
         <v>5</v>
@@ -6671,22 +7193,22 @@
         <v>339</v>
       </c>
       <c r="B131" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C131" t="s">
-        <v>398</v>
+        <v>13</v>
       </c>
       <c r="D131" t="s">
-        <v>365</v>
+        <v>58</v>
       </c>
       <c r="E131" t="s">
-        <v>398</v>
+        <v>13</v>
       </c>
       <c r="F131" t="s">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="G131" t="s">
-        <v>363</v>
+        <v>59</v>
       </c>
       <c r="H131">
         <v>5</v>
@@ -6700,22 +7222,22 @@
         <v>339</v>
       </c>
       <c r="B132" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C132" t="s">
-        <v>360</v>
+        <v>408</v>
       </c>
       <c r="D132" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E132" t="s">
-        <v>360</v>
+        <v>408</v>
       </c>
       <c r="F132" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G132" t="s">
-        <v>14</v>
+        <v>357</v>
       </c>
       <c r="H132">
         <v>5</v>
@@ -6729,22 +7251,22 @@
         <v>339</v>
       </c>
       <c r="B133" t="s">
-        <v>144</v>
+        <v>411</v>
       </c>
       <c r="C133" t="s">
-        <v>145</v>
+        <v>375</v>
       </c>
       <c r="D133" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="E133" t="s">
-        <v>145</v>
+        <v>375</v>
       </c>
       <c r="F133" t="s">
-        <v>58</v>
+        <v>376</v>
       </c>
       <c r="G133" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="H133">
         <v>5</v>
@@ -6758,22 +7280,22 @@
         <v>339</v>
       </c>
       <c r="B134" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C134" t="s">
-        <v>13</v>
+        <v>347</v>
       </c>
       <c r="D134" t="s">
-        <v>58</v>
+        <v>368</v>
       </c>
       <c r="E134" t="s">
-        <v>13</v>
+        <v>347</v>
       </c>
       <c r="F134" t="s">
-        <v>19</v>
+        <v>413</v>
       </c>
       <c r="G134" t="s">
-        <v>18</v>
+        <v>359</v>
       </c>
       <c r="H134">
         <v>5</v>
@@ -6787,22 +7309,22 @@
         <v>339</v>
       </c>
       <c r="B135" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C135" t="s">
-        <v>409</v>
+        <v>358</v>
       </c>
       <c r="D135" t="s">
-        <v>410</v>
+        <v>169</v>
       </c>
       <c r="E135" t="s">
-        <v>409</v>
+        <v>358</v>
       </c>
       <c r="F135" t="s">
-        <v>122</v>
+        <v>415</v>
       </c>
       <c r="G135" t="s">
-        <v>411</v>
+        <v>346</v>
       </c>
       <c r="H135">
         <v>5</v>
@@ -6816,22 +7338,22 @@
         <v>339</v>
       </c>
       <c r="B136" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C136" t="s">
-        <v>365</v>
+        <v>13</v>
       </c>
       <c r="D136" t="s">
-        <v>354</v>
+        <v>18</v>
       </c>
       <c r="E136" t="s">
-        <v>365</v>
+        <v>13</v>
       </c>
       <c r="F136" t="s">
-        <v>355</v>
+        <v>58</v>
       </c>
       <c r="G136" t="s">
-        <v>413</v>
+        <v>98</v>
       </c>
       <c r="H136">
         <v>5</v>
@@ -6845,22 +7367,22 @@
         <v>339</v>
       </c>
       <c r="B137" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C137" t="s">
-        <v>415</v>
+        <v>14</v>
       </c>
       <c r="D137" t="s">
-        <v>369</v>
+        <v>13</v>
       </c>
       <c r="E137" t="s">
-        <v>415</v>
+        <v>14</v>
       </c>
       <c r="F137" t="s">
-        <v>416</v>
+        <v>58</v>
       </c>
       <c r="G137" t="s">
-        <v>368</v>
+        <v>19</v>
       </c>
       <c r="H137">
         <v>5</v>
@@ -6874,22 +7396,22 @@
         <v>339</v>
       </c>
       <c r="B138" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C138" t="s">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="D138" t="s">
-        <v>355</v>
+        <v>18</v>
       </c>
       <c r="E138" t="s">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="F138" t="s">
-        <v>169</v>
+        <v>13</v>
       </c>
       <c r="G138" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="H138">
         <v>5</v>
@@ -6903,22 +7425,22 @@
         <v>339</v>
       </c>
       <c r="B139" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C139" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D139" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E139" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F139" t="s">
-        <v>13</v>
+        <v>369</v>
       </c>
       <c r="G139" t="s">
-        <v>18</v>
+        <v>347</v>
       </c>
       <c r="H139">
         <v>5</v>
@@ -6932,22 +7454,22 @@
         <v>339</v>
       </c>
       <c r="B140" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C140" t="s">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="D140" t="s">
-        <v>422</v>
+        <v>54</v>
       </c>
       <c r="E140" t="s">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="F140" t="s">
-        <v>366</v>
+        <v>143</v>
       </c>
       <c r="G140" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="H140">
         <v>5</v>
@@ -6961,22 +7483,22 @@
         <v>339</v>
       </c>
       <c r="B141" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C141" t="s">
-        <v>424</v>
+        <v>345</v>
       </c>
       <c r="D141" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>424</v>
+        <v>345</v>
       </c>
       <c r="F141" t="s">
-        <v>13</v>
+        <v>371</v>
       </c>
       <c r="G141" t="s">
-        <v>58</v>
+        <v>351</v>
       </c>
       <c r="H141">
         <v>5</v>
@@ -6990,22 +7512,22 @@
         <v>339</v>
       </c>
       <c r="B142" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C142" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D142" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E142" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F142" t="s">
-        <v>143</v>
+        <v>13</v>
       </c>
       <c r="G142" t="s">
-        <v>427</v>
+        <v>19</v>
       </c>
       <c r="H142">
         <v>5</v>
@@ -7019,22 +7541,22 @@
         <v>339</v>
       </c>
       <c r="B143" t="s">
-        <v>16</v>
+        <v>425</v>
       </c>
       <c r="C143" t="s">
-        <v>17</v>
+        <v>426</v>
       </c>
       <c r="D143" t="s">
+        <v>18</v>
+      </c>
+      <c r="E143" t="s">
+        <v>426</v>
+      </c>
+      <c r="F143" t="s">
         <v>13</v>
       </c>
-      <c r="E143" t="s">
-        <v>17</v>
-      </c>
-      <c r="F143" t="s">
-        <v>18</v>
-      </c>
       <c r="G143" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="H143">
         <v>5</v>
@@ -7048,22 +7570,22 @@
         <v>339</v>
       </c>
       <c r="B144" t="s">
+        <v>427</v>
+      </c>
+      <c r="C144" t="s">
+        <v>347</v>
+      </c>
+      <c r="D144" t="s">
+        <v>346</v>
+      </c>
+      <c r="E144" t="s">
+        <v>347</v>
+      </c>
+      <c r="F144" t="s">
+        <v>369</v>
+      </c>
+      <c r="G144" t="s">
         <v>428</v>
-      </c>
-      <c r="C144" t="s">
-        <v>19</v>
-      </c>
-      <c r="D144" t="s">
-        <v>13</v>
-      </c>
-      <c r="E144" t="s">
-        <v>19</v>
-      </c>
-      <c r="F144" t="s">
-        <v>58</v>
-      </c>
-      <c r="G144" t="s">
-        <v>57</v>
       </c>
       <c r="H144">
         <v>5</v>
@@ -7080,19 +7602,19 @@
         <v>429</v>
       </c>
       <c r="C145" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D145" t="s">
         <v>13</v>
       </c>
       <c r="E145" t="s">
+        <v>58</v>
+      </c>
+      <c r="F145" t="s">
+        <v>19</v>
+      </c>
+      <c r="G145" t="s">
         <v>57</v>
-      </c>
-      <c r="F145" t="s">
-        <v>58</v>
-      </c>
-      <c r="G145" t="s">
-        <v>59</v>
       </c>
       <c r="H145">
         <v>5</v>
@@ -7109,19 +7631,19 @@
         <v>430</v>
       </c>
       <c r="C146" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="D146" t="s">
         <v>13</v>
       </c>
       <c r="E146" t="s">
+        <v>19</v>
+      </c>
+      <c r="F146" t="s">
         <v>58</v>
       </c>
-      <c r="F146" t="s">
-        <v>18</v>
-      </c>
       <c r="G146" t="s">
-        <v>431</v>
+        <v>61</v>
       </c>
       <c r="H146">
         <v>5</v>
@@ -7135,22 +7657,22 @@
         <v>339</v>
       </c>
       <c r="B147" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C147" t="s">
-        <v>433</v>
+        <v>57</v>
       </c>
       <c r="D147" t="s">
-        <v>434</v>
+        <v>145</v>
       </c>
       <c r="E147" t="s">
-        <v>433</v>
+        <v>57</v>
       </c>
       <c r="F147" t="s">
-        <v>435</v>
+        <v>13</v>
       </c>
       <c r="G147" t="s">
-        <v>436</v>
+        <v>166</v>
       </c>
       <c r="H147">
         <v>5</v>
@@ -7164,22 +7686,22 @@
         <v>339</v>
       </c>
       <c r="B148" t="s">
-        <v>96</v>
+        <v>432</v>
       </c>
       <c r="C148" t="s">
-        <v>74</v>
+        <v>433</v>
       </c>
       <c r="D148" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="E148" t="s">
-        <v>74</v>
+        <v>433</v>
       </c>
       <c r="F148" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="G148" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="H148">
         <v>5</v>
@@ -7193,22 +7715,22 @@
         <v>339</v>
       </c>
       <c r="B149" t="s">
-        <v>135</v>
-      </c>
-      <c r="C149">
-        <v>40</v>
-      </c>
-      <c r="D149">
-        <v>7</v>
-      </c>
-      <c r="E149">
-        <v>40</v>
-      </c>
-      <c r="F149">
-        <v>12</v>
-      </c>
-      <c r="G149">
-        <v>30</v>
+        <v>434</v>
+      </c>
+      <c r="C149" t="s">
+        <v>13</v>
+      </c>
+      <c r="D149" t="s">
+        <v>18</v>
+      </c>
+      <c r="E149" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" t="s">
+        <v>58</v>
+      </c>
+      <c r="G149" t="s">
+        <v>98</v>
       </c>
       <c r="H149">
         <v>5</v>
@@ -7222,22 +7744,22 @@
         <v>339</v>
       </c>
       <c r="B150" t="s">
-        <v>133</v>
+        <v>435</v>
       </c>
       <c r="C150" t="s">
-        <v>134</v>
+        <v>349</v>
       </c>
       <c r="D150" t="s">
-        <v>116</v>
+        <v>350</v>
       </c>
       <c r="E150" t="s">
-        <v>134</v>
+        <v>349</v>
       </c>
       <c r="F150" t="s">
-        <v>13</v>
+        <v>351</v>
       </c>
       <c r="G150" t="s">
-        <v>31</v>
+        <v>352</v>
       </c>
       <c r="H150">
         <v>5</v>
@@ -7251,22 +7773,22 @@
         <v>339</v>
       </c>
       <c r="B151" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C151" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="D151" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="E151" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
       <c r="F151" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G151" t="s">
-        <v>64</v>
+        <v>363</v>
       </c>
       <c r="H151">
         <v>5</v>
@@ -7277,25 +7799,25 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B152" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C152" t="s">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="D152" t="s">
-        <v>441</v>
+        <v>169</v>
       </c>
       <c r="E152" t="s">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="F152" t="s">
-        <v>442</v>
+        <v>343</v>
       </c>
       <c r="G152" t="s">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="H152">
         <v>5</v>
@@ -7306,25 +7828,25 @@
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
+        <v>339</v>
+      </c>
+      <c r="B153" t="s">
         <v>438</v>
       </c>
-      <c r="B153" t="s">
-        <v>444</v>
-      </c>
       <c r="C153" t="s">
-        <v>445</v>
+        <v>169</v>
       </c>
       <c r="D153" t="s">
-        <v>446</v>
+        <v>357</v>
       </c>
       <c r="E153" t="s">
-        <v>445</v>
+        <v>169</v>
       </c>
       <c r="F153" t="s">
-        <v>447</v>
+        <v>358</v>
       </c>
       <c r="G153" t="s">
-        <v>448</v>
+        <v>359</v>
       </c>
       <c r="H153">
         <v>5</v>
@@ -7335,25 +7857,25 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B154" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C154" t="s">
-        <v>441</v>
+        <v>347</v>
       </c>
       <c r="D154" t="s">
-        <v>442</v>
+        <v>346</v>
       </c>
       <c r="E154" t="s">
-        <v>441</v>
+        <v>347</v>
       </c>
       <c r="F154" t="s">
-        <v>450</v>
+        <v>369</v>
       </c>
       <c r="G154" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="H154">
         <v>5</v>
@@ -7364,25 +7886,25 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B155" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C155" t="s">
-        <v>453</v>
+        <v>365</v>
       </c>
       <c r="D155" t="s">
-        <v>454</v>
+        <v>18</v>
       </c>
       <c r="E155" t="s">
-        <v>453</v>
+        <v>365</v>
       </c>
       <c r="F155" t="s">
-        <v>455</v>
+        <v>13</v>
       </c>
       <c r="G155" t="s">
-        <v>456</v>
+        <v>58</v>
       </c>
       <c r="H155">
         <v>5</v>
@@ -7393,25 +7915,25 @@
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B156" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="C156" t="s">
-        <v>458</v>
+        <v>345</v>
       </c>
       <c r="D156" t="s">
-        <v>459</v>
+        <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>458</v>
+        <v>345</v>
       </c>
       <c r="F156" t="s">
-        <v>460</v>
+        <v>346</v>
       </c>
       <c r="G156" t="s">
-        <v>461</v>
+        <v>347</v>
       </c>
       <c r="H156">
         <v>5</v>
@@ -7422,25 +7944,25 @@
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B157" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="C157" t="s">
-        <v>463</v>
+        <v>368</v>
       </c>
       <c r="D157" t="s">
-        <v>464</v>
+        <v>347</v>
       </c>
       <c r="E157" t="s">
-        <v>463</v>
+        <v>368</v>
       </c>
       <c r="F157" t="s">
-        <v>465</v>
+        <v>369</v>
       </c>
       <c r="G157" t="s">
-        <v>466</v>
+        <v>382</v>
       </c>
       <c r="H157">
         <v>5</v>
@@ -7451,25 +7973,25 @@
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B158" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="C158" t="s">
-        <v>468</v>
+        <v>368</v>
       </c>
       <c r="D158" t="s">
-        <v>469</v>
+        <v>347</v>
       </c>
       <c r="E158" t="s">
-        <v>468</v>
+        <v>368</v>
       </c>
       <c r="F158" t="s">
-        <v>442</v>
+        <v>369</v>
       </c>
       <c r="G158" t="s">
-        <v>458</v>
+        <v>343</v>
       </c>
       <c r="H158">
         <v>5</v>
@@ -7480,25 +8002,25 @@
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B159" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="C159" t="s">
-        <v>471</v>
+        <v>169</v>
       </c>
       <c r="D159" t="s">
-        <v>472</v>
+        <v>357</v>
       </c>
       <c r="E159" t="s">
-        <v>471</v>
+        <v>169</v>
       </c>
       <c r="F159" t="s">
-        <v>473</v>
+        <v>358</v>
       </c>
       <c r="G159" t="s">
-        <v>474</v>
+        <v>380</v>
       </c>
       <c r="H159">
         <v>5</v>
@@ -7509,25 +8031,25 @@
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B160" t="s">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="C160" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="D160" t="s">
-        <v>466</v>
+        <v>382</v>
       </c>
       <c r="E160" t="s">
-        <v>476</v>
+        <v>446</v>
       </c>
       <c r="F160" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="G160" t="s">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="H160">
         <v>5</v>
@@ -7538,25 +8060,25 @@
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B161" t="s">
-        <v>478</v>
+        <v>449</v>
       </c>
       <c r="C161" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="D161" t="s">
+        <v>143</v>
+      </c>
+      <c r="E161" t="s">
         <v>450</v>
       </c>
-      <c r="E161" t="s">
-        <v>479</v>
-      </c>
       <c r="F161" t="s">
-        <v>480</v>
+        <v>54</v>
       </c>
       <c r="G161" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
       <c r="H161">
         <v>5</v>
@@ -7567,25 +8089,25 @@
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B162" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
       <c r="C162" t="s">
-        <v>483</v>
+        <v>132</v>
       </c>
       <c r="D162" t="s">
-        <v>484</v>
+        <v>131</v>
       </c>
       <c r="E162" t="s">
-        <v>483</v>
+        <v>132</v>
       </c>
       <c r="F162" t="s">
-        <v>485</v>
+        <v>453</v>
       </c>
       <c r="G162" t="s">
-        <v>486</v>
+        <v>29</v>
       </c>
       <c r="H162">
         <v>5</v>
@@ -7596,25 +8118,25 @@
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B163" t="s">
-        <v>487</v>
+        <v>454</v>
       </c>
       <c r="C163" t="s">
-        <v>488</v>
+        <v>116</v>
       </c>
       <c r="D163" t="s">
-        <v>445</v>
+        <v>13</v>
       </c>
       <c r="E163" t="s">
-        <v>488</v>
+        <v>116</v>
       </c>
       <c r="F163" t="s">
-        <v>446</v>
+        <v>19</v>
       </c>
       <c r="G163" t="s">
-        <v>447</v>
+        <v>58</v>
       </c>
       <c r="H163">
         <v>5</v>
@@ -7625,25 +8147,25 @@
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B164" t="s">
-        <v>489</v>
+        <v>455</v>
       </c>
       <c r="C164" t="s">
-        <v>479</v>
+        <v>13</v>
       </c>
       <c r="D164" t="s">
-        <v>490</v>
+        <v>58</v>
       </c>
       <c r="E164" t="s">
-        <v>479</v>
+        <v>13</v>
       </c>
       <c r="F164" t="s">
-        <v>468</v>
+        <v>19</v>
       </c>
       <c r="G164" t="s">
-        <v>450</v>
+        <v>18</v>
       </c>
       <c r="H164">
         <v>5</v>
@@ -7654,25 +8176,25 @@
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B165" t="s">
-        <v>491</v>
+        <v>456</v>
       </c>
       <c r="C165" t="s">
-        <v>480</v>
+        <v>17</v>
       </c>
       <c r="D165" t="s">
-        <v>450</v>
+        <v>13</v>
       </c>
       <c r="E165" t="s">
-        <v>480</v>
+        <v>17</v>
       </c>
       <c r="F165" t="s">
-        <v>481</v>
+        <v>18</v>
       </c>
       <c r="G165" t="s">
-        <v>492</v>
+        <v>169</v>
       </c>
       <c r="H165">
         <v>5</v>
@@ -7683,25 +8205,25 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B166" t="s">
-        <v>493</v>
+        <v>457</v>
       </c>
       <c r="C166" t="s">
-        <v>494</v>
+        <v>27</v>
       </c>
       <c r="D166" t="s">
-        <v>495</v>
+        <v>28</v>
       </c>
       <c r="E166" t="s">
-        <v>494</v>
+        <v>27</v>
       </c>
       <c r="F166" t="s">
-        <v>496</v>
+        <v>29</v>
       </c>
       <c r="G166" t="s">
-        <v>497</v>
+        <v>458</v>
       </c>
       <c r="H166">
         <v>5</v>
@@ -7712,25 +8234,25 @@
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B167" t="s">
-        <v>498</v>
+        <v>459</v>
       </c>
       <c r="C167" t="s">
-        <v>446</v>
+        <v>143</v>
       </c>
       <c r="D167" t="s">
-        <v>445</v>
+        <v>54</v>
       </c>
       <c r="E167" t="s">
-        <v>446</v>
+        <v>143</v>
       </c>
       <c r="F167" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G167" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H167">
         <v>5</v>
@@ -7741,25 +8263,25 @@
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B168" t="s">
-        <v>499</v>
+        <v>460</v>
       </c>
       <c r="C168" t="s">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="D168" t="s">
-        <v>501</v>
+        <v>13</v>
       </c>
       <c r="E168" t="s">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="F168" t="s">
-        <v>502</v>
+        <v>58</v>
       </c>
       <c r="G168" t="s">
-        <v>503</v>
+        <v>18</v>
       </c>
       <c r="H168">
         <v>5</v>
@@ -7770,25 +8292,25 @@
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B169" t="s">
-        <v>504</v>
-      </c>
-      <c r="C169" t="s">
-        <v>468</v>
-      </c>
-      <c r="D169" t="s">
-        <v>469</v>
-      </c>
-      <c r="E169" t="s">
-        <v>468</v>
-      </c>
-      <c r="F169" t="s">
-        <v>505</v>
-      </c>
-      <c r="G169" t="s">
-        <v>490</v>
+        <v>461</v>
+      </c>
+      <c r="C169">
+        <v>12</v>
+      </c>
+      <c r="D169">
+        <v>10</v>
+      </c>
+      <c r="E169">
+        <v>12</v>
+      </c>
+      <c r="F169">
+        <v>7</v>
+      </c>
+      <c r="G169">
+        <v>15</v>
       </c>
       <c r="H169">
         <v>5</v>
@@ -7799,25 +8321,25 @@
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B170" t="s">
-        <v>506</v>
+        <v>462</v>
       </c>
       <c r="C170" t="s">
-        <v>507</v>
+        <v>13</v>
       </c>
       <c r="D170" t="s">
-        <v>508</v>
+        <v>58</v>
       </c>
       <c r="E170" t="s">
-        <v>507</v>
+        <v>13</v>
       </c>
       <c r="F170" t="s">
-        <v>509</v>
+        <v>19</v>
       </c>
       <c r="G170" t="s">
-        <v>510</v>
+        <v>18</v>
       </c>
       <c r="H170">
         <v>5</v>
@@ -7828,25 +8350,25 @@
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B171" t="s">
-        <v>511</v>
+        <v>144</v>
       </c>
       <c r="C171" t="s">
-        <v>512</v>
+        <v>145</v>
       </c>
       <c r="D171" t="s">
-        <v>513</v>
+        <v>57</v>
       </c>
       <c r="E171" t="s">
-        <v>512</v>
+        <v>145</v>
       </c>
       <c r="F171" t="s">
-        <v>514</v>
+        <v>13</v>
       </c>
       <c r="G171" t="s">
-        <v>515</v>
+        <v>19</v>
       </c>
       <c r="H171">
         <v>5</v>
@@ -7857,25 +8379,25 @@
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B172" t="s">
-        <v>516</v>
+        <v>463</v>
       </c>
       <c r="C172" t="s">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="D172" t="s">
-        <v>517</v>
+        <v>368</v>
       </c>
       <c r="E172" t="s">
-        <v>443</v>
+        <v>347</v>
       </c>
       <c r="F172" t="s">
-        <v>518</v>
+        <v>169</v>
       </c>
       <c r="G172" t="s">
-        <v>492</v>
+        <v>18</v>
       </c>
       <c r="H172">
         <v>5</v>
@@ -7886,25 +8408,25 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B173" t="s">
-        <v>519</v>
+        <v>464</v>
       </c>
       <c r="C173" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
       <c r="D173" t="s">
-        <v>521</v>
+        <v>345</v>
       </c>
       <c r="E173" t="s">
-        <v>520</v>
+        <v>465</v>
       </c>
       <c r="F173" t="s">
-        <v>522</v>
+        <v>13</v>
       </c>
       <c r="G173" t="s">
-        <v>523</v>
+        <v>18</v>
       </c>
       <c r="H173">
         <v>5</v>
@@ -7915,25 +8437,25 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B174" t="s">
-        <v>524</v>
+        <v>466</v>
       </c>
       <c r="C174" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="D174" t="s">
-        <v>525</v>
+        <v>18</v>
       </c>
       <c r="E174" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="F174" t="s">
-        <v>526</v>
+        <v>13</v>
       </c>
       <c r="G174" t="s">
-        <v>492</v>
+        <v>58</v>
       </c>
       <c r="H174">
         <v>5</v>
@@ -7944,25 +8466,25 @@
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B175" t="s">
-        <v>527</v>
+        <v>96</v>
       </c>
       <c r="C175" t="s">
-        <v>528</v>
+        <v>74</v>
       </c>
       <c r="D175" t="s">
-        <v>526</v>
+        <v>97</v>
       </c>
       <c r="E175" t="s">
-        <v>528</v>
+        <v>74</v>
       </c>
       <c r="F175" t="s">
-        <v>517</v>
+        <v>98</v>
       </c>
       <c r="G175" t="s">
-        <v>492</v>
+        <v>18</v>
       </c>
       <c r="H175">
         <v>5</v>
@@ -7973,25 +8495,25 @@
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B176" t="s">
-        <v>529</v>
+        <v>16</v>
       </c>
       <c r="C176" t="s">
-        <v>446</v>
+        <v>17</v>
       </c>
       <c r="D176" t="s">
-        <v>445</v>
+        <v>13</v>
       </c>
       <c r="E176" t="s">
-        <v>446</v>
+        <v>17</v>
       </c>
       <c r="F176" t="s">
-        <v>447</v>
+        <v>18</v>
       </c>
       <c r="G176" t="s">
-        <v>530</v>
+        <v>19</v>
       </c>
       <c r="H176">
         <v>5</v>
@@ -8002,25 +8524,25 @@
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B177" t="s">
-        <v>531</v>
+        <v>467</v>
       </c>
       <c r="C177" t="s">
-        <v>532</v>
+        <v>468</v>
       </c>
       <c r="D177" t="s">
-        <v>525</v>
+        <v>469</v>
       </c>
       <c r="E177" t="s">
-        <v>532</v>
+        <v>468</v>
       </c>
       <c r="F177" t="s">
-        <v>492</v>
+        <v>122</v>
       </c>
       <c r="G177" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="H177">
         <v>5</v>
@@ -8031,25 +8553,25 @@
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B178" t="s">
-        <v>533</v>
+        <v>471</v>
       </c>
       <c r="C178" t="s">
-        <v>534</v>
+        <v>169</v>
       </c>
       <c r="D178" t="s">
-        <v>535</v>
+        <v>357</v>
       </c>
       <c r="E178" t="s">
-        <v>534</v>
+        <v>169</v>
       </c>
       <c r="F178" t="s">
-        <v>520</v>
+        <v>349</v>
       </c>
       <c r="G178" t="s">
-        <v>536</v>
+        <v>358</v>
       </c>
       <c r="H178">
         <v>5</v>
@@ -8060,25 +8582,25 @@
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B179" t="s">
-        <v>537</v>
+        <v>472</v>
       </c>
       <c r="C179" t="s">
-        <v>538</v>
+        <v>14</v>
       </c>
       <c r="D179" t="s">
-        <v>539</v>
+        <v>345</v>
       </c>
       <c r="E179" t="s">
-        <v>538</v>
+        <v>14</v>
       </c>
       <c r="F179" t="s">
-        <v>540</v>
+        <v>169</v>
       </c>
       <c r="G179" t="s">
-        <v>541</v>
+        <v>357</v>
       </c>
       <c r="H179">
         <v>5</v>
@@ -8089,25 +8611,25 @@
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B180" t="s">
-        <v>542</v>
+        <v>473</v>
       </c>
       <c r="C180" t="s">
-        <v>543</v>
+        <v>375</v>
       </c>
       <c r="D180" t="s">
-        <v>453</v>
+        <v>54</v>
       </c>
       <c r="E180" t="s">
-        <v>543</v>
+        <v>375</v>
       </c>
       <c r="F180" t="s">
-        <v>456</v>
+        <v>143</v>
       </c>
       <c r="G180" t="s">
-        <v>454</v>
+        <v>376</v>
       </c>
       <c r="H180">
         <v>5</v>
@@ -8118,25 +8640,25 @@
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B181" t="s">
-        <v>544</v>
+        <v>474</v>
       </c>
       <c r="C181" t="s">
-        <v>545</v>
+        <v>169</v>
       </c>
       <c r="D181" t="s">
-        <v>546</v>
+        <v>343</v>
       </c>
       <c r="E181" t="s">
-        <v>545</v>
+        <v>169</v>
       </c>
       <c r="F181" t="s">
-        <v>461</v>
+        <v>351</v>
       </c>
       <c r="G181" t="s">
-        <v>458</v>
+        <v>349</v>
       </c>
       <c r="H181">
         <v>5</v>
@@ -8147,25 +8669,25 @@
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B182" t="s">
-        <v>547</v>
+        <v>475</v>
       </c>
       <c r="C182" t="s">
-        <v>548</v>
+        <v>346</v>
       </c>
       <c r="D182" t="s">
-        <v>549</v>
+        <v>347</v>
       </c>
       <c r="E182" t="s">
-        <v>548</v>
+        <v>346</v>
       </c>
       <c r="F182" t="s">
-        <v>550</v>
+        <v>369</v>
       </c>
       <c r="G182" t="s">
-        <v>551</v>
+        <v>415</v>
       </c>
       <c r="H182">
         <v>5</v>
@@ -8176,25 +8698,25 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B183" t="s">
-        <v>552</v>
+        <v>476</v>
       </c>
       <c r="C183" t="s">
-        <v>443</v>
+        <v>369</v>
       </c>
       <c r="D183" t="s">
-        <v>492</v>
+        <v>347</v>
       </c>
       <c r="E183" t="s">
-        <v>443</v>
+        <v>369</v>
       </c>
       <c r="F183" t="s">
-        <v>526</v>
+        <v>368</v>
       </c>
       <c r="G183" t="s">
-        <v>517</v>
+        <v>428</v>
       </c>
       <c r="H183">
         <v>5</v>
@@ -8205,25 +8727,25 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B184" t="s">
-        <v>553</v>
+        <v>477</v>
       </c>
       <c r="C184" t="s">
-        <v>554</v>
+        <v>359</v>
       </c>
       <c r="D184" t="s">
-        <v>555</v>
+        <v>349</v>
       </c>
       <c r="E184" t="s">
-        <v>554</v>
+        <v>359</v>
       </c>
       <c r="F184" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="G184" t="s">
-        <v>557</v>
+        <v>357</v>
       </c>
       <c r="H184">
         <v>5</v>
@@ -8234,25 +8756,25 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B185" t="s">
-        <v>558</v>
+        <v>479</v>
       </c>
       <c r="C185" t="s">
-        <v>469</v>
+        <v>343</v>
       </c>
       <c r="D185" t="s">
-        <v>468</v>
+        <v>342</v>
       </c>
       <c r="E185" t="s">
-        <v>469</v>
+        <v>343</v>
       </c>
       <c r="F185" t="s">
-        <v>458</v>
+        <v>341</v>
       </c>
       <c r="G185" t="s">
-        <v>559</v>
+        <v>14</v>
       </c>
       <c r="H185">
         <v>5</v>
@@ -8263,25 +8785,25 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B186" t="s">
-        <v>560</v>
+        <v>480</v>
       </c>
       <c r="C186" t="s">
-        <v>561</v>
+        <v>341</v>
       </c>
       <c r="D186" t="s">
-        <v>562</v>
+        <v>342</v>
       </c>
       <c r="E186" t="s">
-        <v>561</v>
+        <v>341</v>
       </c>
       <c r="F186" t="s">
-        <v>563</v>
+        <v>343</v>
       </c>
       <c r="G186" t="s">
-        <v>564</v>
+        <v>14</v>
       </c>
       <c r="H186">
         <v>5</v>
@@ -8292,25 +8814,25 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B187" t="s">
-        <v>565</v>
+        <v>481</v>
       </c>
       <c r="C187" t="s">
-        <v>495</v>
+        <v>14</v>
       </c>
       <c r="D187" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="E187" t="s">
-        <v>495</v>
+        <v>14</v>
       </c>
       <c r="F187" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="G187" t="s">
-        <v>497</v>
+        <v>342</v>
       </c>
       <c r="H187">
         <v>5</v>
@@ -8321,25 +8843,25 @@
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B188" t="s">
-        <v>566</v>
+        <v>484</v>
       </c>
       <c r="C188" t="s">
-        <v>567</v>
+        <v>485</v>
       </c>
       <c r="D188" t="s">
-        <v>568</v>
+        <v>486</v>
       </c>
       <c r="E188" t="s">
-        <v>567</v>
+        <v>485</v>
       </c>
       <c r="F188" t="s">
-        <v>569</v>
+        <v>358</v>
       </c>
       <c r="G188" t="s">
-        <v>570</v>
+        <v>345</v>
       </c>
       <c r="H188">
         <v>5</v>
@@ -8350,25 +8872,25 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B189" t="s">
-        <v>571</v>
+        <v>487</v>
       </c>
       <c r="C189" t="s">
-        <v>572</v>
+        <v>58</v>
       </c>
       <c r="D189" t="s">
-        <v>573</v>
+        <v>13</v>
       </c>
       <c r="E189" t="s">
-        <v>572</v>
+        <v>58</v>
       </c>
       <c r="F189" t="s">
-        <v>574</v>
+        <v>18</v>
       </c>
       <c r="G189" t="s">
-        <v>575</v>
+        <v>363</v>
       </c>
       <c r="H189">
         <v>5</v>
@@ -8379,25 +8901,25 @@
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B190" t="s">
-        <v>576</v>
+        <v>488</v>
       </c>
       <c r="C190" t="s">
-        <v>577</v>
+        <v>9</v>
       </c>
       <c r="D190" t="s">
-        <v>578</v>
+        <v>13</v>
       </c>
       <c r="E190" t="s">
-        <v>577</v>
+        <v>9</v>
       </c>
       <c r="F190" t="s">
-        <v>579</v>
+        <v>18</v>
       </c>
       <c r="G190" t="s">
-        <v>580</v>
+        <v>58</v>
       </c>
       <c r="H190">
         <v>5</v>
@@ -8408,25 +8930,25 @@
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B191" t="s">
-        <v>581</v>
+        <v>489</v>
       </c>
       <c r="C191" t="s">
-        <v>582</v>
+        <v>490</v>
       </c>
       <c r="D191" t="s">
-        <v>583</v>
+        <v>491</v>
       </c>
       <c r="E191" t="s">
-        <v>582</v>
+        <v>490</v>
       </c>
       <c r="F191" t="s">
-        <v>584</v>
+        <v>492</v>
       </c>
       <c r="G191" t="s">
-        <v>585</v>
+        <v>493</v>
       </c>
       <c r="H191">
         <v>5</v>
@@ -8437,25 +8959,25 @@
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B192" t="s">
-        <v>586</v>
+        <v>429</v>
       </c>
       <c r="C192" t="s">
-        <v>587</v>
+        <v>58</v>
       </c>
       <c r="D192" t="s">
-        <v>588</v>
+        <v>13</v>
       </c>
       <c r="E192" t="s">
-        <v>587</v>
+        <v>58</v>
       </c>
       <c r="F192" t="s">
-        <v>589</v>
+        <v>19</v>
       </c>
       <c r="G192" t="s">
-        <v>590</v>
+        <v>57</v>
       </c>
       <c r="H192">
         <v>5</v>
@@ -8466,25 +8988,25 @@
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B193" t="s">
-        <v>591</v>
+        <v>494</v>
       </c>
       <c r="C193" t="s">
-        <v>549</v>
+        <v>19</v>
       </c>
       <c r="D193" t="s">
-        <v>551</v>
+        <v>13</v>
       </c>
       <c r="E193" t="s">
-        <v>549</v>
+        <v>19</v>
       </c>
       <c r="F193" t="s">
-        <v>550</v>
+        <v>58</v>
       </c>
       <c r="G193" t="s">
-        <v>548</v>
+        <v>61</v>
       </c>
       <c r="H193">
         <v>5</v>
@@ -8495,25 +9017,25 @@
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B194" t="s">
-        <v>592</v>
+        <v>85</v>
       </c>
       <c r="C194" t="s">
-        <v>593</v>
+        <v>86</v>
       </c>
       <c r="D194" t="s">
-        <v>594</v>
+        <v>13</v>
       </c>
       <c r="E194" t="s">
-        <v>593</v>
+        <v>86</v>
       </c>
       <c r="F194" t="s">
-        <v>532</v>
+        <v>58</v>
       </c>
       <c r="G194" t="s">
-        <v>595</v>
+        <v>19</v>
       </c>
       <c r="H194">
         <v>5</v>
@@ -8524,25 +9046,25 @@
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B195" t="s">
-        <v>596</v>
+        <v>495</v>
       </c>
       <c r="C195" t="s">
-        <v>597</v>
+        <v>395</v>
       </c>
       <c r="D195" t="s">
-        <v>598</v>
+        <v>13</v>
       </c>
       <c r="E195" t="s">
-        <v>597</v>
+        <v>395</v>
       </c>
       <c r="F195" t="s">
-        <v>599</v>
+        <v>58</v>
       </c>
       <c r="G195" t="s">
-        <v>600</v>
+        <v>143</v>
       </c>
       <c r="H195">
         <v>5</v>
@@ -8553,25 +9075,25 @@
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B196" t="s">
-        <v>601</v>
+        <v>496</v>
       </c>
       <c r="C196" t="s">
-        <v>447</v>
+        <v>153</v>
       </c>
       <c r="D196" t="s">
-        <v>602</v>
+        <v>66</v>
       </c>
       <c r="E196" t="s">
-        <v>447</v>
+        <v>153</v>
       </c>
       <c r="F196" t="s">
-        <v>603</v>
+        <v>65</v>
       </c>
       <c r="G196" t="s">
-        <v>445</v>
+        <v>64</v>
       </c>
       <c r="H196">
         <v>5</v>
@@ -8582,25 +9104,25 @@
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B197" t="s">
-        <v>604</v>
+        <v>133</v>
       </c>
       <c r="C197" t="s">
-        <v>605</v>
+        <v>134</v>
       </c>
       <c r="D197" t="s">
-        <v>606</v>
+        <v>116</v>
       </c>
       <c r="E197" t="s">
-        <v>605</v>
+        <v>134</v>
       </c>
       <c r="F197" t="s">
-        <v>607</v>
+        <v>13</v>
       </c>
       <c r="G197" t="s">
-        <v>608</v>
+        <v>31</v>
       </c>
       <c r="H197">
         <v>5</v>
@@ -8611,25 +9133,25 @@
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B198" t="s">
-        <v>609</v>
-      </c>
-      <c r="C198" t="s">
-        <v>594</v>
-      </c>
-      <c r="D198" t="s">
-        <v>532</v>
-      </c>
-      <c r="E198" t="s">
-        <v>594</v>
-      </c>
-      <c r="F198" t="s">
-        <v>525</v>
-      </c>
-      <c r="G198" t="s">
-        <v>450</v>
+        <v>135</v>
+      </c>
+      <c r="C198">
+        <v>40</v>
+      </c>
+      <c r="D198">
+        <v>7</v>
+      </c>
+      <c r="E198">
+        <v>40</v>
+      </c>
+      <c r="F198">
+        <v>12</v>
+      </c>
+      <c r="G198">
+        <v>30</v>
       </c>
       <c r="H198">
         <v>5</v>
@@ -8640,25 +9162,25 @@
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B199" t="s">
-        <v>610</v>
+        <v>405</v>
       </c>
       <c r="C199" t="s">
-        <v>611</v>
+        <v>98</v>
       </c>
       <c r="D199" t="s">
-        <v>612</v>
+        <v>18</v>
       </c>
       <c r="E199" t="s">
-        <v>611</v>
+        <v>98</v>
       </c>
       <c r="F199" t="s">
-        <v>613</v>
+        <v>13</v>
       </c>
       <c r="G199" t="s">
-        <v>614</v>
+        <v>58</v>
       </c>
       <c r="H199">
         <v>5</v>
@@ -8669,25 +9191,25 @@
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B200" t="s">
-        <v>615</v>
+        <v>497</v>
       </c>
       <c r="C200" t="s">
-        <v>616</v>
+        <v>498</v>
       </c>
       <c r="D200" t="s">
-        <v>617</v>
+        <v>499</v>
       </c>
       <c r="E200" t="s">
-        <v>616</v>
+        <v>498</v>
       </c>
       <c r="F200" t="s">
-        <v>618</v>
+        <v>500</v>
       </c>
       <c r="G200" t="s">
-        <v>619</v>
+        <v>501</v>
       </c>
       <c r="H200">
         <v>5</v>
@@ -8698,25 +9220,25 @@
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B201" t="s">
-        <v>620</v>
+        <v>502</v>
       </c>
       <c r="C201" t="s">
-        <v>520</v>
+        <v>349</v>
       </c>
       <c r="D201" t="s">
-        <v>522</v>
+        <v>350</v>
       </c>
       <c r="E201" t="s">
-        <v>520</v>
+        <v>349</v>
       </c>
       <c r="F201" t="s">
-        <v>521</v>
+        <v>351</v>
       </c>
       <c r="G201" t="s">
-        <v>523</v>
+        <v>352</v>
       </c>
       <c r="H201">
         <v>5</v>
@@ -8727,30 +9249,2959 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>438</v>
+        <v>339</v>
       </c>
       <c r="B202" t="s">
+        <v>503</v>
+      </c>
+      <c r="C202" t="s">
+        <v>382</v>
+      </c>
+      <c r="D202" t="s">
+        <v>169</v>
+      </c>
+      <c r="E202" t="s">
+        <v>382</v>
+      </c>
+      <c r="F202" t="s">
+        <v>343</v>
+      </c>
+      <c r="G202" t="s">
+        <v>347</v>
+      </c>
+      <c r="H202">
+        <v>5</v>
+      </c>
+      <c r="I202" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203" t="s">
+        <v>504</v>
+      </c>
+      <c r="B203" t="s">
+        <v>505</v>
+      </c>
+      <c r="C203" t="s">
+        <v>506</v>
+      </c>
+      <c r="D203" t="s">
+        <v>507</v>
+      </c>
+      <c r="E203" t="s">
+        <v>506</v>
+      </c>
+      <c r="F203" t="s">
+        <v>508</v>
+      </c>
+      <c r="G203" t="s">
+        <v>509</v>
+      </c>
+      <c r="H203">
+        <v>5</v>
+      </c>
+      <c r="I203" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" t="s">
+        <v>504</v>
+      </c>
+      <c r="B204" t="s">
+        <v>510</v>
+      </c>
+      <c r="C204" t="s">
+        <v>507</v>
+      </c>
+      <c r="D204" t="s">
+        <v>506</v>
+      </c>
+      <c r="E204" t="s">
+        <v>507</v>
+      </c>
+      <c r="F204" t="s">
+        <v>511</v>
+      </c>
+      <c r="G204" t="s">
+        <v>512</v>
+      </c>
+      <c r="H204">
+        <v>5</v>
+      </c>
+      <c r="I204" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" t="s">
+        <v>504</v>
+      </c>
+      <c r="B205" t="s">
+        <v>513</v>
+      </c>
+      <c r="C205" t="s">
+        <v>508</v>
+      </c>
+      <c r="D205" t="s">
+        <v>509</v>
+      </c>
+      <c r="E205" t="s">
+        <v>508</v>
+      </c>
+      <c r="F205" t="s">
+        <v>511</v>
+      </c>
+      <c r="G205" t="s">
+        <v>514</v>
+      </c>
+      <c r="H205">
+        <v>5</v>
+      </c>
+      <c r="I205" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" t="s">
+        <v>504</v>
+      </c>
+      <c r="B206" t="s">
+        <v>515</v>
+      </c>
+      <c r="C206" t="s">
+        <v>509</v>
+      </c>
+      <c r="D206" t="s">
+        <v>516</v>
+      </c>
+      <c r="E206" t="s">
+        <v>509</v>
+      </c>
+      <c r="F206" t="s">
+        <v>517</v>
+      </c>
+      <c r="G206" t="s">
+        <v>511</v>
+      </c>
+      <c r="H206">
+        <v>5</v>
+      </c>
+      <c r="I206" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" t="s">
+        <v>504</v>
+      </c>
+      <c r="B207" t="s">
+        <v>518</v>
+      </c>
+      <c r="C207" t="s">
+        <v>512</v>
+      </c>
+      <c r="D207" t="s">
+        <v>519</v>
+      </c>
+      <c r="E207" t="s">
+        <v>512</v>
+      </c>
+      <c r="F207" t="s">
+        <v>507</v>
+      </c>
+      <c r="G207" t="s">
+        <v>520</v>
+      </c>
+      <c r="H207">
+        <v>5</v>
+      </c>
+      <c r="I207" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" t="s">
+        <v>504</v>
+      </c>
+      <c r="B208" t="s">
+        <v>521</v>
+      </c>
+      <c r="C208" t="s">
+        <v>511</v>
+      </c>
+      <c r="D208" t="s">
+        <v>507</v>
+      </c>
+      <c r="E208" t="s">
+        <v>511</v>
+      </c>
+      <c r="F208" t="s">
+        <v>508</v>
+      </c>
+      <c r="G208" t="s">
+        <v>506</v>
+      </c>
+      <c r="H208">
+        <v>5</v>
+      </c>
+      <c r="I208" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209" t="s">
+        <v>504</v>
+      </c>
+      <c r="B209" t="s">
+        <v>522</v>
+      </c>
+      <c r="C209" t="s">
+        <v>523</v>
+      </c>
+      <c r="D209" t="s">
+        <v>506</v>
+      </c>
+      <c r="E209" t="s">
+        <v>523</v>
+      </c>
+      <c r="F209" t="s">
+        <v>524</v>
+      </c>
+      <c r="G209" t="s">
+        <v>525</v>
+      </c>
+      <c r="H209">
+        <v>5</v>
+      </c>
+      <c r="I209" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210" t="s">
+        <v>504</v>
+      </c>
+      <c r="B210" t="s">
+        <v>526</v>
+      </c>
+      <c r="C210" t="s">
+        <v>527</v>
+      </c>
+      <c r="D210" t="s">
+        <v>507</v>
+      </c>
+      <c r="E210" t="s">
+        <v>527</v>
+      </c>
+      <c r="F210" t="s">
+        <v>506</v>
+      </c>
+      <c r="G210" t="s">
+        <v>514</v>
+      </c>
+      <c r="H210">
+        <v>5</v>
+      </c>
+      <c r="I210" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211" t="s">
+        <v>504</v>
+      </c>
+      <c r="B211" t="s">
+        <v>528</v>
+      </c>
+      <c r="C211" t="s">
+        <v>514</v>
+      </c>
+      <c r="D211" t="s">
+        <v>508</v>
+      </c>
+      <c r="E211" t="s">
+        <v>514</v>
+      </c>
+      <c r="F211" t="s">
+        <v>507</v>
+      </c>
+      <c r="G211" t="s">
+        <v>529</v>
+      </c>
+      <c r="H211">
+        <v>5</v>
+      </c>
+      <c r="I211" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212" t="s">
+        <v>504</v>
+      </c>
+      <c r="B212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C212" t="s">
+        <v>531</v>
+      </c>
+      <c r="D212" t="s">
+        <v>532</v>
+      </c>
+      <c r="E212" t="s">
+        <v>531</v>
+      </c>
+      <c r="F212" t="s">
+        <v>533</v>
+      </c>
+      <c r="G212" t="s">
+        <v>534</v>
+      </c>
+      <c r="H212">
+        <v>5</v>
+      </c>
+      <c r="I212" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213" t="s">
+        <v>504</v>
+      </c>
+      <c r="B213" t="s">
+        <v>535</v>
+      </c>
+      <c r="C213" t="s">
+        <v>536</v>
+      </c>
+      <c r="D213" t="s">
+        <v>537</v>
+      </c>
+      <c r="E213" t="s">
+        <v>536</v>
+      </c>
+      <c r="F213" t="s">
+        <v>538</v>
+      </c>
+      <c r="G213" t="s">
+        <v>517</v>
+      </c>
+      <c r="H213">
+        <v>5</v>
+      </c>
+      <c r="I213" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="A214" t="s">
+        <v>504</v>
+      </c>
+      <c r="B214" t="s">
+        <v>539</v>
+      </c>
+      <c r="C214" t="s">
+        <v>540</v>
+      </c>
+      <c r="D214" t="s">
+        <v>541</v>
+      </c>
+      <c r="E214" t="s">
+        <v>540</v>
+      </c>
+      <c r="F214" t="s">
+        <v>508</v>
+      </c>
+      <c r="G214" t="s">
+        <v>524</v>
+      </c>
+      <c r="H214">
+        <v>5</v>
+      </c>
+      <c r="I214" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215" t="s">
+        <v>504</v>
+      </c>
+      <c r="B215" t="s">
+        <v>542</v>
+      </c>
+      <c r="C215" t="s">
+        <v>506</v>
+      </c>
+      <c r="D215" t="s">
+        <v>507</v>
+      </c>
+      <c r="E215" t="s">
+        <v>506</v>
+      </c>
+      <c r="F215" t="s">
+        <v>508</v>
+      </c>
+      <c r="G215" t="s">
+        <v>523</v>
+      </c>
+      <c r="H215">
+        <v>5</v>
+      </c>
+      <c r="I215" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216" t="s">
+        <v>504</v>
+      </c>
+      <c r="B216" t="s">
+        <v>543</v>
+      </c>
+      <c r="C216" t="s">
+        <v>544</v>
+      </c>
+      <c r="D216" t="s">
+        <v>545</v>
+      </c>
+      <c r="E216" t="s">
+        <v>544</v>
+      </c>
+      <c r="F216" t="s">
+        <v>546</v>
+      </c>
+      <c r="G216" t="s">
+        <v>529</v>
+      </c>
+      <c r="H216">
+        <v>5</v>
+      </c>
+      <c r="I216" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217" t="s">
+        <v>504</v>
+      </c>
+      <c r="B217" t="s">
+        <v>547</v>
+      </c>
+      <c r="C217" t="s">
+        <v>512</v>
+      </c>
+      <c r="D217" t="s">
+        <v>519</v>
+      </c>
+      <c r="E217" t="s">
+        <v>512</v>
+      </c>
+      <c r="F217" t="s">
+        <v>548</v>
+      </c>
+      <c r="G217" t="s">
+        <v>520</v>
+      </c>
+      <c r="H217">
+        <v>5</v>
+      </c>
+      <c r="I217" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218" t="s">
+        <v>504</v>
+      </c>
+      <c r="B218" t="s">
+        <v>549</v>
+      </c>
+      <c r="C218" t="s">
+        <v>506</v>
+      </c>
+      <c r="D218" t="s">
+        <v>507</v>
+      </c>
+      <c r="E218" t="s">
+        <v>506</v>
+      </c>
+      <c r="F218" t="s">
+        <v>508</v>
+      </c>
+      <c r="G218" t="s">
+        <v>511</v>
+      </c>
+      <c r="H218">
+        <v>5</v>
+      </c>
+      <c r="I218" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219" t="s">
+        <v>504</v>
+      </c>
+      <c r="B219" t="s">
+        <v>550</v>
+      </c>
+      <c r="C219" t="s">
+        <v>532</v>
+      </c>
+      <c r="D219" t="s">
+        <v>531</v>
+      </c>
+      <c r="E219" t="s">
+        <v>532</v>
+      </c>
+      <c r="F219" t="s">
+        <v>534</v>
+      </c>
+      <c r="G219" t="s">
+        <v>551</v>
+      </c>
+      <c r="H219">
+        <v>5</v>
+      </c>
+      <c r="I219" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" t="s">
+        <v>504</v>
+      </c>
+      <c r="B220" t="s">
+        <v>552</v>
+      </c>
+      <c r="C220" t="s">
+        <v>541</v>
+      </c>
+      <c r="D220" t="s">
+        <v>540</v>
+      </c>
+      <c r="E220" t="s">
+        <v>541</v>
+      </c>
+      <c r="F220" t="s">
+        <v>508</v>
+      </c>
+      <c r="G220" t="s">
+        <v>529</v>
+      </c>
+      <c r="H220">
+        <v>5</v>
+      </c>
+      <c r="I220" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" t="s">
+        <v>504</v>
+      </c>
+      <c r="B221" t="s">
+        <v>553</v>
+      </c>
+      <c r="C221" t="s">
+        <v>507</v>
+      </c>
+      <c r="D221" t="s">
+        <v>506</v>
+      </c>
+      <c r="E221" t="s">
+        <v>507</v>
+      </c>
+      <c r="F221" t="s">
+        <v>509</v>
+      </c>
+      <c r="G221" t="s">
+        <v>511</v>
+      </c>
+      <c r="H221">
+        <v>5</v>
+      </c>
+      <c r="I221" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" t="s">
+        <v>504</v>
+      </c>
+      <c r="B222" t="s">
+        <v>554</v>
+      </c>
+      <c r="C222" t="s">
+        <v>538</v>
+      </c>
+      <c r="D222" t="s">
+        <v>529</v>
+      </c>
+      <c r="E222" t="s">
+        <v>538</v>
+      </c>
+      <c r="F222" t="s">
+        <v>517</v>
+      </c>
+      <c r="G222" t="s">
+        <v>516</v>
+      </c>
+      <c r="H222">
+        <v>5</v>
+      </c>
+      <c r="I222" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" t="s">
+        <v>504</v>
+      </c>
+      <c r="B223" t="s">
+        <v>555</v>
+      </c>
+      <c r="C223" t="s">
+        <v>520</v>
+      </c>
+      <c r="D223" t="s">
+        <v>551</v>
+      </c>
+      <c r="E223" t="s">
+        <v>520</v>
+      </c>
+      <c r="F223" t="s">
+        <v>556</v>
+      </c>
+      <c r="G223" t="s">
+        <v>557</v>
+      </c>
+      <c r="H223">
+        <v>5</v>
+      </c>
+      <c r="I223" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" t="s">
+        <v>504</v>
+      </c>
+      <c r="B224" t="s">
+        <v>558</v>
+      </c>
+      <c r="C224" t="s">
+        <v>545</v>
+      </c>
+      <c r="D224" t="s">
+        <v>514</v>
+      </c>
+      <c r="E224" t="s">
+        <v>545</v>
+      </c>
+      <c r="F224" t="s">
+        <v>506</v>
+      </c>
+      <c r="G224" t="s">
+        <v>559</v>
+      </c>
+      <c r="H224">
+        <v>5</v>
+      </c>
+      <c r="I224" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" t="s">
+        <v>504</v>
+      </c>
+      <c r="B225" t="s">
+        <v>560</v>
+      </c>
+      <c r="C225" t="s">
+        <v>561</v>
+      </c>
+      <c r="D225" t="s">
+        <v>525</v>
+      </c>
+      <c r="E225" t="s">
+        <v>561</v>
+      </c>
+      <c r="F225" t="s">
+        <v>508</v>
+      </c>
+      <c r="G225" t="s">
+        <v>524</v>
+      </c>
+      <c r="H225">
+        <v>5</v>
+      </c>
+      <c r="I225" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226" t="s">
+        <v>504</v>
+      </c>
+      <c r="B226" t="s">
+        <v>562</v>
+      </c>
+      <c r="C226" t="s">
+        <v>517</v>
+      </c>
+      <c r="D226" t="s">
+        <v>516</v>
+      </c>
+      <c r="E226" t="s">
+        <v>517</v>
+      </c>
+      <c r="F226" t="s">
+        <v>509</v>
+      </c>
+      <c r="G226" t="s">
+        <v>511</v>
+      </c>
+      <c r="H226">
+        <v>5</v>
+      </c>
+      <c r="I226" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227" t="s">
+        <v>504</v>
+      </c>
+      <c r="B227" t="s">
+        <v>563</v>
+      </c>
+      <c r="C227" t="s">
+        <v>519</v>
+      </c>
+      <c r="D227" t="s">
+        <v>512</v>
+      </c>
+      <c r="E227" t="s">
+        <v>519</v>
+      </c>
+      <c r="F227" t="s">
+        <v>564</v>
+      </c>
+      <c r="G227" t="s">
+        <v>565</v>
+      </c>
+      <c r="H227">
+        <v>5</v>
+      </c>
+      <c r="I227" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228" t="s">
+        <v>504</v>
+      </c>
+      <c r="B228" t="s">
+        <v>566</v>
+      </c>
+      <c r="C228" t="s">
+        <v>520</v>
+      </c>
+      <c r="D228" t="s">
+        <v>567</v>
+      </c>
+      <c r="E228" t="s">
+        <v>520</v>
+      </c>
+      <c r="F228" t="s">
+        <v>568</v>
+      </c>
+      <c r="G228" t="s">
+        <v>534</v>
+      </c>
+      <c r="H228">
+        <v>5</v>
+      </c>
+      <c r="I228" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="A229" t="s">
+        <v>504</v>
+      </c>
+      <c r="B229" t="s">
+        <v>569</v>
+      </c>
+      <c r="C229" t="s">
+        <v>512</v>
+      </c>
+      <c r="D229" t="s">
+        <v>548</v>
+      </c>
+      <c r="E229" t="s">
+        <v>512</v>
+      </c>
+      <c r="F229" t="s">
+        <v>551</v>
+      </c>
+      <c r="G229" t="s">
+        <v>556</v>
+      </c>
+      <c r="H229">
+        <v>5</v>
+      </c>
+      <c r="I229" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="A230" t="s">
+        <v>504</v>
+      </c>
+      <c r="B230" t="s">
+        <v>570</v>
+      </c>
+      <c r="C230" t="s">
+        <v>527</v>
+      </c>
+      <c r="D230" t="s">
+        <v>506</v>
+      </c>
+      <c r="E230" t="s">
+        <v>527</v>
+      </c>
+      <c r="F230" t="s">
+        <v>507</v>
+      </c>
+      <c r="G230" t="s">
+        <v>509</v>
+      </c>
+      <c r="H230">
+        <v>5</v>
+      </c>
+      <c r="I230" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="A231" t="s">
+        <v>504</v>
+      </c>
+      <c r="B231" t="s">
+        <v>571</v>
+      </c>
+      <c r="C231" t="s">
+        <v>514</v>
+      </c>
+      <c r="D231" t="s">
+        <v>529</v>
+      </c>
+      <c r="E231" t="s">
+        <v>514</v>
+      </c>
+      <c r="F231" t="s">
+        <v>538</v>
+      </c>
+      <c r="G231" t="s">
+        <v>531</v>
+      </c>
+      <c r="H231">
+        <v>5</v>
+      </c>
+      <c r="I231" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="A232" t="s">
+        <v>504</v>
+      </c>
+      <c r="B232" t="s">
+        <v>572</v>
+      </c>
+      <c r="C232" t="s">
+        <v>508</v>
+      </c>
+      <c r="D232" t="s">
+        <v>509</v>
+      </c>
+      <c r="E232" t="s">
+        <v>508</v>
+      </c>
+      <c r="F232" t="s">
+        <v>506</v>
+      </c>
+      <c r="G232" t="s">
+        <v>507</v>
+      </c>
+      <c r="H232">
+        <v>5</v>
+      </c>
+      <c r="I232" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="A233" t="s">
+        <v>504</v>
+      </c>
+      <c r="B233" t="s">
+        <v>573</v>
+      </c>
+      <c r="C233" t="s">
+        <v>548</v>
+      </c>
+      <c r="D233" t="s">
+        <v>551</v>
+      </c>
+      <c r="E233" t="s">
+        <v>548</v>
+      </c>
+      <c r="F233" t="s">
+        <v>557</v>
+      </c>
+      <c r="G233" t="s">
+        <v>541</v>
+      </c>
+      <c r="H233">
+        <v>5</v>
+      </c>
+      <c r="I233" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="A234" t="s">
+        <v>504</v>
+      </c>
+      <c r="B234" t="s">
+        <v>574</v>
+      </c>
+      <c r="C234" t="s">
+        <v>514</v>
+      </c>
+      <c r="D234" t="s">
+        <v>517</v>
+      </c>
+      <c r="E234" t="s">
+        <v>514</v>
+      </c>
+      <c r="F234" t="s">
+        <v>538</v>
+      </c>
+      <c r="G234" t="s">
+        <v>529</v>
+      </c>
+      <c r="H234">
+        <v>5</v>
+      </c>
+      <c r="I234" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" t="s">
+        <v>504</v>
+      </c>
+      <c r="B235" t="s">
+        <v>575</v>
+      </c>
+      <c r="C235" t="s">
+        <v>561</v>
+      </c>
+      <c r="D235" t="s">
+        <v>523</v>
+      </c>
+      <c r="E235" t="s">
+        <v>561</v>
+      </c>
+      <c r="F235" t="s">
+        <v>540</v>
+      </c>
+      <c r="G235" t="s">
+        <v>506</v>
+      </c>
+      <c r="H235">
+        <v>5</v>
+      </c>
+      <c r="I235" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
+      <c r="A236" t="s">
+        <v>504</v>
+      </c>
+      <c r="B236" t="s">
+        <v>576</v>
+      </c>
+      <c r="C236" t="s">
+        <v>556</v>
+      </c>
+      <c r="D236" t="s">
+        <v>551</v>
+      </c>
+      <c r="E236" t="s">
+        <v>556</v>
+      </c>
+      <c r="F236" t="s">
+        <v>557</v>
+      </c>
+      <c r="G236" t="s">
+        <v>520</v>
+      </c>
+      <c r="H236">
+        <v>5</v>
+      </c>
+      <c r="I236" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
+      <c r="A237" t="s">
+        <v>504</v>
+      </c>
+      <c r="B237" t="s">
+        <v>577</v>
+      </c>
+      <c r="C237" t="s">
+        <v>578</v>
+      </c>
+      <c r="D237" t="s">
+        <v>559</v>
+      </c>
+      <c r="E237" t="s">
+        <v>578</v>
+      </c>
+      <c r="F237" t="s">
+        <v>507</v>
+      </c>
+      <c r="G237" t="s">
+        <v>531</v>
+      </c>
+      <c r="H237">
+        <v>5</v>
+      </c>
+      <c r="I237" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
+      <c r="A238" t="s">
+        <v>504</v>
+      </c>
+      <c r="B238" t="s">
+        <v>579</v>
+      </c>
+      <c r="C238" t="s">
+        <v>520</v>
+      </c>
+      <c r="D238" t="s">
+        <v>557</v>
+      </c>
+      <c r="E238" t="s">
+        <v>520</v>
+      </c>
+      <c r="F238" t="s">
+        <v>551</v>
+      </c>
+      <c r="G238" t="s">
+        <v>532</v>
+      </c>
+      <c r="H238">
+        <v>5</v>
+      </c>
+      <c r="I238" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
+      <c r="A239" t="s">
+        <v>504</v>
+      </c>
+      <c r="B239" t="s">
+        <v>580</v>
+      </c>
+      <c r="C239" t="s">
+        <v>519</v>
+      </c>
+      <c r="D239" t="s">
+        <v>512</v>
+      </c>
+      <c r="E239" t="s">
+        <v>519</v>
+      </c>
+      <c r="F239" t="s">
+        <v>565</v>
+      </c>
+      <c r="G239" t="s">
+        <v>581</v>
+      </c>
+      <c r="H239">
+        <v>5</v>
+      </c>
+      <c r="I239" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
+      <c r="A240" t="s">
+        <v>504</v>
+      </c>
+      <c r="B240" t="s">
+        <v>582</v>
+      </c>
+      <c r="C240" t="s">
+        <v>506</v>
+      </c>
+      <c r="D240" t="s">
+        <v>507</v>
+      </c>
+      <c r="E240" t="s">
+        <v>506</v>
+      </c>
+      <c r="F240" t="s">
+        <v>509</v>
+      </c>
+      <c r="G240" t="s">
+        <v>523</v>
+      </c>
+      <c r="H240">
+        <v>5</v>
+      </c>
+      <c r="I240" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" t="s">
+        <v>504</v>
+      </c>
+      <c r="B241" t="s">
+        <v>583</v>
+      </c>
+      <c r="C241" t="s">
+        <v>508</v>
+      </c>
+      <c r="D241" t="s">
+        <v>584</v>
+      </c>
+      <c r="E241" t="s">
+        <v>508</v>
+      </c>
+      <c r="F241" t="s">
+        <v>509</v>
+      </c>
+      <c r="G241" t="s">
+        <v>511</v>
+      </c>
+      <c r="H241">
+        <v>5</v>
+      </c>
+      <c r="I241" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
+      <c r="A242" t="s">
+        <v>504</v>
+      </c>
+      <c r="B242" t="s">
+        <v>585</v>
+      </c>
+      <c r="C242" t="s">
+        <v>586</v>
+      </c>
+      <c r="D242" t="s">
+        <v>564</v>
+      </c>
+      <c r="E242" t="s">
+        <v>586</v>
+      </c>
+      <c r="F242" t="s">
+        <v>587</v>
+      </c>
+      <c r="G242" t="s">
+        <v>545</v>
+      </c>
+      <c r="H242">
+        <v>5</v>
+      </c>
+      <c r="I242" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
+      <c r="A243" t="s">
+        <v>504</v>
+      </c>
+      <c r="B243" t="s">
+        <v>588</v>
+      </c>
+      <c r="C243" t="s">
+        <v>548</v>
+      </c>
+      <c r="D243" t="s">
+        <v>589</v>
+      </c>
+      <c r="E243" t="s">
+        <v>548</v>
+      </c>
+      <c r="F243" t="s">
+        <v>581</v>
+      </c>
+      <c r="G243" t="s">
+        <v>565</v>
+      </c>
+      <c r="H243">
+        <v>5</v>
+      </c>
+      <c r="I243" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
+      <c r="A244" t="s">
+        <v>504</v>
+      </c>
+      <c r="B244" t="s">
+        <v>590</v>
+      </c>
+      <c r="C244" t="s">
+        <v>506</v>
+      </c>
+      <c r="D244" t="s">
+        <v>561</v>
+      </c>
+      <c r="E244" t="s">
+        <v>506</v>
+      </c>
+      <c r="F244" t="s">
+        <v>508</v>
+      </c>
+      <c r="G244" t="s">
+        <v>523</v>
+      </c>
+      <c r="H244">
+        <v>5</v>
+      </c>
+      <c r="I244" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
+      <c r="A245" t="s">
+        <v>504</v>
+      </c>
+      <c r="B245" t="s">
+        <v>591</v>
+      </c>
+      <c r="C245" t="s">
+        <v>511</v>
+      </c>
+      <c r="D245" t="s">
+        <v>509</v>
+      </c>
+      <c r="E245" t="s">
+        <v>511</v>
+      </c>
+      <c r="F245" t="s">
+        <v>507</v>
+      </c>
+      <c r="G245" t="s">
+        <v>508</v>
+      </c>
+      <c r="H245">
+        <v>5</v>
+      </c>
+      <c r="I245" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
+      <c r="A246" t="s">
+        <v>504</v>
+      </c>
+      <c r="B246" t="s">
+        <v>592</v>
+      </c>
+      <c r="C246" t="s">
+        <v>586</v>
+      </c>
+      <c r="D246" t="s">
+        <v>512</v>
+      </c>
+      <c r="E246" t="s">
+        <v>586</v>
+      </c>
+      <c r="F246" t="s">
+        <v>564</v>
+      </c>
+      <c r="G246" t="s">
+        <v>589</v>
+      </c>
+      <c r="H246">
+        <v>5</v>
+      </c>
+      <c r="I246" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
+      <c r="A247" t="s">
+        <v>504</v>
+      </c>
+      <c r="B247" t="s">
+        <v>593</v>
+      </c>
+      <c r="C247" t="s">
+        <v>507</v>
+      </c>
+      <c r="D247" t="s">
+        <v>559</v>
+      </c>
+      <c r="E247" t="s">
+        <v>507</v>
+      </c>
+      <c r="F247" t="s">
+        <v>578</v>
+      </c>
+      <c r="G247" t="s">
+        <v>514</v>
+      </c>
+      <c r="H247">
+        <v>5</v>
+      </c>
+      <c r="I247" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
+      <c r="A248" t="s">
+        <v>504</v>
+      </c>
+      <c r="B248" t="s">
+        <v>594</v>
+      </c>
+      <c r="C248" t="s">
+        <v>508</v>
+      </c>
+      <c r="D248" t="s">
+        <v>506</v>
+      </c>
+      <c r="E248" t="s">
+        <v>508</v>
+      </c>
+      <c r="F248" t="s">
+        <v>511</v>
+      </c>
+      <c r="G248" t="s">
+        <v>507</v>
+      </c>
+      <c r="H248">
+        <v>5</v>
+      </c>
+      <c r="I248" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
+      <c r="A249" t="s">
+        <v>504</v>
+      </c>
+      <c r="B249" t="s">
+        <v>595</v>
+      </c>
+      <c r="C249" t="s">
+        <v>548</v>
+      </c>
+      <c r="D249" t="s">
+        <v>512</v>
+      </c>
+      <c r="E249" t="s">
+        <v>548</v>
+      </c>
+      <c r="F249" t="s">
+        <v>589</v>
+      </c>
+      <c r="G249" t="s">
+        <v>551</v>
+      </c>
+      <c r="H249">
+        <v>5</v>
+      </c>
+      <c r="I249" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
+      <c r="A250" t="s">
+        <v>504</v>
+      </c>
+      <c r="B250" t="s">
+        <v>596</v>
+      </c>
+      <c r="C250" t="s">
+        <v>509</v>
+      </c>
+      <c r="D250" t="s">
+        <v>511</v>
+      </c>
+      <c r="E250" t="s">
+        <v>509</v>
+      </c>
+      <c r="F250" t="s">
+        <v>584</v>
+      </c>
+      <c r="G250" t="s">
+        <v>508</v>
+      </c>
+      <c r="H250">
+        <v>5</v>
+      </c>
+      <c r="I250" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
+      <c r="A251" t="s">
+        <v>504</v>
+      </c>
+      <c r="B251" t="s">
+        <v>597</v>
+      </c>
+      <c r="C251" t="s">
+        <v>531</v>
+      </c>
+      <c r="D251" t="s">
+        <v>533</v>
+      </c>
+      <c r="E251" t="s">
+        <v>531</v>
+      </c>
+      <c r="F251" t="s">
+        <v>532</v>
+      </c>
+      <c r="G251" t="s">
+        <v>534</v>
+      </c>
+      <c r="H251">
+        <v>5</v>
+      </c>
+      <c r="I251" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
+      <c r="A252" t="s">
+        <v>504</v>
+      </c>
+      <c r="B252" t="s">
+        <v>598</v>
+      </c>
+      <c r="C252" t="s">
+        <v>512</v>
+      </c>
+      <c r="D252" t="s">
+        <v>519</v>
+      </c>
+      <c r="E252" t="s">
+        <v>512</v>
+      </c>
+      <c r="F252" t="s">
+        <v>520</v>
+      </c>
+      <c r="G252" t="s">
+        <v>507</v>
+      </c>
+      <c r="H252">
+        <v>5</v>
+      </c>
+      <c r="I252" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
+      <c r="A253" t="s">
+        <v>599</v>
+      </c>
+      <c r="B253" t="s">
+        <v>600</v>
+      </c>
+      <c r="C253" t="s">
+        <v>601</v>
+      </c>
+      <c r="D253" t="s">
+        <v>602</v>
+      </c>
+      <c r="E253" t="s">
+        <v>601</v>
+      </c>
+      <c r="F253" t="s">
+        <v>603</v>
+      </c>
+      <c r="G253" t="s">
+        <v>604</v>
+      </c>
+      <c r="H253">
+        <v>5</v>
+      </c>
+      <c r="I253" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
+      <c r="A254" t="s">
+        <v>599</v>
+      </c>
+      <c r="B254" t="s">
+        <v>605</v>
+      </c>
+      <c r="C254" t="s">
+        <v>606</v>
+      </c>
+      <c r="D254" t="s">
+        <v>607</v>
+      </c>
+      <c r="E254" t="s">
+        <v>606</v>
+      </c>
+      <c r="F254" t="s">
+        <v>608</v>
+      </c>
+      <c r="G254" t="s">
+        <v>609</v>
+      </c>
+      <c r="H254">
+        <v>5</v>
+      </c>
+      <c r="I254" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
+      <c r="A255" t="s">
+        <v>599</v>
+      </c>
+      <c r="B255" t="s">
+        <v>610</v>
+      </c>
+      <c r="C255" t="s">
+        <v>611</v>
+      </c>
+      <c r="D255" t="s">
+        <v>612</v>
+      </c>
+      <c r="E255" t="s">
+        <v>611</v>
+      </c>
+      <c r="F255" t="s">
+        <v>613</v>
+      </c>
+      <c r="G255" t="s">
+        <v>614</v>
+      </c>
+      <c r="H255">
+        <v>5</v>
+      </c>
+      <c r="I255" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
+      <c r="A256" t="s">
+        <v>599</v>
+      </c>
+      <c r="B256" t="s">
+        <v>615</v>
+      </c>
+      <c r="C256" t="s">
+        <v>616</v>
+      </c>
+      <c r="D256" t="s">
+        <v>617</v>
+      </c>
+      <c r="E256" t="s">
+        <v>616</v>
+      </c>
+      <c r="F256" t="s">
+        <v>618</v>
+      </c>
+      <c r="G256" t="s">
+        <v>619</v>
+      </c>
+      <c r="H256">
+        <v>5</v>
+      </c>
+      <c r="I256" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
+      <c r="A257" t="s">
+        <v>599</v>
+      </c>
+      <c r="B257" t="s">
+        <v>620</v>
+      </c>
+      <c r="C257" t="s">
         <v>621</v>
       </c>
-      <c r="C202" t="s">
-        <v>513</v>
-      </c>
-      <c r="D202" t="s">
-        <v>515</v>
-      </c>
-      <c r="E202" t="s">
-        <v>513</v>
-      </c>
-      <c r="F202" t="s">
+      <c r="D257" t="s">
         <v>622</v>
       </c>
-      <c r="G202" t="s">
+      <c r="E257" t="s">
+        <v>621</v>
+      </c>
+      <c r="F257" t="s">
         <v>623</v>
       </c>
-      <c r="H202">
-        <v>5</v>
-      </c>
-      <c r="I202" t="b">
+      <c r="G257" t="s">
+        <v>624</v>
+      </c>
+      <c r="H257">
+        <v>5</v>
+      </c>
+      <c r="I257" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
+      <c r="A258" t="s">
+        <v>599</v>
+      </c>
+      <c r="B258" t="s">
+        <v>625</v>
+      </c>
+      <c r="C258" t="s">
+        <v>626</v>
+      </c>
+      <c r="D258" t="s">
+        <v>609</v>
+      </c>
+      <c r="E258" t="s">
+        <v>626</v>
+      </c>
+      <c r="F258" t="s">
+        <v>627</v>
+      </c>
+      <c r="G258" t="s">
+        <v>628</v>
+      </c>
+      <c r="H258">
+        <v>5</v>
+      </c>
+      <c r="I258" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
+      <c r="A259" t="s">
+        <v>599</v>
+      </c>
+      <c r="B259" t="s">
+        <v>629</v>
+      </c>
+      <c r="C259" t="s">
+        <v>630</v>
+      </c>
+      <c r="D259" t="s">
+        <v>631</v>
+      </c>
+      <c r="E259" t="s">
+        <v>630</v>
+      </c>
+      <c r="F259" t="s">
+        <v>632</v>
+      </c>
+      <c r="G259" t="s">
+        <v>633</v>
+      </c>
+      <c r="H259">
+        <v>5</v>
+      </c>
+      <c r="I259" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
+      <c r="A260" t="s">
+        <v>599</v>
+      </c>
+      <c r="B260" t="s">
+        <v>634</v>
+      </c>
+      <c r="C260" t="s">
+        <v>635</v>
+      </c>
+      <c r="D260" t="s">
+        <v>602</v>
+      </c>
+      <c r="E260" t="s">
+        <v>635</v>
+      </c>
+      <c r="F260" t="s">
+        <v>601</v>
+      </c>
+      <c r="G260" t="s">
+        <v>603</v>
+      </c>
+      <c r="H260">
+        <v>5</v>
+      </c>
+      <c r="I260" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
+      <c r="A261" t="s">
+        <v>599</v>
+      </c>
+      <c r="B261" t="s">
+        <v>636</v>
+      </c>
+      <c r="C261" t="s">
+        <v>626</v>
+      </c>
+      <c r="D261" t="s">
+        <v>637</v>
+      </c>
+      <c r="E261" t="s">
+        <v>626</v>
+      </c>
+      <c r="F261" t="s">
+        <v>638</v>
+      </c>
+      <c r="G261" t="s">
+        <v>609</v>
+      </c>
+      <c r="H261">
+        <v>5</v>
+      </c>
+      <c r="I261" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
+      <c r="A262" t="s">
+        <v>599</v>
+      </c>
+      <c r="B262" t="s">
+        <v>639</v>
+      </c>
+      <c r="C262" t="s">
+        <v>640</v>
+      </c>
+      <c r="D262" t="s">
+        <v>609</v>
+      </c>
+      <c r="E262" t="s">
+        <v>640</v>
+      </c>
+      <c r="F262" t="s">
+        <v>641</v>
+      </c>
+      <c r="G262" t="s">
+        <v>642</v>
+      </c>
+      <c r="H262">
+        <v>5</v>
+      </c>
+      <c r="I262" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
+      <c r="A263" t="s">
+        <v>599</v>
+      </c>
+      <c r="B263" t="s">
+        <v>643</v>
+      </c>
+      <c r="C263" t="s">
+        <v>644</v>
+      </c>
+      <c r="D263" t="s">
+        <v>645</v>
+      </c>
+      <c r="E263" t="s">
+        <v>644</v>
+      </c>
+      <c r="F263" t="s">
+        <v>646</v>
+      </c>
+      <c r="G263" t="s">
+        <v>647</v>
+      </c>
+      <c r="H263">
+        <v>5</v>
+      </c>
+      <c r="I263" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
+      <c r="A264" t="s">
+        <v>599</v>
+      </c>
+      <c r="B264" t="s">
+        <v>648</v>
+      </c>
+      <c r="C264" t="s">
+        <v>602</v>
+      </c>
+      <c r="D264" t="s">
+        <v>601</v>
+      </c>
+      <c r="E264" t="s">
+        <v>602</v>
+      </c>
+      <c r="F264" t="s">
+        <v>604</v>
+      </c>
+      <c r="G264" t="s">
+        <v>649</v>
+      </c>
+      <c r="H264">
+        <v>5</v>
+      </c>
+      <c r="I264" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
+      <c r="A265" t="s">
+        <v>599</v>
+      </c>
+      <c r="B265" t="s">
+        <v>650</v>
+      </c>
+      <c r="C265" t="s">
+        <v>651</v>
+      </c>
+      <c r="D265" t="s">
+        <v>652</v>
+      </c>
+      <c r="E265" t="s">
+        <v>651</v>
+      </c>
+      <c r="F265" t="s">
+        <v>653</v>
+      </c>
+      <c r="G265" t="s">
+        <v>654</v>
+      </c>
+      <c r="H265">
+        <v>5</v>
+      </c>
+      <c r="I265" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
+      <c r="A266" t="s">
+        <v>599</v>
+      </c>
+      <c r="B266" t="s">
+        <v>655</v>
+      </c>
+      <c r="C266" t="s">
+        <v>638</v>
+      </c>
+      <c r="D266" t="s">
+        <v>656</v>
+      </c>
+      <c r="E266" t="s">
+        <v>638</v>
+      </c>
+      <c r="F266" t="s">
+        <v>657</v>
+      </c>
+      <c r="G266" t="s">
+        <v>637</v>
+      </c>
+      <c r="H266">
+        <v>5</v>
+      </c>
+      <c r="I266" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
+      <c r="A267" t="s">
+        <v>599</v>
+      </c>
+      <c r="B267" t="s">
+        <v>658</v>
+      </c>
+      <c r="C267" t="s">
+        <v>659</v>
+      </c>
+      <c r="D267" t="s">
+        <v>660</v>
+      </c>
+      <c r="E267" t="s">
+        <v>659</v>
+      </c>
+      <c r="F267" t="s">
+        <v>661</v>
+      </c>
+      <c r="G267" t="s">
+        <v>662</v>
+      </c>
+      <c r="H267">
+        <v>5</v>
+      </c>
+      <c r="I267" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
+      <c r="A268" t="s">
+        <v>599</v>
+      </c>
+      <c r="B268" t="s">
+        <v>663</v>
+      </c>
+      <c r="C268" t="s">
+        <v>664</v>
+      </c>
+      <c r="D268" t="s">
+        <v>665</v>
+      </c>
+      <c r="E268" t="s">
+        <v>664</v>
+      </c>
+      <c r="F268" t="s">
+        <v>666</v>
+      </c>
+      <c r="G268" t="s">
+        <v>667</v>
+      </c>
+      <c r="H268">
+        <v>5</v>
+      </c>
+      <c r="I268" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
+      <c r="A269" t="s">
+        <v>599</v>
+      </c>
+      <c r="B269" t="s">
+        <v>668</v>
+      </c>
+      <c r="C269" t="s">
+        <v>669</v>
+      </c>
+      <c r="D269" t="s">
+        <v>640</v>
+      </c>
+      <c r="E269" t="s">
+        <v>669</v>
+      </c>
+      <c r="F269" t="s">
+        <v>670</v>
+      </c>
+      <c r="G269" t="s">
+        <v>628</v>
+      </c>
+      <c r="H269">
+        <v>5</v>
+      </c>
+      <c r="I269" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
+      <c r="A270" t="s">
+        <v>599</v>
+      </c>
+      <c r="B270" t="s">
+        <v>671</v>
+      </c>
+      <c r="C270" t="s">
+        <v>672</v>
+      </c>
+      <c r="D270" t="s">
+        <v>673</v>
+      </c>
+      <c r="E270" t="s">
+        <v>672</v>
+      </c>
+      <c r="F270" t="s">
+        <v>674</v>
+      </c>
+      <c r="G270" t="s">
+        <v>675</v>
+      </c>
+      <c r="H270">
+        <v>5</v>
+      </c>
+      <c r="I270" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
+      <c r="A271" t="s">
+        <v>599</v>
+      </c>
+      <c r="B271" t="s">
+        <v>676</v>
+      </c>
+      <c r="C271" t="s">
+        <v>677</v>
+      </c>
+      <c r="D271" t="s">
+        <v>678</v>
+      </c>
+      <c r="E271" t="s">
+        <v>677</v>
+      </c>
+      <c r="F271" t="s">
+        <v>612</v>
+      </c>
+      <c r="G271" t="s">
+        <v>613</v>
+      </c>
+      <c r="H271">
+        <v>5</v>
+      </c>
+      <c r="I271" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9">
+      <c r="A272" t="s">
+        <v>599</v>
+      </c>
+      <c r="B272" t="s">
+        <v>679</v>
+      </c>
+      <c r="C272" t="s">
+        <v>680</v>
+      </c>
+      <c r="D272" t="s">
+        <v>681</v>
+      </c>
+      <c r="E272" t="s">
+        <v>680</v>
+      </c>
+      <c r="F272" t="s">
+        <v>682</v>
+      </c>
+      <c r="G272" t="s">
+        <v>683</v>
+      </c>
+      <c r="H272">
+        <v>5</v>
+      </c>
+      <c r="I272" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="A273" t="s">
+        <v>599</v>
+      </c>
+      <c r="B273" t="s">
+        <v>684</v>
+      </c>
+      <c r="C273" t="s">
+        <v>669</v>
+      </c>
+      <c r="D273" t="s">
+        <v>642</v>
+      </c>
+      <c r="E273" t="s">
+        <v>669</v>
+      </c>
+      <c r="F273" t="s">
+        <v>685</v>
+      </c>
+      <c r="G273" t="s">
+        <v>627</v>
+      </c>
+      <c r="H273">
+        <v>5</v>
+      </c>
+      <c r="I273" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9">
+      <c r="A274" t="s">
+        <v>599</v>
+      </c>
+      <c r="B274" t="s">
+        <v>686</v>
+      </c>
+      <c r="C274" t="s">
+        <v>687</v>
+      </c>
+      <c r="D274" t="s">
+        <v>685</v>
+      </c>
+      <c r="E274" t="s">
+        <v>687</v>
+      </c>
+      <c r="F274" t="s">
+        <v>627</v>
+      </c>
+      <c r="G274" t="s">
+        <v>628</v>
+      </c>
+      <c r="H274">
+        <v>5</v>
+      </c>
+      <c r="I274" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9">
+      <c r="A275" t="s">
+        <v>599</v>
+      </c>
+      <c r="B275" t="s">
+        <v>688</v>
+      </c>
+      <c r="C275" t="s">
+        <v>602</v>
+      </c>
+      <c r="D275" t="s">
+        <v>601</v>
+      </c>
+      <c r="E275" t="s">
+        <v>602</v>
+      </c>
+      <c r="F275" t="s">
+        <v>603</v>
+      </c>
+      <c r="G275" t="s">
+        <v>649</v>
+      </c>
+      <c r="H275">
+        <v>5</v>
+      </c>
+      <c r="I275" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9">
+      <c r="A276" t="s">
+        <v>599</v>
+      </c>
+      <c r="B276" t="s">
+        <v>689</v>
+      </c>
+      <c r="C276" t="s">
+        <v>690</v>
+      </c>
+      <c r="D276" t="s">
+        <v>642</v>
+      </c>
+      <c r="E276" t="s">
+        <v>690</v>
+      </c>
+      <c r="F276" t="s">
+        <v>628</v>
+      </c>
+      <c r="G276" t="s">
+        <v>609</v>
+      </c>
+      <c r="H276">
+        <v>5</v>
+      </c>
+      <c r="I276" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9">
+      <c r="A277" t="s">
+        <v>599</v>
+      </c>
+      <c r="B277" t="s">
+        <v>691</v>
+      </c>
+      <c r="C277" t="s">
+        <v>692</v>
+      </c>
+      <c r="D277" t="s">
+        <v>635</v>
+      </c>
+      <c r="E277" t="s">
+        <v>692</v>
+      </c>
+      <c r="F277" t="s">
+        <v>680</v>
+      </c>
+      <c r="G277" t="s">
+        <v>693</v>
+      </c>
+      <c r="H277">
+        <v>5</v>
+      </c>
+      <c r="I277" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9">
+      <c r="A278" t="s">
+        <v>599</v>
+      </c>
+      <c r="B278" t="s">
+        <v>694</v>
+      </c>
+      <c r="C278" t="s">
+        <v>695</v>
+      </c>
+      <c r="D278" t="s">
+        <v>696</v>
+      </c>
+      <c r="E278" t="s">
+        <v>695</v>
+      </c>
+      <c r="F278" t="s">
+        <v>697</v>
+      </c>
+      <c r="G278" t="s">
+        <v>698</v>
+      </c>
+      <c r="H278">
+        <v>5</v>
+      </c>
+      <c r="I278" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9">
+      <c r="A279" t="s">
+        <v>599</v>
+      </c>
+      <c r="B279" t="s">
+        <v>699</v>
+      </c>
+      <c r="C279" t="s">
+        <v>700</v>
+      </c>
+      <c r="D279" t="s">
+        <v>701</v>
+      </c>
+      <c r="E279" t="s">
+        <v>700</v>
+      </c>
+      <c r="F279" t="s">
+        <v>702</v>
+      </c>
+      <c r="G279" t="s">
+        <v>703</v>
+      </c>
+      <c r="H279">
+        <v>5</v>
+      </c>
+      <c r="I279" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9">
+      <c r="A280" t="s">
+        <v>599</v>
+      </c>
+      <c r="B280" t="s">
+        <v>704</v>
+      </c>
+      <c r="C280" t="s">
+        <v>705</v>
+      </c>
+      <c r="D280" t="s">
+        <v>706</v>
+      </c>
+      <c r="E280" t="s">
+        <v>705</v>
+      </c>
+      <c r="F280" t="s">
+        <v>707</v>
+      </c>
+      <c r="G280" t="s">
+        <v>708</v>
+      </c>
+      <c r="H280">
+        <v>5</v>
+      </c>
+      <c r="I280" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9">
+      <c r="A281" t="s">
+        <v>599</v>
+      </c>
+      <c r="B281" t="s">
+        <v>709</v>
+      </c>
+      <c r="C281" t="s">
+        <v>710</v>
+      </c>
+      <c r="D281" t="s">
+        <v>711</v>
+      </c>
+      <c r="E281" t="s">
+        <v>710</v>
+      </c>
+      <c r="F281" t="s">
+        <v>712</v>
+      </c>
+      <c r="G281" t="s">
+        <v>713</v>
+      </c>
+      <c r="H281">
+        <v>5</v>
+      </c>
+      <c r="I281" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9">
+      <c r="A282" t="s">
+        <v>599</v>
+      </c>
+      <c r="B282" t="s">
+        <v>714</v>
+      </c>
+      <c r="C282" t="s">
+        <v>638</v>
+      </c>
+      <c r="D282" t="s">
+        <v>656</v>
+      </c>
+      <c r="E282" t="s">
+        <v>638</v>
+      </c>
+      <c r="F282" t="s">
+        <v>657</v>
+      </c>
+      <c r="G282" t="s">
+        <v>715</v>
+      </c>
+      <c r="H282">
+        <v>5</v>
+      </c>
+      <c r="I282" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9">
+      <c r="A283" t="s">
+        <v>599</v>
+      </c>
+      <c r="B283" t="s">
+        <v>716</v>
+      </c>
+      <c r="C283" t="s">
+        <v>717</v>
+      </c>
+      <c r="D283" t="s">
+        <v>718</v>
+      </c>
+      <c r="E283" t="s">
+        <v>717</v>
+      </c>
+      <c r="F283" t="s">
+        <v>719</v>
+      </c>
+      <c r="G283" t="s">
+        <v>720</v>
+      </c>
+      <c r="H283">
+        <v>5</v>
+      </c>
+      <c r="I283" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9">
+      <c r="A284" t="s">
+        <v>599</v>
+      </c>
+      <c r="B284" t="s">
+        <v>721</v>
+      </c>
+      <c r="C284" t="s">
+        <v>722</v>
+      </c>
+      <c r="D284" t="s">
+        <v>723</v>
+      </c>
+      <c r="E284" t="s">
+        <v>722</v>
+      </c>
+      <c r="F284" t="s">
+        <v>724</v>
+      </c>
+      <c r="G284" t="s">
+        <v>725</v>
+      </c>
+      <c r="H284">
+        <v>5</v>
+      </c>
+      <c r="I284" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9">
+      <c r="A285" t="s">
+        <v>599</v>
+      </c>
+      <c r="B285" t="s">
+        <v>726</v>
+      </c>
+      <c r="C285" t="s">
+        <v>669</v>
+      </c>
+      <c r="D285" t="s">
+        <v>628</v>
+      </c>
+      <c r="E285" t="s">
+        <v>669</v>
+      </c>
+      <c r="F285" t="s">
+        <v>685</v>
+      </c>
+      <c r="G285" t="s">
+        <v>627</v>
+      </c>
+      <c r="H285">
+        <v>5</v>
+      </c>
+      <c r="I285" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9">
+      <c r="A286" t="s">
+        <v>599</v>
+      </c>
+      <c r="B286" t="s">
+        <v>727</v>
+      </c>
+      <c r="C286" t="s">
+        <v>728</v>
+      </c>
+      <c r="D286" t="s">
+        <v>729</v>
+      </c>
+      <c r="E286" t="s">
+        <v>728</v>
+      </c>
+      <c r="F286" t="s">
+        <v>730</v>
+      </c>
+      <c r="G286" t="s">
+        <v>731</v>
+      </c>
+      <c r="H286">
+        <v>5</v>
+      </c>
+      <c r="I286" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9">
+      <c r="A287" t="s">
+        <v>599</v>
+      </c>
+      <c r="B287" t="s">
+        <v>732</v>
+      </c>
+      <c r="C287" t="s">
+        <v>733</v>
+      </c>
+      <c r="D287" t="s">
+        <v>734</v>
+      </c>
+      <c r="E287" t="s">
+        <v>733</v>
+      </c>
+      <c r="F287" t="s">
+        <v>735</v>
+      </c>
+      <c r="G287" t="s">
+        <v>736</v>
+      </c>
+      <c r="H287">
+        <v>5</v>
+      </c>
+      <c r="I287" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9">
+      <c r="A288" t="s">
+        <v>599</v>
+      </c>
+      <c r="B288" t="s">
+        <v>737</v>
+      </c>
+      <c r="C288" t="s">
+        <v>738</v>
+      </c>
+      <c r="D288" t="s">
+        <v>739</v>
+      </c>
+      <c r="E288" t="s">
+        <v>738</v>
+      </c>
+      <c r="F288" t="s">
+        <v>619</v>
+      </c>
+      <c r="G288" t="s">
+        <v>616</v>
+      </c>
+      <c r="H288">
+        <v>5</v>
+      </c>
+      <c r="I288" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9">
+      <c r="A289" t="s">
+        <v>599</v>
+      </c>
+      <c r="B289" t="s">
+        <v>740</v>
+      </c>
+      <c r="C289" t="s">
+        <v>741</v>
+      </c>
+      <c r="D289" t="s">
+        <v>611</v>
+      </c>
+      <c r="E289" t="s">
+        <v>741</v>
+      </c>
+      <c r="F289" t="s">
+        <v>612</v>
+      </c>
+      <c r="G289" t="s">
+        <v>742</v>
+      </c>
+      <c r="H289">
+        <v>5</v>
+      </c>
+      <c r="I289" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9">
+      <c r="A290" t="s">
+        <v>599</v>
+      </c>
+      <c r="B290" t="s">
+        <v>743</v>
+      </c>
+      <c r="C290" t="s">
+        <v>603</v>
+      </c>
+      <c r="D290" t="s">
+        <v>744</v>
+      </c>
+      <c r="E290" t="s">
+        <v>603</v>
+      </c>
+      <c r="F290" t="s">
+        <v>601</v>
+      </c>
+      <c r="G290" t="s">
+        <v>745</v>
+      </c>
+      <c r="H290">
+        <v>5</v>
+      </c>
+      <c r="I290" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9">
+      <c r="A291" t="s">
+        <v>599</v>
+      </c>
+      <c r="B291" t="s">
+        <v>746</v>
+      </c>
+      <c r="C291" t="s">
+        <v>745</v>
+      </c>
+      <c r="D291" t="s">
+        <v>747</v>
+      </c>
+      <c r="E291" t="s">
+        <v>745</v>
+      </c>
+      <c r="F291" t="s">
+        <v>603</v>
+      </c>
+      <c r="G291" t="s">
+        <v>748</v>
+      </c>
+      <c r="H291">
+        <v>5</v>
+      </c>
+      <c r="I291" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9">
+      <c r="A292" t="s">
+        <v>599</v>
+      </c>
+      <c r="B292" t="s">
+        <v>749</v>
+      </c>
+      <c r="C292" t="s">
+        <v>750</v>
+      </c>
+      <c r="D292" t="s">
+        <v>751</v>
+      </c>
+      <c r="E292" t="s">
+        <v>750</v>
+      </c>
+      <c r="F292" t="s">
+        <v>752</v>
+      </c>
+      <c r="G292" t="s">
+        <v>753</v>
+      </c>
+      <c r="H292">
+        <v>5</v>
+      </c>
+      <c r="I292" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9">
+      <c r="A293" t="s">
+        <v>599</v>
+      </c>
+      <c r="B293" t="s">
+        <v>754</v>
+      </c>
+      <c r="C293" t="s">
+        <v>755</v>
+      </c>
+      <c r="D293" t="s">
+        <v>756</v>
+      </c>
+      <c r="E293" t="s">
+        <v>755</v>
+      </c>
+      <c r="F293" t="s">
+        <v>757</v>
+      </c>
+      <c r="G293" t="s">
+        <v>758</v>
+      </c>
+      <c r="H293">
+        <v>5</v>
+      </c>
+      <c r="I293" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9">
+      <c r="A294" t="s">
+        <v>599</v>
+      </c>
+      <c r="B294" t="s">
+        <v>759</v>
+      </c>
+      <c r="C294" t="s">
+        <v>760</v>
+      </c>
+      <c r="D294" t="s">
+        <v>761</v>
+      </c>
+      <c r="E294" t="s">
+        <v>760</v>
+      </c>
+      <c r="F294" t="s">
+        <v>762</v>
+      </c>
+      <c r="G294" t="s">
+        <v>763</v>
+      </c>
+      <c r="H294">
+        <v>5</v>
+      </c>
+      <c r="I294" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9">
+      <c r="A295" t="s">
+        <v>599</v>
+      </c>
+      <c r="B295" t="s">
+        <v>764</v>
+      </c>
+      <c r="C295" t="s">
+        <v>626</v>
+      </c>
+      <c r="D295" t="s">
+        <v>628</v>
+      </c>
+      <c r="E295" t="s">
+        <v>626</v>
+      </c>
+      <c r="F295" t="s">
+        <v>609</v>
+      </c>
+      <c r="G295" t="s">
+        <v>685</v>
+      </c>
+      <c r="H295">
+        <v>5</v>
+      </c>
+      <c r="I295" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9">
+      <c r="A296" t="s">
+        <v>599</v>
+      </c>
+      <c r="B296" t="s">
+        <v>765</v>
+      </c>
+      <c r="C296" t="s">
+        <v>766</v>
+      </c>
+      <c r="D296" t="s">
+        <v>767</v>
+      </c>
+      <c r="E296" t="s">
+        <v>766</v>
+      </c>
+      <c r="F296" t="s">
+        <v>768</v>
+      </c>
+      <c r="G296" t="s">
+        <v>769</v>
+      </c>
+      <c r="H296">
+        <v>5</v>
+      </c>
+      <c r="I296" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9">
+      <c r="A297" t="s">
+        <v>599</v>
+      </c>
+      <c r="B297" t="s">
+        <v>770</v>
+      </c>
+      <c r="C297" t="s">
+        <v>771</v>
+      </c>
+      <c r="D297" t="s">
+        <v>772</v>
+      </c>
+      <c r="E297" t="s">
+        <v>771</v>
+      </c>
+      <c r="F297" t="s">
+        <v>292</v>
+      </c>
+      <c r="G297" t="s">
+        <v>773</v>
+      </c>
+      <c r="H297">
+        <v>5</v>
+      </c>
+      <c r="I297" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9">
+      <c r="A298" t="s">
+        <v>599</v>
+      </c>
+      <c r="B298" t="s">
+        <v>774</v>
+      </c>
+      <c r="C298" t="s">
+        <v>775</v>
+      </c>
+      <c r="D298" t="s">
+        <v>776</v>
+      </c>
+      <c r="E298" t="s">
+        <v>775</v>
+      </c>
+      <c r="F298" t="s">
+        <v>777</v>
+      </c>
+      <c r="G298" t="s">
+        <v>778</v>
+      </c>
+      <c r="H298">
+        <v>5</v>
+      </c>
+      <c r="I298" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9">
+      <c r="A299" t="s">
+        <v>599</v>
+      </c>
+      <c r="B299" t="s">
+        <v>779</v>
+      </c>
+      <c r="C299" t="s">
+        <v>780</v>
+      </c>
+      <c r="D299" t="s">
+        <v>781</v>
+      </c>
+      <c r="E299" t="s">
+        <v>780</v>
+      </c>
+      <c r="F299" t="s">
+        <v>782</v>
+      </c>
+      <c r="G299" t="s">
+        <v>783</v>
+      </c>
+      <c r="H299">
+        <v>5</v>
+      </c>
+      <c r="I299" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9">
+      <c r="A300" t="s">
+        <v>599</v>
+      </c>
+      <c r="B300" t="s">
+        <v>784</v>
+      </c>
+      <c r="C300" t="s">
+        <v>785</v>
+      </c>
+      <c r="D300" t="s">
+        <v>786</v>
+      </c>
+      <c r="E300" t="s">
+        <v>785</v>
+      </c>
+      <c r="F300" t="s">
+        <v>787</v>
+      </c>
+      <c r="G300" t="s">
+        <v>788</v>
+      </c>
+      <c r="H300">
+        <v>5</v>
+      </c>
+      <c r="I300" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9">
+      <c r="A301" t="s">
+        <v>599</v>
+      </c>
+      <c r="B301" t="s">
+        <v>789</v>
+      </c>
+      <c r="C301" t="s">
+        <v>672</v>
+      </c>
+      <c r="D301" t="s">
+        <v>790</v>
+      </c>
+      <c r="E301" t="s">
+        <v>672</v>
+      </c>
+      <c r="F301" t="s">
+        <v>673</v>
+      </c>
+      <c r="G301" t="s">
+        <v>674</v>
+      </c>
+      <c r="H301">
+        <v>5</v>
+      </c>
+      <c r="I301" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9">
+      <c r="A302" t="s">
+        <v>599</v>
+      </c>
+      <c r="B302" t="s">
+        <v>791</v>
+      </c>
+      <c r="C302" t="s">
+        <v>792</v>
+      </c>
+      <c r="D302" t="s">
+        <v>690</v>
+      </c>
+      <c r="E302" t="s">
+        <v>792</v>
+      </c>
+      <c r="F302" t="s">
+        <v>642</v>
+      </c>
+      <c r="G302" t="s">
+        <v>609</v>
+      </c>
+      <c r="H302">
+        <v>5</v>
+      </c>
+      <c r="I302" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9">
+      <c r="A303" t="s">
+        <v>599</v>
+      </c>
+      <c r="B303" t="s">
+        <v>793</v>
+      </c>
+      <c r="C303" t="s">
+        <v>794</v>
+      </c>
+      <c r="D303" t="s">
+        <v>795</v>
+      </c>
+      <c r="E303" t="s">
+        <v>794</v>
+      </c>
+      <c r="F303" t="s">
+        <v>796</v>
+      </c>
+      <c r="G303" t="s">
+        <v>797</v>
+      </c>
+      <c r="H303">
+        <v>5</v>
+      </c>
+      <c r="I303" t="b">
         <v>0</v>
       </c>
     </row>
